--- a/data/ATH PRICE LIST - MAIN.xlsx
+++ b/data/ATH PRICE LIST - MAIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1037F93-50F7-47EB-9B07-0AEDF72C9C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED65F06-6616-4804-852C-663334A79F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRY STORE" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="HYGIENE" sheetId="2" r:id="rId3"/>
+    <sheet name="HYGIENE" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="1290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="1386">
   <si>
     <t>ITEM CODE</t>
   </si>
@@ -3900,13 +3900,301 @@
   </si>
   <si>
     <t>SODACREAM</t>
+  </si>
+  <si>
+    <t>ATH-HYG001</t>
+  </si>
+  <si>
+    <t>WASHING POWDER 10KG</t>
+  </si>
+  <si>
+    <t>ATH-HYG002</t>
+  </si>
+  <si>
+    <t>WASHING POWDER 6X1KG</t>
+  </si>
+  <si>
+    <t>ATH-HYG003</t>
+  </si>
+  <si>
+    <t>FABRIC SOFTNER 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG004</t>
+  </si>
+  <si>
+    <t>WASHING UP LIQUID 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG005</t>
+  </si>
+  <si>
+    <t>RINSE AID 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG006</t>
+  </si>
+  <si>
+    <t>DISHWASHER POWDER 5KG</t>
+  </si>
+  <si>
+    <t>ATH-HYG007</t>
+  </si>
+  <si>
+    <t>DISHWASHER LIQUID 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG008</t>
+  </si>
+  <si>
+    <t>GREEN PAN SCRUBS 10NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG009</t>
+  </si>
+  <si>
+    <t>BRUSHES FOR DISHWASHING NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG010</t>
+  </si>
+  <si>
+    <t>RUBBER GLOVES KITCHEN 6PAIR</t>
+  </si>
+  <si>
+    <t>ATH-HYG011</t>
+  </si>
+  <si>
+    <t>SPONGE WITH SCRUBBER 5NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG012</t>
+  </si>
+  <si>
+    <t>WIRE PAN SCRUBS 10NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG013</t>
+  </si>
+  <si>
+    <t>LATEX GLOVES FOR COOKS 100NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG014</t>
+  </si>
+  <si>
+    <t>BLEACH 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG015</t>
+  </si>
+  <si>
+    <t>ANTI BAC LIQUID CLEANER SPRAY 6X750ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG016</t>
+  </si>
+  <si>
+    <t>JIF CREAM CLEANER 15X500ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG017</t>
+  </si>
+  <si>
+    <t>WINDOW CLEANER 6X750ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG018</t>
+  </si>
+  <si>
+    <t>MULTI CLEANING SPRAY 6X750ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG019</t>
+  </si>
+  <si>
+    <t>FLOOR POLISH 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG020</t>
+  </si>
+  <si>
+    <t>FLOOR STRIPPER 5LTR</t>
+  </si>
+  <si>
+    <t>ATH-HYG021</t>
+  </si>
+  <si>
+    <t>KITCHEN SPRAY 6X750ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG022</t>
+  </si>
+  <si>
+    <t>FLY SPRAY 300ML 6X300ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG023</t>
+  </si>
+  <si>
+    <t>TOILET CLANER LIQUID 6X750ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG024</t>
+  </si>
+  <si>
+    <t>TOILET AIR FRESHNER SPRAY 6X400ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG025</t>
+  </si>
+  <si>
+    <t>TOILET PAPER  ROLL 60NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG026</t>
+  </si>
+  <si>
+    <t>BLACK BIN LINERS 200</t>
+  </si>
+  <si>
+    <t>ATH-HYG027</t>
+  </si>
+  <si>
+    <t>SWING BIN LINERS 20X15NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG028</t>
+  </si>
+  <si>
+    <t>PEDAL BIN LINERS 20X30NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG029</t>
+  </si>
+  <si>
+    <t>PAPER TOWEL ROLL  CENTRE FEED 6NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG030</t>
+  </si>
+  <si>
+    <t>CLING FILM ROL CATERING SIZE 18INCH</t>
+  </si>
+  <si>
+    <t>ATH-HYG031</t>
+  </si>
+  <si>
+    <t>ALUMINIUM FOIL - CATERING SIZE  ROLL 18INCH</t>
+  </si>
+  <si>
+    <t>ATH-HYG032</t>
+  </si>
+  <si>
+    <t>BAKING PAPER (GREASEPROOF PAPER) ROLL</t>
+  </si>
+  <si>
+    <t>ATH-HYG033</t>
+  </si>
+  <si>
+    <t>PLASTIC FORKS 1000</t>
+  </si>
+  <si>
+    <t>ATH-HYG034</t>
+  </si>
+  <si>
+    <t>PLASTIC KNIVES 1000</t>
+  </si>
+  <si>
+    <t>ATH-HYG035</t>
+  </si>
+  <si>
+    <t>PLASTIC TEASPOON 1000</t>
+  </si>
+  <si>
+    <t>ATH-HYG036</t>
+  </si>
+  <si>
+    <t>EPS POLY CUPS 7OZ 1000</t>
+  </si>
+  <si>
+    <t>ATH-HYG037</t>
+  </si>
+  <si>
+    <t>PAPER CUPS 10OZ 1000</t>
+  </si>
+  <si>
+    <t>ATH-HYG038</t>
+  </si>
+  <si>
+    <t>PLASIC CUPS 7OZ 2000</t>
+  </si>
+  <si>
+    <t>ATH-HYG039</t>
+  </si>
+  <si>
+    <t>WHITE PAPER  TABLE NAPKINS 5000</t>
+  </si>
+  <si>
+    <t>ATH-HYG040</t>
+  </si>
+  <si>
+    <t>TOOTHPASTE 12NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG041</t>
+  </si>
+  <si>
+    <t>TOOTHBRUSH 12NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG042</t>
+  </si>
+  <si>
+    <t>SHOWER GEL 6X250ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG043</t>
+  </si>
+  <si>
+    <t>SOAP BAR DOVE 100G</t>
+  </si>
+  <si>
+    <t>ATH-HYG044</t>
+  </si>
+  <si>
+    <t>SHAMPOO 6NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG045</t>
+  </si>
+  <si>
+    <t>HAND SOAP LIQUID WITH PUMP 6X250ML</t>
+  </si>
+  <si>
+    <t>ATH-HYG046</t>
+  </si>
+  <si>
+    <t>DEODORANT SPRAY 6NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG047</t>
+  </si>
+  <si>
+    <t>DISPOSABLE RAZOR 5X5NO</t>
+  </si>
+  <si>
+    <t>ATH-HYG048</t>
+  </si>
+  <si>
+    <t>SHAVING FOAM 6NO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3945,6 +4233,19 @@
       <name val="Open Sans"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF003459"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3969,7 +4270,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3992,11 +4293,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD7E2EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7E2EA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD7E2EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4031,6 +4345,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4374,15 +4709,12 @@
   <dimension ref="A1:H631"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="8" width="14" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="47.77734375" customWidth="1"/>
+    <col min="3" max="8" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4408,7 +4740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -4434,7 +4766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -4454,14 +4786,14 @@
         <v>8.51</v>
       </c>
       <c r="G3" s="5">
-        <f>F3*1.6</f>
-        <v>13.616</v>
+        <f>F3*1.3</f>
+        <v>11.063000000000001</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -4481,14 +4813,14 @@
         <v>7.5</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" ref="G4:G67" si="0">F4*1.6</f>
-        <v>12</v>
+        <f t="shared" ref="G4:G67" si="0">F4*1.3</f>
+        <v>9.75</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -4509,7 +4841,7 @@
       </c>
       <c r="G5" s="5">
         <f t="shared" si="0"/>
-        <v>6.6239999999999997</v>
+        <v>5.3819999999999997</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>9</v>
@@ -4536,7 +4868,7 @@
       </c>
       <c r="G6" s="5">
         <f t="shared" si="0"/>
-        <v>6.8959999999999999</v>
+        <v>5.6029999999999998</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>9</v>
@@ -4557,7 +4889,7 @@
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>40.112000000000002</v>
+        <v>32.591000000000001</v>
       </c>
       <c r="H7" s="10"/>
     </row>
@@ -4576,7 +4908,7 @@
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>35.616000000000007</v>
+        <v>28.938000000000002</v>
       </c>
       <c r="H8" s="10"/>
     </row>
@@ -4601,7 +4933,7 @@
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>20.16</v>
+        <v>16.38</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>9</v>
@@ -4628,7 +4960,7 @@
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>16.32</v>
+        <v>13.26</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>9</v>
@@ -4649,7 +4981,7 @@
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>24.463999999999999</v>
+        <v>19.876999999999999</v>
       </c>
       <c r="H11" s="10"/>
     </row>
@@ -4674,7 +5006,7 @@
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>16.32</v>
+        <v>13.26</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>9</v>
@@ -4701,7 +5033,7 @@
       </c>
       <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>17.28</v>
+        <v>14.040000000000001</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>9</v>
@@ -4722,7 +5054,7 @@
       </c>
       <c r="G14" s="5">
         <f t="shared" si="0"/>
-        <v>14.384</v>
+        <v>11.687000000000001</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -4747,7 +5079,7 @@
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>17.28</v>
+        <v>14.040000000000001</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>9</v>
@@ -4768,7 +5100,7 @@
       </c>
       <c r="G16" s="5">
         <f t="shared" si="0"/>
-        <v>21.6</v>
+        <v>17.55</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -4793,13 +5125,13 @@
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>20.256</v>
+        <v>16.458000000000002</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>1203</v>
       </c>
@@ -4820,13 +5152,13 @@
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>17.760000000000002</v>
+        <v>14.43</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>1204</v>
       </c>
@@ -4847,13 +5179,13 @@
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>23.984000000000002</v>
+        <v>19.487000000000002</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>1205</v>
       </c>
@@ -4874,13 +5206,13 @@
       </c>
       <c r="G20" s="5">
         <f t="shared" si="0"/>
-        <v>21.680000000000003</v>
+        <v>17.615000000000002</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>1206</v>
       </c>
@@ -4901,7 +5233,7 @@
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>5.7439999999999998</v>
+        <v>4.6669999999999998</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>9</v>
@@ -4928,7 +5260,7 @@
       </c>
       <c r="G22" s="5">
         <f t="shared" si="0"/>
-        <v>14.384</v>
+        <v>11.687000000000001</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>9</v>
@@ -4981,7 +5313,7 @@
       </c>
       <c r="G24" s="5">
         <f t="shared" si="0"/>
-        <v>18.224</v>
+        <v>14.807</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>9</v>
@@ -5008,7 +5340,7 @@
       </c>
       <c r="G25" s="5">
         <f t="shared" si="0"/>
-        <v>17.263999999999999</v>
+        <v>14.026999999999999</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>9</v>
@@ -5035,7 +5367,7 @@
       </c>
       <c r="G26" s="5">
         <f t="shared" si="0"/>
-        <v>18.224</v>
+        <v>14.807</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>9</v>
@@ -5062,7 +5394,7 @@
       </c>
       <c r="G27" s="5">
         <f t="shared" si="0"/>
-        <v>38.384</v>
+        <v>31.186999999999998</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>9</v>
@@ -5089,7 +5421,7 @@
       </c>
       <c r="G28" s="5">
         <f t="shared" si="0"/>
-        <v>19.760000000000002</v>
+        <v>16.055</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>9</v>
@@ -5116,7 +5448,7 @@
       </c>
       <c r="G29" s="5">
         <f t="shared" si="0"/>
-        <v>47.984000000000002</v>
+        <v>38.987000000000002</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>9</v>
@@ -5143,7 +5475,7 @@
       </c>
       <c r="G30" s="5">
         <f t="shared" si="0"/>
-        <v>20.144000000000002</v>
+        <v>16.367000000000001</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>9</v>
@@ -5170,7 +5502,7 @@
       </c>
       <c r="G31" s="5">
         <f t="shared" si="0"/>
-        <v>20.144000000000002</v>
+        <v>16.367000000000001</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>9</v>
@@ -5197,7 +5529,7 @@
       </c>
       <c r="G32" s="5">
         <f t="shared" si="0"/>
-        <v>38.207999999999998</v>
+        <v>31.044</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>9</v>
@@ -5224,7 +5556,7 @@
       </c>
       <c r="G33" s="5">
         <f t="shared" si="0"/>
-        <v>23.408000000000001</v>
+        <v>19.019000000000002</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>9</v>
@@ -5251,7 +5583,7 @@
       </c>
       <c r="G34" s="5">
         <f t="shared" si="0"/>
-        <v>18.224</v>
+        <v>14.807</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>9</v>
@@ -5278,7 +5610,7 @@
       </c>
       <c r="G35" s="5">
         <f t="shared" si="0"/>
-        <v>23.408000000000001</v>
+        <v>19.019000000000002</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>9</v>
@@ -5305,7 +5637,7 @@
       </c>
       <c r="G36" s="5">
         <f t="shared" si="0"/>
-        <v>18.175999999999998</v>
+        <v>14.767999999999999</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>9</v>
@@ -5358,7 +5690,7 @@
       </c>
       <c r="G38" s="5">
         <f t="shared" si="0"/>
-        <v>12.56</v>
+        <v>10.205</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>9</v>
@@ -5385,7 +5717,7 @@
       </c>
       <c r="G39" s="5">
         <f t="shared" si="0"/>
-        <v>12.56</v>
+        <v>10.205</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>9</v>
@@ -5412,7 +5744,7 @@
       </c>
       <c r="G40" s="5">
         <f t="shared" si="0"/>
-        <v>12.56</v>
+        <v>10.205</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>9</v>
@@ -5439,7 +5771,7 @@
       </c>
       <c r="G41" s="5">
         <f t="shared" si="0"/>
-        <v>30.8</v>
+        <v>25.025000000000002</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>9</v>
@@ -5466,7 +5798,7 @@
       </c>
       <c r="G42" s="5">
         <f t="shared" si="0"/>
-        <v>23.6</v>
+        <v>19.175000000000001</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>9</v>
@@ -5493,7 +5825,7 @@
       </c>
       <c r="G43" s="5">
         <f t="shared" si="0"/>
-        <v>14.384</v>
+        <v>11.687000000000001</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>9</v>
@@ -5520,7 +5852,7 @@
       </c>
       <c r="G44" s="5">
         <f t="shared" si="0"/>
-        <v>13.584000000000001</v>
+        <v>11.037000000000001</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>9</v>
@@ -5547,7 +5879,7 @@
       </c>
       <c r="G45" s="5">
         <f t="shared" si="0"/>
-        <v>18.8</v>
+        <v>15.275</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>9</v>
@@ -5574,7 +5906,7 @@
       </c>
       <c r="G46" s="5">
         <f t="shared" si="0"/>
-        <v>38.384</v>
+        <v>31.186999999999998</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>9</v>
@@ -5601,7 +5933,7 @@
       </c>
       <c r="G47" s="5">
         <f t="shared" si="0"/>
-        <v>29.904000000000003</v>
+        <v>24.297000000000004</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>9</v>
@@ -5628,7 +5960,7 @@
       </c>
       <c r="G48" s="5">
         <f t="shared" si="0"/>
-        <v>42.224000000000004</v>
+        <v>34.307000000000002</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>9</v>
@@ -5680,8 +6012,8 @@
         <v>118.69</v>
       </c>
       <c r="G50" s="5">
-        <f t="shared" si="0"/>
-        <v>189.904</v>
+        <f>F50*1.25</f>
+        <v>148.36250000000001</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>9</v>
@@ -5707,8 +6039,8 @@
         <v>16.489999999999998</v>
       </c>
       <c r="G51" s="5">
-        <f t="shared" si="0"/>
-        <v>26.384</v>
+        <f t="shared" ref="G51:G114" si="1">F51*1.25</f>
+        <v>20.612499999999997</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>9</v>
@@ -5734,8 +6066,8 @@
         <v>78.989999999999995</v>
       </c>
       <c r="G52" s="5">
-        <f t="shared" si="0"/>
-        <v>126.384</v>
+        <f t="shared" si="1"/>
+        <v>98.737499999999997</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>9</v>
@@ -5761,8 +6093,8 @@
         <v>10.99</v>
       </c>
       <c r="G53" s="5">
-        <f t="shared" si="0"/>
-        <v>17.584</v>
+        <f t="shared" si="1"/>
+        <v>13.737500000000001</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>9</v>
@@ -5788,8 +6120,8 @@
         <v>28.99</v>
       </c>
       <c r="G54" s="5">
-        <f t="shared" si="0"/>
-        <v>46.384</v>
+        <f t="shared" si="1"/>
+        <v>36.237499999999997</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>9</v>
@@ -5815,8 +6147,8 @@
         <v>31.99</v>
       </c>
       <c r="G55" s="5">
-        <f t="shared" si="0"/>
-        <v>51.183999999999997</v>
+        <f t="shared" si="1"/>
+        <v>39.987499999999997</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>9</v>
@@ -5842,8 +6174,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G56" s="5">
-        <f t="shared" si="0"/>
-        <v>27.183999999999997</v>
+        <f t="shared" si="1"/>
+        <v>21.237499999999997</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>9</v>
@@ -5869,8 +6201,8 @@
         <v>29.99</v>
       </c>
       <c r="G57" s="5">
-        <f t="shared" si="0"/>
-        <v>47.984000000000002</v>
+        <f t="shared" si="1"/>
+        <v>37.487499999999997</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>9</v>
@@ -5896,8 +6228,8 @@
         <v>17.489999999999998</v>
       </c>
       <c r="G58" s="5">
-        <f t="shared" si="0"/>
-        <v>27.983999999999998</v>
+        <f t="shared" si="1"/>
+        <v>21.862499999999997</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>9</v>
@@ -5923,8 +6255,8 @@
         <v>9.99</v>
       </c>
       <c r="G59" s="5">
-        <f t="shared" si="0"/>
-        <v>15.984000000000002</v>
+        <f t="shared" si="1"/>
+        <v>12.487500000000001</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>9</v>
@@ -5950,8 +6282,8 @@
         <v>6.49</v>
       </c>
       <c r="G60" s="5">
-        <f t="shared" si="0"/>
-        <v>10.384</v>
+        <f t="shared" si="1"/>
+        <v>8.1125000000000007</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>9</v>
@@ -5977,8 +6309,8 @@
         <v>6.59</v>
       </c>
       <c r="G61" s="5">
-        <f t="shared" si="0"/>
-        <v>10.544</v>
+        <f t="shared" si="1"/>
+        <v>8.2375000000000007</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>9</v>
@@ -6004,8 +6336,8 @@
         <v>9.99</v>
       </c>
       <c r="G62" s="5">
-        <f t="shared" si="0"/>
-        <v>15.984000000000002</v>
+        <f t="shared" si="1"/>
+        <v>12.487500000000001</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>9</v>
@@ -6057,8 +6389,8 @@
         <v>8.89</v>
       </c>
       <c r="G64" s="5">
-        <f t="shared" si="0"/>
-        <v>14.224000000000002</v>
+        <f t="shared" si="1"/>
+        <v>11.112500000000001</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>9</v>
@@ -6084,8 +6416,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G65" s="5">
-        <f t="shared" si="0"/>
-        <v>27.183999999999997</v>
+        <f t="shared" si="1"/>
+        <v>21.237499999999997</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>9</v>
@@ -6111,8 +6443,8 @@
         <v>5.75</v>
       </c>
       <c r="G66" s="5">
-        <f t="shared" si="0"/>
-        <v>9.2000000000000011</v>
+        <f t="shared" si="1"/>
+        <v>7.1875</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>9</v>
@@ -6138,8 +6470,8 @@
         <v>22.99</v>
       </c>
       <c r="G67" s="5">
-        <f t="shared" si="0"/>
-        <v>36.783999999999999</v>
+        <f t="shared" si="1"/>
+        <v>28.737499999999997</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>9</v>
@@ -6165,8 +6497,8 @@
         <v>11.59</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" ref="G68:G131" si="1">F68*1.6</f>
-        <v>18.544</v>
+        <f t="shared" si="1"/>
+        <v>14.487500000000001</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>9</v>
@@ -6193,7 +6525,7 @@
       </c>
       <c r="G69" s="5">
         <f t="shared" si="1"/>
-        <v>18.544</v>
+        <v>14.487500000000001</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>9</v>
@@ -6220,7 +6552,7 @@
       </c>
       <c r="G70" s="5">
         <f t="shared" si="1"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>9</v>
@@ -6247,7 +6579,7 @@
       </c>
       <c r="G71" s="5">
         <f t="shared" si="1"/>
-        <v>11.344000000000001</v>
+        <v>8.8625000000000007</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>9</v>
@@ -6274,7 +6606,7 @@
       </c>
       <c r="G72" s="5">
         <f t="shared" si="1"/>
-        <v>10.544</v>
+        <v>8.2375000000000007</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>9</v>
@@ -6301,7 +6633,7 @@
       </c>
       <c r="G73" s="5">
         <f t="shared" si="1"/>
-        <v>15.984000000000002</v>
+        <v>12.487500000000001</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>9</v>
@@ -6328,7 +6660,7 @@
       </c>
       <c r="G74" s="5">
         <f t="shared" si="1"/>
-        <v>11.184000000000001</v>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>9</v>
@@ -6355,7 +6687,7 @@
       </c>
       <c r="G75" s="5">
         <f t="shared" si="1"/>
-        <v>3.5200000000000005</v>
+        <v>2.75</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>9</v>
@@ -6382,7 +6714,7 @@
       </c>
       <c r="G76" s="5">
         <f t="shared" si="1"/>
-        <v>16.784000000000002</v>
+        <v>13.112500000000001</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>9</v>
@@ -6409,7 +6741,7 @@
       </c>
       <c r="G77" s="5">
         <f t="shared" si="1"/>
-        <v>16.463999999999999</v>
+        <v>12.862499999999999</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>9</v>
@@ -6430,7 +6762,7 @@
       </c>
       <c r="G78" s="5">
         <f t="shared" si="1"/>
-        <v>50.384</v>
+        <v>39.362499999999997</v>
       </c>
       <c r="H78" s="10"/>
     </row>
@@ -6455,7 +6787,7 @@
       </c>
       <c r="G79" s="5">
         <f t="shared" si="1"/>
-        <v>15.824000000000002</v>
+        <v>12.362500000000001</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>9</v>
@@ -6508,7 +6840,7 @@
       </c>
       <c r="G81" s="5">
         <f t="shared" si="1"/>
-        <v>45.584000000000003</v>
+        <v>35.612499999999997</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>9</v>
@@ -6535,7 +6867,7 @@
       </c>
       <c r="G82" s="5">
         <f t="shared" si="1"/>
-        <v>18.864000000000001</v>
+        <v>14.737499999999999</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>9</v>
@@ -6562,7 +6894,7 @@
       </c>
       <c r="G83" s="5">
         <f t="shared" si="1"/>
-        <v>25.584000000000003</v>
+        <v>19.987500000000001</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>9</v>
@@ -6589,7 +6921,7 @@
       </c>
       <c r="G84" s="5">
         <f t="shared" si="1"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>9</v>
@@ -6616,7 +6948,7 @@
       </c>
       <c r="G85" s="5">
         <f t="shared" si="1"/>
-        <v>27.183999999999997</v>
+        <v>21.237499999999997</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>9</v>
@@ -6643,7 +6975,7 @@
       </c>
       <c r="G86" s="5">
         <f t="shared" si="1"/>
-        <v>27.183999999999997</v>
+        <v>21.237499999999997</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>9</v>
@@ -6696,7 +7028,7 @@
       </c>
       <c r="G88" s="5">
         <f t="shared" si="1"/>
-        <v>15.824000000000002</v>
+        <v>12.362500000000001</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>9</v>
@@ -6723,7 +7055,7 @@
       </c>
       <c r="G89" s="5">
         <f t="shared" si="1"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>9</v>
@@ -6750,7 +7082,7 @@
       </c>
       <c r="G90" s="5">
         <f t="shared" si="1"/>
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>9</v>
@@ -6777,7 +7109,7 @@
       </c>
       <c r="G91" s="5">
         <f t="shared" si="1"/>
-        <v>2.2399999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>9</v>
@@ -6804,7 +7136,7 @@
       </c>
       <c r="G92" s="5">
         <f t="shared" si="1"/>
-        <v>21.263999999999999</v>
+        <v>16.612499999999997</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>9</v>
@@ -6831,7 +7163,7 @@
       </c>
       <c r="G93" s="5">
         <f t="shared" si="1"/>
-        <v>21.263999999999999</v>
+        <v>16.612499999999997</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>9</v>
@@ -6858,7 +7190,7 @@
       </c>
       <c r="G94" s="5">
         <f t="shared" si="1"/>
-        <v>38.64</v>
+        <v>30.1875</v>
       </c>
       <c r="H94" s="10" t="s">
         <v>9</v>
@@ -6885,7 +7217,7 @@
       </c>
       <c r="G95" s="5">
         <f t="shared" si="1"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>9</v>
@@ -6912,7 +7244,7 @@
       </c>
       <c r="G96" s="5">
         <f t="shared" si="1"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>9</v>
@@ -6939,7 +7271,7 @@
       </c>
       <c r="G97" s="5">
         <f t="shared" si="1"/>
-        <v>24.624000000000002</v>
+        <v>19.237500000000001</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>9</v>
@@ -6966,7 +7298,7 @@
       </c>
       <c r="G98" s="5">
         <f t="shared" si="1"/>
-        <v>163.024</v>
+        <v>127.3625</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>9</v>
@@ -7046,7 +7378,7 @@
       </c>
       <c r="G101" s="5">
         <f t="shared" si="1"/>
-        <v>68.784000000000006</v>
+        <v>53.737500000000004</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>9</v>
@@ -7073,7 +7405,7 @@
       </c>
       <c r="G102" s="5">
         <f t="shared" si="1"/>
-        <v>17.584</v>
+        <v>13.737500000000001</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>9</v>
@@ -7100,7 +7432,7 @@
       </c>
       <c r="G103" s="5">
         <f t="shared" si="1"/>
-        <v>31.344000000000001</v>
+        <v>24.487500000000001</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>9</v>
@@ -7127,7 +7459,7 @@
       </c>
       <c r="G104" s="5">
         <f t="shared" si="1"/>
-        <v>17.263999999999999</v>
+        <v>13.487499999999999</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>9</v>
@@ -7154,7 +7486,7 @@
       </c>
       <c r="G105" s="5">
         <f t="shared" si="1"/>
-        <v>13.744</v>
+        <v>10.737500000000001</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>9</v>
@@ -7207,7 +7539,7 @@
       </c>
       <c r="G107" s="5">
         <f t="shared" si="1"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>9</v>
@@ -7234,7 +7566,7 @@
       </c>
       <c r="G108" s="5">
         <f t="shared" si="1"/>
-        <v>2.4000000000000004</v>
+        <v>1.875</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>9</v>
@@ -7261,7 +7593,7 @@
       </c>
       <c r="G109" s="5">
         <f t="shared" si="1"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>9</v>
@@ -7288,7 +7620,7 @@
       </c>
       <c r="G110" s="5">
         <f t="shared" si="1"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>9</v>
@@ -7315,7 +7647,7 @@
       </c>
       <c r="G111" s="5">
         <f t="shared" si="1"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>9</v>
@@ -7342,7 +7674,7 @@
       </c>
       <c r="G112" s="5">
         <f t="shared" si="1"/>
-        <v>39.984000000000002</v>
+        <v>31.237499999999997</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>9</v>
@@ -7369,7 +7701,7 @@
       </c>
       <c r="G113" s="5">
         <f t="shared" si="1"/>
-        <v>11.440000000000001</v>
+        <v>8.9375</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>9</v>
@@ -7396,7 +7728,7 @@
       </c>
       <c r="G114" s="5">
         <f t="shared" si="1"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>9</v>
@@ -7422,8 +7754,8 @@
         <v>8.99</v>
       </c>
       <c r="G115" s="5">
-        <f t="shared" si="1"/>
-        <v>14.384</v>
+        <f t="shared" ref="G115:G178" si="2">F115*1.25</f>
+        <v>11.237500000000001</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>9</v>
@@ -7475,8 +7807,8 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G117" s="5">
-        <f t="shared" si="1"/>
-        <v>31.983999999999998</v>
+        <f t="shared" si="2"/>
+        <v>24.987499999999997</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>9</v>
@@ -7502,8 +7834,8 @@
         <v>14.99</v>
       </c>
       <c r="G118" s="5">
-        <f t="shared" si="1"/>
-        <v>23.984000000000002</v>
+        <f t="shared" si="2"/>
+        <v>18.737500000000001</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>9</v>
@@ -7529,8 +7861,8 @@
         <v>9.49</v>
       </c>
       <c r="G119" s="5">
-        <f t="shared" si="1"/>
-        <v>15.184000000000001</v>
+        <f t="shared" si="2"/>
+        <v>11.862500000000001</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>9</v>
@@ -7556,8 +7888,8 @@
         <v>14.99</v>
       </c>
       <c r="G120" s="5">
-        <f t="shared" si="1"/>
-        <v>23.984000000000002</v>
+        <f t="shared" si="2"/>
+        <v>18.737500000000001</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>9</v>
@@ -7583,8 +7915,8 @@
         <v>9.19</v>
       </c>
       <c r="G121" s="5">
-        <f t="shared" si="1"/>
-        <v>14.704000000000001</v>
+        <f t="shared" si="2"/>
+        <v>11.487499999999999</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>9</v>
@@ -7610,8 +7942,8 @@
         <v>14.99</v>
       </c>
       <c r="G122" s="5">
-        <f t="shared" si="1"/>
-        <v>23.984000000000002</v>
+        <f t="shared" si="2"/>
+        <v>18.737500000000001</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>9</v>
@@ -7637,8 +7969,8 @@
         <v>6.99</v>
       </c>
       <c r="G123" s="5">
-        <f t="shared" si="1"/>
-        <v>11.184000000000001</v>
+        <f t="shared" si="2"/>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>9</v>
@@ -7664,8 +7996,8 @@
         <v>25.65</v>
       </c>
       <c r="G124" s="5">
-        <f t="shared" si="1"/>
-        <v>41.04</v>
+        <f t="shared" si="2"/>
+        <v>32.0625</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>9</v>
@@ -7691,8 +8023,8 @@
         <v>6.59</v>
       </c>
       <c r="G125" s="5">
-        <f t="shared" si="1"/>
-        <v>10.544</v>
+        <f t="shared" si="2"/>
+        <v>8.2375000000000007</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>9</v>
@@ -7718,8 +8050,8 @@
         <v>9.99</v>
       </c>
       <c r="G126" s="5">
-        <f t="shared" si="1"/>
-        <v>15.984000000000002</v>
+        <f t="shared" si="2"/>
+        <v>12.487500000000001</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>9</v>
@@ -7745,8 +8077,8 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G127" s="5">
-        <f t="shared" si="1"/>
-        <v>31.983999999999998</v>
+        <f t="shared" si="2"/>
+        <v>24.987499999999997</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>9</v>
@@ -7772,8 +8104,8 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="G128" s="5">
-        <f t="shared" si="1"/>
-        <v>13.263999999999999</v>
+        <f t="shared" si="2"/>
+        <v>10.362499999999999</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>9</v>
@@ -7799,8 +8131,8 @@
         <v>14.99</v>
       </c>
       <c r="G129" s="5">
-        <f t="shared" si="1"/>
-        <v>23.984000000000002</v>
+        <f t="shared" si="2"/>
+        <v>18.737500000000001</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>9</v>
@@ -7826,8 +8158,8 @@
         <v>19.190000000000001</v>
       </c>
       <c r="G130" s="5">
-        <f t="shared" si="1"/>
-        <v>30.704000000000004</v>
+        <f t="shared" si="2"/>
+        <v>23.987500000000001</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>9</v>
@@ -7853,8 +8185,8 @@
         <v>13.29</v>
       </c>
       <c r="G131" s="5">
-        <f t="shared" si="1"/>
-        <v>21.263999999999999</v>
+        <f t="shared" si="2"/>
+        <v>16.612499999999997</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>9</v>
@@ -7880,8 +8212,8 @@
         <v>12.49</v>
       </c>
       <c r="G132" s="5">
-        <f t="shared" ref="G132:G195" si="2">F132*1.6</f>
-        <v>19.984000000000002</v>
+        <f t="shared" si="2"/>
+        <v>15.612500000000001</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>9</v>
@@ -7908,7 +8240,7 @@
       </c>
       <c r="G133" s="5">
         <f t="shared" si="2"/>
-        <v>16.784000000000002</v>
+        <v>13.112500000000001</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>9</v>
@@ -7935,7 +8267,7 @@
       </c>
       <c r="G134" s="5">
         <f t="shared" si="2"/>
-        <v>18.704000000000001</v>
+        <v>14.612499999999999</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>9</v>
@@ -7962,7 +8294,7 @@
       </c>
       <c r="G135" s="5">
         <f t="shared" si="2"/>
-        <v>16.144000000000002</v>
+        <v>12.612500000000001</v>
       </c>
       <c r="H135" s="10" t="s">
         <v>9</v>
@@ -7989,7 +8321,7 @@
       </c>
       <c r="G136" s="5">
         <f t="shared" si="2"/>
-        <v>18.384</v>
+        <v>14.362500000000001</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>9</v>
@@ -8016,7 +8348,7 @@
       </c>
       <c r="G137" s="5">
         <f t="shared" si="2"/>
-        <v>28.463999999999999</v>
+        <v>22.237499999999997</v>
       </c>
       <c r="H137" s="10" t="s">
         <v>9</v>
@@ -8043,7 +8375,7 @@
       </c>
       <c r="G138" s="5">
         <f t="shared" si="2"/>
-        <v>4.944</v>
+        <v>3.8624999999999998</v>
       </c>
       <c r="H138" s="6" t="s">
         <v>9</v>
@@ -8070,7 +8402,7 @@
       </c>
       <c r="G139" s="5">
         <f t="shared" si="2"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>9</v>
@@ -8097,7 +8429,7 @@
       </c>
       <c r="G140" s="5">
         <f t="shared" si="2"/>
-        <v>15.664</v>
+        <v>12.237499999999999</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>9</v>
@@ -8124,7 +8456,7 @@
       </c>
       <c r="G141" s="5">
         <f t="shared" si="2"/>
-        <v>7.1840000000000011</v>
+        <v>5.6125000000000007</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>9</v>
@@ -8151,7 +8483,7 @@
       </c>
       <c r="G142" s="5">
         <f t="shared" si="2"/>
-        <v>17.424000000000003</v>
+        <v>13.612500000000001</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>9</v>
@@ -8178,7 +8510,7 @@
       </c>
       <c r="G143" s="5">
         <f t="shared" si="2"/>
-        <v>38.064</v>
+        <v>29.737499999999997</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>9</v>
@@ -8205,7 +8537,7 @@
       </c>
       <c r="G144" s="5">
         <f t="shared" si="2"/>
-        <v>60.784000000000006</v>
+        <v>47.487500000000004</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>9</v>
@@ -8232,7 +8564,7 @@
       </c>
       <c r="G145" s="5">
         <f t="shared" si="2"/>
-        <v>25.584000000000003</v>
+        <v>19.987500000000001</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>9</v>
@@ -8259,7 +8591,7 @@
       </c>
       <c r="G146" s="5">
         <f t="shared" si="2"/>
-        <v>12.4</v>
+        <v>9.6875</v>
       </c>
       <c r="H146" s="6" t="s">
         <v>9</v>
@@ -8286,7 +8618,7 @@
       </c>
       <c r="G147" s="5">
         <f t="shared" si="2"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>9</v>
@@ -8313,7 +8645,7 @@
       </c>
       <c r="G148" s="5">
         <f t="shared" si="2"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>9</v>
@@ -8340,7 +8672,7 @@
       </c>
       <c r="G149" s="5">
         <f t="shared" si="2"/>
-        <v>39.504000000000005</v>
+        <v>30.862500000000001</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>9</v>
@@ -8367,7 +8699,7 @@
       </c>
       <c r="G150" s="5">
         <f t="shared" si="2"/>
-        <v>10.704000000000001</v>
+        <v>8.3625000000000007</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>9</v>
@@ -8394,7 +8726,7 @@
       </c>
       <c r="G151" s="5">
         <f t="shared" si="2"/>
-        <v>16.303999999999998</v>
+        <v>12.737499999999999</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>9</v>
@@ -8421,7 +8753,7 @@
       </c>
       <c r="G152" s="5">
         <f t="shared" si="2"/>
-        <v>41.04</v>
+        <v>32.0625</v>
       </c>
       <c r="H152" s="6" t="s">
         <v>9</v>
@@ -8448,7 +8780,7 @@
       </c>
       <c r="G153" s="5">
         <f t="shared" si="2"/>
-        <v>24.144000000000002</v>
+        <v>18.862500000000001</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>9</v>
@@ -8475,7 +8807,7 @@
       </c>
       <c r="G154" s="5">
         <f t="shared" si="2"/>
-        <v>13.200000000000001</v>
+        <v>10.3125</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>9</v>
@@ -8502,7 +8834,7 @@
       </c>
       <c r="G155" s="5">
         <f t="shared" si="2"/>
-        <v>45.584000000000003</v>
+        <v>35.612499999999997</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>9</v>
@@ -8529,7 +8861,7 @@
       </c>
       <c r="G156" s="5">
         <f t="shared" si="2"/>
-        <v>23.984000000000002</v>
+        <v>18.737500000000001</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>9</v>
@@ -8556,7 +8888,7 @@
       </c>
       <c r="G157" s="5">
         <f t="shared" si="2"/>
-        <v>23.984000000000002</v>
+        <v>18.737500000000001</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>9</v>
@@ -8583,7 +8915,7 @@
       </c>
       <c r="G158" s="5">
         <f t="shared" si="2"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>9</v>
@@ -8610,7 +8942,7 @@
       </c>
       <c r="G159" s="5">
         <f t="shared" si="2"/>
-        <v>10.384</v>
+        <v>8.1125000000000007</v>
       </c>
       <c r="H159" s="10" t="s">
         <v>9</v>
@@ -8637,7 +8969,7 @@
       </c>
       <c r="G160" s="5">
         <f t="shared" si="2"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>9</v>
@@ -8664,7 +8996,7 @@
       </c>
       <c r="G161" s="5">
         <f t="shared" si="2"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H161" s="10" t="s">
         <v>9</v>
@@ -8691,7 +9023,7 @@
       </c>
       <c r="G162" s="5">
         <f t="shared" si="2"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>9</v>
@@ -8718,7 +9050,7 @@
       </c>
       <c r="G163" s="5">
         <f t="shared" si="2"/>
-        <v>11.184000000000001</v>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H163" s="10" t="s">
         <v>9</v>
@@ -8745,7 +9077,7 @@
       </c>
       <c r="G164" s="5">
         <f t="shared" si="2"/>
-        <v>9.2640000000000011</v>
+        <v>7.2374999999999998</v>
       </c>
       <c r="H164" s="6" t="s">
         <v>9</v>
@@ -8772,7 +9104,7 @@
       </c>
       <c r="G165" s="5">
         <f t="shared" si="2"/>
-        <v>11.984000000000002</v>
+        <v>9.3625000000000007</v>
       </c>
       <c r="H165" s="10" t="s">
         <v>9</v>
@@ -8799,7 +9131,7 @@
       </c>
       <c r="G166" s="5">
         <f t="shared" si="2"/>
-        <v>15.984000000000002</v>
+        <v>12.487500000000001</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>9</v>
@@ -8852,7 +9184,7 @@
       </c>
       <c r="G168" s="5">
         <f t="shared" si="2"/>
-        <v>32.783999999999999</v>
+        <v>25.612499999999997</v>
       </c>
       <c r="H168" s="10" t="s">
         <v>9</v>
@@ -8879,7 +9211,7 @@
       </c>
       <c r="G169" s="5">
         <f t="shared" si="2"/>
-        <v>29.584</v>
+        <v>23.112499999999997</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>9</v>
@@ -8906,7 +9238,7 @@
       </c>
       <c r="G170" s="5">
         <f t="shared" si="2"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H170" s="10" t="s">
         <v>9</v>
@@ -8933,7 +9265,7 @@
       </c>
       <c r="G171" s="5">
         <f t="shared" si="2"/>
-        <v>29.584</v>
+        <v>23.112499999999997</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>9</v>
@@ -8960,7 +9292,7 @@
       </c>
       <c r="G172" s="5">
         <f t="shared" si="2"/>
-        <v>31.983999999999998</v>
+        <v>24.987499999999997</v>
       </c>
       <c r="H172" s="10" t="s">
         <v>9</v>
@@ -8987,7 +9319,7 @@
       </c>
       <c r="G173" s="5">
         <f t="shared" si="2"/>
-        <v>17.584</v>
+        <v>13.737500000000001</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>9</v>
@@ -9014,7 +9346,7 @@
       </c>
       <c r="G174" s="5">
         <f t="shared" si="2"/>
-        <v>28.304000000000002</v>
+        <v>22.112500000000001</v>
       </c>
       <c r="H174" s="10" t="s">
         <v>9</v>
@@ -9041,7 +9373,7 @@
       </c>
       <c r="G175" s="5">
         <f t="shared" si="2"/>
-        <v>31.983999999999998</v>
+        <v>24.987499999999997</v>
       </c>
       <c r="H175" s="6" t="s">
         <v>9</v>
@@ -9068,7 +9400,7 @@
       </c>
       <c r="G176" s="5">
         <f t="shared" si="2"/>
-        <v>15.184000000000001</v>
+        <v>11.862500000000001</v>
       </c>
       <c r="H176" s="10" t="s">
         <v>9</v>
@@ -9095,7 +9427,7 @@
       </c>
       <c r="G177" s="5">
         <f t="shared" si="2"/>
-        <v>10.864000000000001</v>
+        <v>8.4875000000000007</v>
       </c>
       <c r="H177" s="6" t="s">
         <v>9</v>
@@ -9122,7 +9454,7 @@
       </c>
       <c r="G178" s="5">
         <f t="shared" si="2"/>
-        <v>10.864000000000001</v>
+        <v>8.4875000000000007</v>
       </c>
       <c r="H178" s="10" t="s">
         <v>9</v>
@@ -9148,8 +9480,8 @@
         <v>6.79</v>
       </c>
       <c r="G179" s="5">
-        <f t="shared" si="2"/>
-        <v>10.864000000000001</v>
+        <f t="shared" ref="G179:G242" si="3">F179*1.25</f>
+        <v>8.4875000000000007</v>
       </c>
       <c r="H179" s="6" t="s">
         <v>9</v>
@@ -9175,8 +9507,8 @@
         <v>9.49</v>
       </c>
       <c r="G180" s="5">
-        <f t="shared" si="2"/>
-        <v>15.184000000000001</v>
+        <f t="shared" si="3"/>
+        <v>11.862500000000001</v>
       </c>
       <c r="H180" s="10" t="s">
         <v>9</v>
@@ -9202,8 +9534,8 @@
         <v>11.89</v>
       </c>
       <c r="G181" s="5">
-        <f t="shared" si="2"/>
-        <v>19.024000000000001</v>
+        <f t="shared" si="3"/>
+        <v>14.862500000000001</v>
       </c>
       <c r="H181" s="6" t="s">
         <v>9</v>
@@ -9229,8 +9561,8 @@
         <v>14.59</v>
       </c>
       <c r="G182" s="5">
-        <f t="shared" si="2"/>
-        <v>23.344000000000001</v>
+        <f t="shared" si="3"/>
+        <v>18.237500000000001</v>
       </c>
       <c r="H182" s="10" t="s">
         <v>9</v>
@@ -9256,8 +9588,8 @@
         <v>14.19</v>
       </c>
       <c r="G183" s="5">
-        <f t="shared" si="2"/>
-        <v>22.704000000000001</v>
+        <f t="shared" si="3"/>
+        <v>17.737500000000001</v>
       </c>
       <c r="H183" s="6" t="s">
         <v>9</v>
@@ -9283,8 +9615,8 @@
         <v>6.59</v>
       </c>
       <c r="G184" s="5">
-        <f t="shared" si="2"/>
-        <v>10.544</v>
+        <f t="shared" si="3"/>
+        <v>8.2375000000000007</v>
       </c>
       <c r="H184" s="10" t="s">
         <v>9</v>
@@ -9310,8 +9642,8 @@
         <v>6.59</v>
       </c>
       <c r="G185" s="5">
-        <f t="shared" si="2"/>
-        <v>10.544</v>
+        <f t="shared" si="3"/>
+        <v>8.2375000000000007</v>
       </c>
       <c r="H185" s="6" t="s">
         <v>9</v>
@@ -9337,8 +9669,8 @@
         <v>14.79</v>
       </c>
       <c r="G186" s="5">
-        <f t="shared" si="2"/>
-        <v>23.664000000000001</v>
+        <f t="shared" si="3"/>
+        <v>18.487499999999997</v>
       </c>
       <c r="H186" s="10" t="s">
         <v>9</v>
@@ -9364,8 +9696,8 @@
         <v>61.79</v>
       </c>
       <c r="G187" s="5">
-        <f t="shared" si="2"/>
-        <v>98.864000000000004</v>
+        <f t="shared" si="3"/>
+        <v>77.237499999999997</v>
       </c>
       <c r="H187" s="6" t="s">
         <v>9</v>
@@ -9391,8 +9723,8 @@
         <v>49.99</v>
       </c>
       <c r="G188" s="5">
-        <f t="shared" si="2"/>
-        <v>79.984000000000009</v>
+        <f t="shared" si="3"/>
+        <v>62.487500000000004</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>9</v>
@@ -9418,8 +9750,8 @@
         <v>14.79</v>
       </c>
       <c r="G189" s="5">
-        <f t="shared" si="2"/>
-        <v>23.664000000000001</v>
+        <f t="shared" si="3"/>
+        <v>18.487499999999997</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>9</v>
@@ -9471,8 +9803,8 @@
         <v>11.79</v>
       </c>
       <c r="G191" s="5">
-        <f t="shared" si="2"/>
-        <v>18.864000000000001</v>
+        <f t="shared" si="3"/>
+        <v>14.737499999999999</v>
       </c>
       <c r="H191" s="10" t="s">
         <v>9</v>
@@ -9498,8 +9830,8 @@
         <v>34.49</v>
       </c>
       <c r="G192" s="5">
-        <f t="shared" si="2"/>
-        <v>55.184000000000005</v>
+        <f t="shared" si="3"/>
+        <v>43.112500000000004</v>
       </c>
       <c r="H192" s="6" t="s">
         <v>9</v>
@@ -9525,8 +9857,8 @@
         <v>34.49</v>
       </c>
       <c r="G193" s="5">
-        <f t="shared" si="2"/>
-        <v>55.184000000000005</v>
+        <f t="shared" si="3"/>
+        <v>43.112500000000004</v>
       </c>
       <c r="H193" s="10" t="s">
         <v>9</v>
@@ -9552,8 +9884,8 @@
         <v>34.49</v>
       </c>
       <c r="G194" s="5">
-        <f t="shared" si="2"/>
-        <v>55.184000000000005</v>
+        <f t="shared" si="3"/>
+        <v>43.112500000000004</v>
       </c>
       <c r="H194" s="6" t="s">
         <v>9</v>
@@ -9579,8 +9911,8 @@
         <v>34.49</v>
       </c>
       <c r="G195" s="5">
-        <f t="shared" si="2"/>
-        <v>55.184000000000005</v>
+        <f t="shared" si="3"/>
+        <v>43.112500000000004</v>
       </c>
       <c r="H195" s="10" t="s">
         <v>9</v>
@@ -9606,8 +9938,8 @@
         <v>34.49</v>
       </c>
       <c r="G196" s="5">
-        <f t="shared" ref="G196:G259" si="3">F196*1.6</f>
-        <v>55.184000000000005</v>
+        <f t="shared" si="3"/>
+        <v>43.112500000000004</v>
       </c>
       <c r="H196" s="6" t="s">
         <v>9</v>
@@ -9634,7 +9966,7 @@
       </c>
       <c r="G197" s="5">
         <f t="shared" si="3"/>
-        <v>55.184000000000005</v>
+        <v>43.112500000000004</v>
       </c>
       <c r="H197" s="10" t="s">
         <v>9</v>
@@ -9687,7 +10019,7 @@
       </c>
       <c r="G199" s="5">
         <f t="shared" si="3"/>
-        <v>37.904000000000003</v>
+        <v>29.612500000000001</v>
       </c>
       <c r="H199" s="6" t="s">
         <v>9</v>
@@ -9714,7 +10046,7 @@
       </c>
       <c r="G200" s="5">
         <f t="shared" si="3"/>
-        <v>29.904000000000003</v>
+        <v>23.362500000000001</v>
       </c>
       <c r="H200" s="10" t="s">
         <v>9</v>
@@ -9741,7 +10073,7 @@
       </c>
       <c r="G201" s="5">
         <f t="shared" si="3"/>
-        <v>29.904000000000003</v>
+        <v>23.362500000000001</v>
       </c>
       <c r="H201" s="6" t="s">
         <v>9</v>
@@ -9768,7 +10100,7 @@
       </c>
       <c r="G202" s="5">
         <f t="shared" si="3"/>
-        <v>1.2000000000000002</v>
+        <v>0.9375</v>
       </c>
       <c r="H202" s="10" t="s">
         <v>9</v>
@@ -9795,7 +10127,7 @@
       </c>
       <c r="G203" s="5">
         <f t="shared" si="3"/>
-        <v>37.904000000000003</v>
+        <v>29.612500000000001</v>
       </c>
       <c r="H203" s="6" t="s">
         <v>9</v>
@@ -9822,7 +10154,7 @@
       </c>
       <c r="G204" s="5">
         <f t="shared" si="3"/>
-        <v>1.2000000000000002</v>
+        <v>0.9375</v>
       </c>
       <c r="H204" s="10" t="s">
         <v>9</v>
@@ -9849,7 +10181,7 @@
       </c>
       <c r="G205" s="5">
         <f t="shared" si="3"/>
-        <v>39.984000000000002</v>
+        <v>31.237499999999997</v>
       </c>
       <c r="H205" s="6" t="s">
         <v>9</v>
@@ -9876,7 +10208,7 @@
       </c>
       <c r="G206" s="5">
         <f t="shared" si="3"/>
-        <v>35.183999999999997</v>
+        <v>27.487499999999997</v>
       </c>
       <c r="H206" s="10" t="s">
         <v>9</v>
@@ -9903,7 +10235,7 @@
       </c>
       <c r="G207" s="5">
         <f t="shared" si="3"/>
-        <v>29.584</v>
+        <v>23.112499999999997</v>
       </c>
       <c r="H207" s="6" t="s">
         <v>9</v>
@@ -9930,7 +10262,7 @@
       </c>
       <c r="G208" s="5">
         <f t="shared" si="3"/>
-        <v>19.984000000000002</v>
+        <v>15.612500000000001</v>
       </c>
       <c r="H208" s="10" t="s">
         <v>9</v>
@@ -9957,7 +10289,7 @@
       </c>
       <c r="G209" s="5">
         <f t="shared" si="3"/>
-        <v>7.1840000000000011</v>
+        <v>5.6125000000000007</v>
       </c>
       <c r="H209" s="6" t="s">
         <v>9</v>
@@ -10010,7 +10342,7 @@
       </c>
       <c r="G211" s="5">
         <f t="shared" si="3"/>
-        <v>41.584000000000003</v>
+        <v>32.487499999999997</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>9</v>
@@ -10037,7 +10369,7 @@
       </c>
       <c r="G212" s="5">
         <f t="shared" si="3"/>
-        <v>49.584000000000003</v>
+        <v>38.737499999999997</v>
       </c>
       <c r="H212" s="6" t="s">
         <v>9</v>
@@ -10064,7 +10396,7 @@
       </c>
       <c r="G213" s="5">
         <f t="shared" si="3"/>
-        <v>20.784000000000002</v>
+        <v>16.237500000000001</v>
       </c>
       <c r="H213" s="10" t="s">
         <v>9</v>
@@ -10091,7 +10423,7 @@
       </c>
       <c r="G214" s="5">
         <f t="shared" si="3"/>
-        <v>28.783999999999999</v>
+        <v>22.487499999999997</v>
       </c>
       <c r="H214" s="6" t="s">
         <v>9</v>
@@ -10118,7 +10450,7 @@
       </c>
       <c r="G215" s="5">
         <f t="shared" si="3"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H215" s="10" t="s">
         <v>9</v>
@@ -10145,7 +10477,7 @@
       </c>
       <c r="G216" s="5">
         <f t="shared" si="3"/>
-        <v>7.1840000000000011</v>
+        <v>5.6125000000000007</v>
       </c>
       <c r="H216" s="6" t="s">
         <v>9</v>
@@ -10172,7 +10504,7 @@
       </c>
       <c r="G217" s="5">
         <f t="shared" si="3"/>
-        <v>8.7840000000000007</v>
+        <v>6.8625000000000007</v>
       </c>
       <c r="H217" s="10" t="s">
         <v>9</v>
@@ -10199,7 +10531,7 @@
       </c>
       <c r="G218" s="5">
         <f t="shared" si="3"/>
-        <v>6.2240000000000002</v>
+        <v>4.8624999999999998</v>
       </c>
       <c r="H218" s="6" t="s">
         <v>9</v>
@@ -10226,7 +10558,7 @@
       </c>
       <c r="G219" s="5">
         <f t="shared" si="3"/>
-        <v>6.0640000000000001</v>
+        <v>4.7374999999999998</v>
       </c>
       <c r="H219" s="10" t="s">
         <v>9</v>
@@ -10253,7 +10585,7 @@
       </c>
       <c r="G220" s="5">
         <f t="shared" si="3"/>
-        <v>9.5840000000000014</v>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H220" s="6" t="s">
         <v>9</v>
@@ -10280,7 +10612,7 @@
       </c>
       <c r="G221" s="5">
         <f t="shared" si="3"/>
-        <v>13.904</v>
+        <v>10.862499999999999</v>
       </c>
       <c r="H221" s="10" t="s">
         <v>9</v>
@@ -10307,7 +10639,7 @@
       </c>
       <c r="G222" s="5">
         <f t="shared" si="3"/>
-        <v>13.728000000000002</v>
+        <v>10.725</v>
       </c>
       <c r="H222" s="6" t="s">
         <v>9</v>
@@ -10334,7 +10666,7 @@
       </c>
       <c r="G223" s="5">
         <f t="shared" si="3"/>
-        <v>31.983999999999998</v>
+        <v>24.987499999999997</v>
       </c>
       <c r="H223" s="10" t="s">
         <v>9</v>
@@ -10355,7 +10687,7 @@
       </c>
       <c r="G224" s="5">
         <f t="shared" si="3"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H224" s="10"/>
     </row>
@@ -10374,7 +10706,7 @@
       </c>
       <c r="G225" s="5">
         <f t="shared" si="3"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H225" s="10"/>
     </row>
@@ -10393,7 +10725,7 @@
       </c>
       <c r="G226" s="5">
         <f t="shared" si="3"/>
-        <v>5.7439999999999998</v>
+        <v>4.4874999999999998</v>
       </c>
       <c r="H226" s="10"/>
     </row>
@@ -10457,7 +10789,7 @@
       </c>
       <c r="G229" s="5">
         <f t="shared" si="3"/>
-        <v>16.463999999999999</v>
+        <v>12.862499999999999</v>
       </c>
       <c r="H229" s="6" t="s">
         <v>9</v>
@@ -10484,7 +10816,7 @@
       </c>
       <c r="G230" s="5">
         <f t="shared" si="3"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H230" s="10" t="s">
         <v>9</v>
@@ -10511,7 +10843,7 @@
       </c>
       <c r="G231" s="5">
         <f t="shared" si="3"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H231" s="6" t="s">
         <v>9</v>
@@ -10538,7 +10870,7 @@
       </c>
       <c r="G232" s="5">
         <f t="shared" si="3"/>
-        <v>16.463999999999999</v>
+        <v>12.862499999999999</v>
       </c>
       <c r="H232" s="10" t="s">
         <v>9</v>
@@ -10565,7 +10897,7 @@
       </c>
       <c r="G233" s="5">
         <f t="shared" si="3"/>
-        <v>38.384</v>
+        <v>29.987499999999997</v>
       </c>
       <c r="H233" s="6" t="s">
         <v>9</v>
@@ -10592,7 +10924,7 @@
       </c>
       <c r="G234" s="5">
         <f t="shared" si="3"/>
-        <v>15.184000000000001</v>
+        <v>11.862500000000001</v>
       </c>
       <c r="H234" s="10" t="s">
         <v>9</v>
@@ -10619,7 +10951,7 @@
       </c>
       <c r="G235" s="5">
         <f t="shared" si="3"/>
-        <v>15.184000000000001</v>
+        <v>11.862500000000001</v>
       </c>
       <c r="H235" s="6" t="s">
         <v>9</v>
@@ -10646,7 +10978,7 @@
       </c>
       <c r="G236" s="5">
         <f t="shared" si="3"/>
-        <v>10.384</v>
+        <v>8.1125000000000007</v>
       </c>
       <c r="H236" s="10" t="s">
         <v>9</v>
@@ -10673,7 +11005,7 @@
       </c>
       <c r="G237" s="5">
         <f t="shared" si="3"/>
-        <v>15.984000000000002</v>
+        <v>12.487500000000001</v>
       </c>
       <c r="H237" s="6" t="s">
         <v>9</v>
@@ -10700,7 +11032,7 @@
       </c>
       <c r="G238" s="5">
         <f t="shared" si="3"/>
-        <v>14.064</v>
+        <v>10.987499999999999</v>
       </c>
       <c r="H238" s="10" t="s">
         <v>9</v>
@@ -10753,7 +11085,7 @@
       </c>
       <c r="G240" s="5">
         <f t="shared" si="3"/>
-        <v>15.280000000000001</v>
+        <v>11.9375</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>9</v>
@@ -10780,7 +11112,7 @@
       </c>
       <c r="G241" s="5">
         <f t="shared" si="3"/>
-        <v>14.704000000000001</v>
+        <v>11.487499999999999</v>
       </c>
       <c r="H241" s="10" t="s">
         <v>9</v>
@@ -10807,7 +11139,7 @@
       </c>
       <c r="G242" s="5">
         <f t="shared" si="3"/>
-        <v>21.424000000000003</v>
+        <v>16.737500000000001</v>
       </c>
       <c r="H242" s="6" t="s">
         <v>9</v>
@@ -10833,8 +11165,8 @@
         <v>20.99</v>
       </c>
       <c r="G243" s="5">
-        <f t="shared" si="3"/>
-        <v>33.583999999999996</v>
+        <f t="shared" ref="G243:G306" si="4">F243*1.25</f>
+        <v>26.237499999999997</v>
       </c>
       <c r="H243" s="10" t="s">
         <v>9</v>
@@ -10860,8 +11192,8 @@
         <v>4.49</v>
       </c>
       <c r="G244" s="5">
-        <f t="shared" si="3"/>
-        <v>7.1840000000000011</v>
+        <f t="shared" si="4"/>
+        <v>5.6125000000000007</v>
       </c>
       <c r="H244" s="6" t="s">
         <v>9</v>
@@ -10887,8 +11219,8 @@
         <v>21.99</v>
       </c>
       <c r="G245" s="5">
-        <f t="shared" si="3"/>
-        <v>35.183999999999997</v>
+        <f t="shared" si="4"/>
+        <v>27.487499999999997</v>
       </c>
       <c r="H245" s="10" t="s">
         <v>9</v>
@@ -10914,8 +11246,8 @@
         <v>23.49</v>
       </c>
       <c r="G246" s="5">
-        <f t="shared" si="3"/>
-        <v>37.583999999999996</v>
+        <f t="shared" si="4"/>
+        <v>29.362499999999997</v>
       </c>
       <c r="H246" s="6" t="s">
         <v>9</v>
@@ -10941,8 +11273,8 @@
         <v>22.99</v>
       </c>
       <c r="G247" s="5">
-        <f t="shared" si="3"/>
-        <v>36.783999999999999</v>
+        <f t="shared" si="4"/>
+        <v>28.737499999999997</v>
       </c>
       <c r="H247" s="10" t="s">
         <v>9</v>
@@ -10968,8 +11300,8 @@
         <v>25.49</v>
       </c>
       <c r="G248" s="5">
-        <f t="shared" si="3"/>
-        <v>40.783999999999999</v>
+        <f t="shared" si="4"/>
+        <v>31.862499999999997</v>
       </c>
       <c r="H248" s="6" t="s">
         <v>9</v>
@@ -10995,8 +11327,8 @@
         <v>9.49</v>
       </c>
       <c r="G249" s="5">
-        <f t="shared" si="3"/>
-        <v>15.184000000000001</v>
+        <f t="shared" si="4"/>
+        <v>11.862500000000001</v>
       </c>
       <c r="H249" s="10" t="s">
         <v>9</v>
@@ -11048,8 +11380,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G251" s="5">
-        <f t="shared" si="3"/>
-        <v>27.183999999999997</v>
+        <f t="shared" si="4"/>
+        <v>21.237499999999997</v>
       </c>
       <c r="H251" s="6" t="s">
         <v>9</v>
@@ -11075,8 +11407,8 @@
         <v>19.350000000000001</v>
       </c>
       <c r="G252" s="5">
-        <f t="shared" si="3"/>
-        <v>30.960000000000004</v>
+        <f t="shared" si="4"/>
+        <v>24.1875</v>
       </c>
       <c r="H252" s="10" t="s">
         <v>9</v>
@@ -11102,8 +11434,8 @@
         <v>16.55</v>
       </c>
       <c r="G253" s="5">
-        <f t="shared" si="3"/>
-        <v>26.480000000000004</v>
+        <f t="shared" si="4"/>
+        <v>20.6875</v>
       </c>
       <c r="H253" s="6" t="s">
         <v>9</v>
@@ -11129,8 +11461,8 @@
         <v>13.89</v>
       </c>
       <c r="G254" s="5">
-        <f t="shared" si="3"/>
-        <v>22.224000000000004</v>
+        <f t="shared" si="4"/>
+        <v>17.362500000000001</v>
       </c>
       <c r="H254" s="10" t="s">
         <v>9</v>
@@ -11156,8 +11488,8 @@
         <v>22.09</v>
       </c>
       <c r="G255" s="5">
-        <f t="shared" si="3"/>
-        <v>35.344000000000001</v>
+        <f t="shared" si="4"/>
+        <v>27.612500000000001</v>
       </c>
       <c r="H255" s="6" t="s">
         <v>9</v>
@@ -11183,8 +11515,8 @@
         <v>7.59</v>
       </c>
       <c r="G256" s="5">
-        <f t="shared" si="3"/>
-        <v>12.144</v>
+        <f t="shared" si="4"/>
+        <v>9.4875000000000007</v>
       </c>
       <c r="H256" s="10" t="s">
         <v>9</v>
@@ -11210,8 +11542,8 @@
         <v>15.69</v>
       </c>
       <c r="G257" s="5">
-        <f t="shared" si="3"/>
-        <v>25.103999999999999</v>
+        <f t="shared" si="4"/>
+        <v>19.612500000000001</v>
       </c>
       <c r="H257" s="6" t="s">
         <v>9</v>
@@ -11237,8 +11569,8 @@
         <v>16.59</v>
       </c>
       <c r="G258" s="5">
-        <f t="shared" si="3"/>
-        <v>26.544</v>
+        <f t="shared" si="4"/>
+        <v>20.737500000000001</v>
       </c>
       <c r="H258" s="10" t="s">
         <v>9</v>
@@ -11264,8 +11596,8 @@
         <v>27.75</v>
       </c>
       <c r="G259" s="5">
-        <f t="shared" si="3"/>
-        <v>44.400000000000006</v>
+        <f t="shared" si="4"/>
+        <v>34.6875</v>
       </c>
       <c r="H259" s="6" t="s">
         <v>9</v>
@@ -11291,8 +11623,8 @@
         <v>3.49</v>
       </c>
       <c r="G260" s="5">
-        <f t="shared" ref="G260:G323" si="4">F260*1.6</f>
-        <v>5.5840000000000005</v>
+        <f t="shared" si="4"/>
+        <v>4.3625000000000007</v>
       </c>
       <c r="H260" s="10" t="s">
         <v>9</v>
@@ -11345,7 +11677,7 @@
       </c>
       <c r="G262" s="5">
         <f t="shared" si="4"/>
-        <v>46.336000000000006</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="H262" s="6" t="s">
         <v>9</v>
@@ -11372,7 +11704,7 @@
       </c>
       <c r="G263" s="5">
         <f t="shared" si="4"/>
-        <v>74.864000000000004</v>
+        <v>58.487499999999997</v>
       </c>
       <c r="H263" s="10" t="s">
         <v>9</v>
@@ -11399,7 +11731,7 @@
       </c>
       <c r="G264" s="5">
         <f t="shared" si="4"/>
-        <v>38.544000000000004</v>
+        <v>30.112500000000001</v>
       </c>
       <c r="H264" s="6" t="s">
         <v>9</v>
@@ -11426,7 +11758,7 @@
       </c>
       <c r="G265" s="5">
         <f t="shared" si="4"/>
-        <v>46.384</v>
+        <v>36.237499999999997</v>
       </c>
       <c r="H265" s="10" t="s">
         <v>9</v>
@@ -11453,7 +11785,7 @@
       </c>
       <c r="G266" s="5">
         <f t="shared" si="4"/>
-        <v>8.7840000000000007</v>
+        <v>6.8625000000000007</v>
       </c>
       <c r="H266" s="6" t="s">
         <v>9</v>
@@ -11480,7 +11812,7 @@
       </c>
       <c r="G267" s="5">
         <f t="shared" si="4"/>
-        <v>21.584000000000003</v>
+        <v>16.862500000000001</v>
       </c>
       <c r="H267" s="10" t="s">
         <v>9</v>
@@ -11507,7 +11839,7 @@
       </c>
       <c r="G268" s="5">
         <f t="shared" si="4"/>
-        <v>26.384</v>
+        <v>20.612499999999997</v>
       </c>
       <c r="H268" s="6" t="s">
         <v>9</v>
@@ -11534,7 +11866,7 @@
       </c>
       <c r="G269" s="5">
         <f t="shared" si="4"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>9</v>
@@ -11561,7 +11893,7 @@
       </c>
       <c r="G270" s="5">
         <f t="shared" si="4"/>
-        <v>39.183999999999997</v>
+        <v>30.612499999999997</v>
       </c>
       <c r="H270" s="6" t="s">
         <v>9</v>
@@ -11614,7 +11946,7 @@
       </c>
       <c r="G272" s="5">
         <f t="shared" si="4"/>
-        <v>43.183999999999997</v>
+        <v>33.737499999999997</v>
       </c>
       <c r="H272" s="10" t="s">
         <v>9</v>
@@ -11641,7 +11973,7 @@
       </c>
       <c r="G273" s="5">
         <f t="shared" si="4"/>
-        <v>30.064</v>
+        <v>23.487499999999997</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>9</v>
@@ -11668,7 +12000,7 @@
       </c>
       <c r="G274" s="5">
         <f t="shared" si="4"/>
-        <v>31.183999999999997</v>
+        <v>24.362499999999997</v>
       </c>
       <c r="H274" s="10" t="s">
         <v>9</v>
@@ -11695,7 +12027,7 @@
       </c>
       <c r="G275" s="5">
         <f t="shared" si="4"/>
-        <v>50.864000000000004</v>
+        <v>39.737499999999997</v>
       </c>
       <c r="H275" s="6" t="s">
         <v>9</v>
@@ -11722,7 +12054,7 @@
       </c>
       <c r="G276" s="5">
         <f t="shared" si="4"/>
-        <v>51.984000000000009</v>
+        <v>40.612500000000004</v>
       </c>
       <c r="H276" s="10" t="s">
         <v>9</v>
@@ -11749,7 +12081,7 @@
       </c>
       <c r="G277" s="5">
         <f t="shared" si="4"/>
-        <v>11.184000000000001</v>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>9</v>
@@ -11802,7 +12134,7 @@
       </c>
       <c r="G279" s="5">
         <f t="shared" si="4"/>
-        <v>31.824000000000002</v>
+        <v>24.862500000000001</v>
       </c>
       <c r="H279" s="10" t="s">
         <v>9</v>
@@ -11829,7 +12161,7 @@
       </c>
       <c r="G280" s="5">
         <f t="shared" si="4"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H280" s="6" t="s">
         <v>9</v>
@@ -11856,7 +12188,7 @@
       </c>
       <c r="G281" s="5">
         <f t="shared" si="4"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H281" s="10" t="s">
         <v>9</v>
@@ -11883,7 +12215,7 @@
       </c>
       <c r="G282" s="5">
         <f t="shared" si="4"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H282" s="6" t="s">
         <v>9</v>
@@ -11910,7 +12242,7 @@
       </c>
       <c r="G283" s="5">
         <f t="shared" si="4"/>
-        <v>8.7840000000000007</v>
+        <v>6.8625000000000007</v>
       </c>
       <c r="H283" s="10" t="s">
         <v>9</v>
@@ -11937,7 +12269,7 @@
       </c>
       <c r="G284" s="5">
         <f t="shared" si="4"/>
-        <v>7.9840000000000009</v>
+        <v>6.2375000000000007</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>9</v>
@@ -11964,7 +12296,7 @@
       </c>
       <c r="G285" s="5">
         <f t="shared" si="4"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H285" s="10" t="s">
         <v>9</v>
@@ -11991,7 +12323,7 @@
       </c>
       <c r="G286" s="5">
         <f t="shared" si="4"/>
-        <v>8.7840000000000007</v>
+        <v>6.8625000000000007</v>
       </c>
       <c r="H286" s="6" t="s">
         <v>9</v>
@@ -12018,7 +12350,7 @@
       </c>
       <c r="G287" s="5">
         <f t="shared" si="4"/>
-        <v>20.784000000000002</v>
+        <v>16.237500000000001</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>9</v>
@@ -12045,7 +12377,7 @@
       </c>
       <c r="G288" s="5">
         <f t="shared" si="4"/>
-        <v>19.184000000000001</v>
+        <v>14.987500000000001</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>9</v>
@@ -12072,7 +12404,7 @@
       </c>
       <c r="G289" s="5">
         <f t="shared" si="4"/>
-        <v>7.9840000000000009</v>
+        <v>6.2375000000000007</v>
       </c>
       <c r="H289" s="10" t="s">
         <v>9</v>
@@ -12099,7 +12431,7 @@
       </c>
       <c r="G290" s="5">
         <f t="shared" si="4"/>
-        <v>15.184000000000001</v>
+        <v>11.862500000000001</v>
       </c>
       <c r="H290" s="6" t="s">
         <v>9</v>
@@ -12126,7 +12458,7 @@
       </c>
       <c r="G291" s="5">
         <f t="shared" si="4"/>
-        <v>9.5840000000000014</v>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H291" s="10" t="s">
         <v>9</v>
@@ -12153,7 +12485,7 @@
       </c>
       <c r="G292" s="5">
         <f t="shared" si="4"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H292" s="6" t="s">
         <v>9</v>
@@ -12180,7 +12512,7 @@
       </c>
       <c r="G293" s="5">
         <f t="shared" si="4"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>9</v>
@@ -12207,7 +12539,7 @@
       </c>
       <c r="G294" s="5">
         <f t="shared" si="4"/>
-        <v>7.9840000000000009</v>
+        <v>6.2375000000000007</v>
       </c>
       <c r="H294" s="6" t="s">
         <v>9</v>
@@ -12234,7 +12566,7 @@
       </c>
       <c r="G295" s="5">
         <f t="shared" si="4"/>
-        <v>7.9680000000000009</v>
+        <v>6.2250000000000005</v>
       </c>
       <c r="H295" s="10" t="s">
         <v>9</v>
@@ -12261,7 +12593,7 @@
       </c>
       <c r="G296" s="5">
         <f t="shared" si="4"/>
-        <v>10.704000000000001</v>
+        <v>8.3625000000000007</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>9</v>
@@ -12288,7 +12620,7 @@
       </c>
       <c r="G297" s="5">
         <f t="shared" si="4"/>
-        <v>5.6000000000000005</v>
+        <v>4.375</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>9</v>
@@ -12315,7 +12647,7 @@
       </c>
       <c r="G298" s="5">
         <f t="shared" si="4"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H298" s="6" t="s">
         <v>9</v>
@@ -12342,7 +12674,7 @@
       </c>
       <c r="G299" s="5">
         <f t="shared" si="4"/>
-        <v>9.5840000000000014</v>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>9</v>
@@ -12369,7 +12701,7 @@
       </c>
       <c r="G300" s="5">
         <f t="shared" si="4"/>
-        <v>4.7840000000000007</v>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H300" s="6" t="s">
         <v>9</v>
@@ -12396,7 +12728,7 @@
       </c>
       <c r="G301" s="5">
         <f t="shared" si="4"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>9</v>
@@ -12423,7 +12755,7 @@
       </c>
       <c r="G302" s="5">
         <f t="shared" si="4"/>
-        <v>4.7840000000000007</v>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H302" s="6" t="s">
         <v>9</v>
@@ -12450,7 +12782,7 @@
       </c>
       <c r="G303" s="5">
         <f t="shared" si="4"/>
-        <v>4.7840000000000007</v>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H303" s="10" t="s">
         <v>9</v>
@@ -12477,7 +12809,7 @@
       </c>
       <c r="G304" s="5">
         <f t="shared" si="4"/>
-        <v>4.7840000000000007</v>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H304" s="6" t="s">
         <v>9</v>
@@ -12504,7 +12836,7 @@
       </c>
       <c r="G305" s="5">
         <f t="shared" si="4"/>
-        <v>3.6640000000000001</v>
+        <v>2.8624999999999998</v>
       </c>
       <c r="H305" s="10" t="s">
         <v>9</v>
@@ -12531,7 +12863,7 @@
       </c>
       <c r="G306" s="5">
         <f t="shared" si="4"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H306" s="6" t="s">
         <v>9</v>
@@ -12551,8 +12883,8 @@
         <v>5.99</v>
       </c>
       <c r="G307" s="5">
-        <f t="shared" si="4"/>
-        <v>9.5840000000000014</v>
+        <f t="shared" ref="G307:G370" si="5">F307*1.25</f>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H307" s="6"/>
     </row>
@@ -12602,8 +12934,8 @@
         <v>7.49</v>
       </c>
       <c r="G309" s="5">
-        <f t="shared" si="4"/>
-        <v>11.984000000000002</v>
+        <f t="shared" si="5"/>
+        <v>9.3625000000000007</v>
       </c>
       <c r="H309" s="10" t="s">
         <v>9</v>
@@ -12629,8 +12961,8 @@
         <v>7.49</v>
       </c>
       <c r="G310" s="5">
-        <f t="shared" si="4"/>
-        <v>11.984000000000002</v>
+        <f t="shared" si="5"/>
+        <v>9.3625000000000007</v>
       </c>
       <c r="H310" s="6" t="s">
         <v>9</v>
@@ -12656,8 +12988,8 @@
         <v>15.09</v>
       </c>
       <c r="G311" s="5">
-        <f t="shared" si="4"/>
-        <v>24.144000000000002</v>
+        <f t="shared" si="5"/>
+        <v>18.862500000000001</v>
       </c>
       <c r="H311" s="10" t="s">
         <v>9</v>
@@ -12683,8 +13015,8 @@
         <v>11.49</v>
       </c>
       <c r="G312" s="5">
-        <f t="shared" si="4"/>
-        <v>18.384</v>
+        <f t="shared" si="5"/>
+        <v>14.362500000000001</v>
       </c>
       <c r="H312" s="6" t="s">
         <v>9</v>
@@ -12710,8 +13042,8 @@
         <v>6.99</v>
       </c>
       <c r="G313" s="5">
-        <f t="shared" si="4"/>
-        <v>11.184000000000001</v>
+        <f t="shared" si="5"/>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H313" s="10" t="s">
         <v>9</v>
@@ -12737,8 +13069,8 @@
         <v>11.55</v>
       </c>
       <c r="G314" s="5">
-        <f t="shared" si="4"/>
-        <v>18.48</v>
+        <f t="shared" si="5"/>
+        <v>14.4375</v>
       </c>
       <c r="H314" s="6" t="s">
         <v>9</v>
@@ -12764,8 +13096,8 @@
         <v>1.49</v>
       </c>
       <c r="G315" s="5">
-        <f t="shared" si="4"/>
-        <v>2.3839999999999999</v>
+        <f t="shared" si="5"/>
+        <v>1.8625</v>
       </c>
       <c r="H315" s="10" t="s">
         <v>9</v>
@@ -12817,8 +13149,8 @@
         <v>19.5</v>
       </c>
       <c r="G317" s="5">
-        <f t="shared" si="4"/>
-        <v>31.200000000000003</v>
+        <f t="shared" si="5"/>
+        <v>24.375</v>
       </c>
       <c r="H317" s="6" t="s">
         <v>9</v>
@@ -12844,8 +13176,8 @@
         <v>25.74</v>
       </c>
       <c r="G318" s="5">
-        <f t="shared" si="4"/>
-        <v>41.183999999999997</v>
+        <f t="shared" si="5"/>
+        <v>32.174999999999997</v>
       </c>
       <c r="H318" s="10" t="s">
         <v>9</v>
@@ -12871,8 +13203,8 @@
         <v>37.79</v>
       </c>
       <c r="G319" s="5">
-        <f t="shared" si="4"/>
-        <v>60.463999999999999</v>
+        <f t="shared" si="5"/>
+        <v>47.237499999999997</v>
       </c>
       <c r="H319" s="6" t="s">
         <v>9</v>
@@ -12898,8 +13230,8 @@
         <v>25.5</v>
       </c>
       <c r="G320" s="5">
-        <f t="shared" si="4"/>
-        <v>40.800000000000004</v>
+        <f t="shared" si="5"/>
+        <v>31.875</v>
       </c>
       <c r="H320" s="10" t="s">
         <v>9</v>
@@ -12925,8 +13257,8 @@
         <v>19.739999999999998</v>
       </c>
       <c r="G321" s="5">
-        <f t="shared" si="4"/>
-        <v>31.584</v>
+        <f t="shared" si="5"/>
+        <v>24.674999999999997</v>
       </c>
       <c r="H321" s="6" t="s">
         <v>9</v>
@@ -12952,8 +13284,8 @@
         <v>29.94</v>
       </c>
       <c r="G322" s="5">
-        <f t="shared" si="4"/>
-        <v>47.904000000000003</v>
+        <f t="shared" si="5"/>
+        <v>37.425000000000004</v>
       </c>
       <c r="H322" s="10" t="s">
         <v>9</v>
@@ -12979,8 +13311,8 @@
         <v>38.94</v>
       </c>
       <c r="G323" s="5">
-        <f t="shared" si="4"/>
-        <v>62.304000000000002</v>
+        <f t="shared" si="5"/>
+        <v>48.674999999999997</v>
       </c>
       <c r="H323" s="6" t="s">
         <v>9</v>
@@ -13006,8 +13338,8 @@
         <v>17.489999999999998</v>
       </c>
       <c r="G324" s="5">
-        <f t="shared" ref="G324:G387" si="5">F324*1.6</f>
-        <v>27.983999999999998</v>
+        <f t="shared" si="5"/>
+        <v>21.862499999999997</v>
       </c>
       <c r="H324" s="10" t="s">
         <v>9</v>
@@ -13034,7 +13366,7 @@
       </c>
       <c r="G325" s="5">
         <f t="shared" si="5"/>
-        <v>19.184000000000001</v>
+        <v>14.987500000000001</v>
       </c>
       <c r="H325" s="6" t="s">
         <v>9</v>
@@ -13061,7 +13393,7 @@
       </c>
       <c r="G326" s="5">
         <f t="shared" si="5"/>
-        <v>17.904</v>
+        <v>13.987499999999999</v>
       </c>
       <c r="H326" s="10" t="s">
         <v>9</v>
@@ -13086,7 +13418,7 @@
       </c>
       <c r="G327" s="5">
         <f t="shared" si="5"/>
-        <v>17.904</v>
+        <v>13.987499999999999</v>
       </c>
       <c r="H327" s="6" t="s">
         <v>9</v>
@@ -13113,7 +13445,7 @@
       </c>
       <c r="G328" s="5">
         <f t="shared" si="5"/>
-        <v>46.800000000000004</v>
+        <v>36.5625</v>
       </c>
       <c r="H328" s="10" t="s">
         <v>9</v>
@@ -13140,7 +13472,7 @@
       </c>
       <c r="G329" s="5">
         <f t="shared" si="5"/>
-        <v>11.344000000000001</v>
+        <v>8.8625000000000007</v>
       </c>
       <c r="H329" s="6" t="s">
         <v>9</v>
@@ -13167,7 +13499,7 @@
       </c>
       <c r="G330" s="5">
         <f t="shared" si="5"/>
-        <v>16.72</v>
+        <v>13.0625</v>
       </c>
       <c r="H330" s="10" t="s">
         <v>9</v>
@@ -13194,7 +13526,7 @@
       </c>
       <c r="G331" s="5">
         <f t="shared" si="5"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H331" s="6" t="s">
         <v>9</v>
@@ -13221,7 +13553,7 @@
       </c>
       <c r="G332" s="5">
         <f t="shared" si="5"/>
-        <v>23.76</v>
+        <v>18.5625</v>
       </c>
       <c r="H332" s="10" t="s">
         <v>9</v>
@@ -13248,7 +13580,7 @@
       </c>
       <c r="G333" s="5">
         <f t="shared" si="5"/>
-        <v>14.704000000000001</v>
+        <v>11.487499999999999</v>
       </c>
       <c r="H333" s="6" t="s">
         <v>9</v>
@@ -13269,7 +13601,7 @@
       </c>
       <c r="G334" s="5">
         <f t="shared" si="5"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H334" s="6"/>
     </row>
@@ -13286,7 +13618,7 @@
       </c>
       <c r="G335" s="5">
         <f t="shared" si="5"/>
-        <v>6.8640000000000008</v>
+        <v>5.3624999999999998</v>
       </c>
       <c r="H335" s="6"/>
     </row>
@@ -13337,7 +13669,7 @@
       </c>
       <c r="G337" s="5">
         <f t="shared" si="5"/>
-        <v>7.1840000000000011</v>
+        <v>5.6125000000000007</v>
       </c>
       <c r="H337" s="10" t="s">
         <v>9</v>
@@ -13364,7 +13696,7 @@
       </c>
       <c r="G338" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H338" s="6" t="s">
         <v>9</v>
@@ -13391,7 +13723,7 @@
       </c>
       <c r="G339" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H339" s="10" t="s">
         <v>9</v>
@@ -13418,7 +13750,7 @@
       </c>
       <c r="G340" s="5">
         <f t="shared" si="5"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H340" s="6" t="s">
         <v>9</v>
@@ -13445,7 +13777,7 @@
       </c>
       <c r="G341" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H341" s="10" t="s">
         <v>9</v>
@@ -13472,7 +13804,7 @@
       </c>
       <c r="G342" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H342" s="6" t="s">
         <v>9</v>
@@ -13499,7 +13831,7 @@
       </c>
       <c r="G343" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H343" s="10" t="s">
         <v>9</v>
@@ -13526,7 +13858,7 @@
       </c>
       <c r="G344" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H344" s="6" t="s">
         <v>9</v>
@@ -13553,7 +13885,7 @@
       </c>
       <c r="G345" s="5">
         <f t="shared" si="5"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H345" s="10" t="s">
         <v>9</v>
@@ -13580,7 +13912,7 @@
       </c>
       <c r="G346" s="5">
         <f t="shared" si="5"/>
-        <v>11.184000000000001</v>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H346" s="6" t="s">
         <v>9</v>
@@ -13607,7 +13939,7 @@
       </c>
       <c r="G347" s="5">
         <f t="shared" si="5"/>
-        <v>20.784000000000002</v>
+        <v>16.237500000000001</v>
       </c>
       <c r="H347" s="10" t="s">
         <v>9</v>
@@ -13634,7 +13966,7 @@
       </c>
       <c r="G348" s="5">
         <f t="shared" si="5"/>
-        <v>21.584000000000003</v>
+        <v>16.862500000000001</v>
       </c>
       <c r="H348" s="6" t="s">
         <v>9</v>
@@ -13661,7 +13993,7 @@
       </c>
       <c r="G349" s="5">
         <f t="shared" si="5"/>
-        <v>15.984000000000002</v>
+        <v>12.487500000000001</v>
       </c>
       <c r="H349" s="10" t="s">
         <v>9</v>
@@ -13688,7 +14020,7 @@
       </c>
       <c r="G350" s="5">
         <f t="shared" si="5"/>
-        <v>17.584</v>
+        <v>13.737500000000001</v>
       </c>
       <c r="H350" s="6" t="s">
         <v>9</v>
@@ -13715,7 +14047,7 @@
       </c>
       <c r="G351" s="5">
         <f t="shared" si="5"/>
-        <v>14.384</v>
+        <v>11.237500000000001</v>
       </c>
       <c r="H351" s="10" t="s">
         <v>9</v>
@@ -13742,7 +14074,7 @@
       </c>
       <c r="G352" s="5">
         <f t="shared" si="5"/>
-        <v>20.784000000000002</v>
+        <v>16.237500000000001</v>
       </c>
       <c r="H352" s="6" t="s">
         <v>9</v>
@@ -13769,7 +14101,7 @@
       </c>
       <c r="G353" s="5">
         <f t="shared" si="5"/>
-        <v>11.664000000000001</v>
+        <v>9.1125000000000007</v>
       </c>
       <c r="H353" s="10" t="s">
         <v>9</v>
@@ -13796,7 +14128,7 @@
       </c>
       <c r="G354" s="5">
         <f t="shared" si="5"/>
-        <v>25.584000000000003</v>
+        <v>19.987500000000001</v>
       </c>
       <c r="H354" s="6" t="s">
         <v>9</v>
@@ -13823,7 +14155,7 @@
       </c>
       <c r="G355" s="5">
         <f t="shared" si="5"/>
-        <v>51.183999999999997</v>
+        <v>39.987499999999997</v>
       </c>
       <c r="H355" s="10" t="s">
         <v>9</v>
@@ -13850,7 +14182,7 @@
       </c>
       <c r="G356" s="5">
         <f t="shared" si="5"/>
-        <v>23.984000000000002</v>
+        <v>18.737500000000001</v>
       </c>
       <c r="H356" s="6" t="s">
         <v>9</v>
@@ -13877,7 +14209,7 @@
       </c>
       <c r="G357" s="5">
         <f t="shared" si="5"/>
-        <v>27.183999999999997</v>
+        <v>21.237499999999997</v>
       </c>
       <c r="H357" s="10" t="s">
         <v>9</v>
@@ -13898,7 +14230,7 @@
       </c>
       <c r="G358" s="5">
         <f t="shared" si="5"/>
-        <v>37.583999999999996</v>
+        <v>29.362499999999997</v>
       </c>
       <c r="H358" s="10"/>
     </row>
@@ -13917,7 +14249,7 @@
       </c>
       <c r="G359" s="5">
         <f t="shared" si="5"/>
-        <v>18.384</v>
+        <v>14.362500000000001</v>
       </c>
       <c r="H359" s="10"/>
     </row>
@@ -13936,7 +14268,7 @@
       </c>
       <c r="G360" s="5">
         <f t="shared" si="5"/>
-        <v>25.584000000000003</v>
+        <v>19.987500000000001</v>
       </c>
       <c r="H360" s="10"/>
     </row>
@@ -13961,7 +14293,7 @@
       </c>
       <c r="G361" s="5">
         <f t="shared" si="5"/>
-        <v>11.344000000000001</v>
+        <v>8.8625000000000007</v>
       </c>
       <c r="H361" s="6" t="s">
         <v>9</v>
@@ -13988,7 +14320,7 @@
       </c>
       <c r="G362" s="5">
         <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H362" s="10" t="s">
         <v>9</v>
@@ -14041,7 +14373,7 @@
       </c>
       <c r="G364" s="5">
         <f t="shared" si="5"/>
-        <v>10.384</v>
+        <v>8.1125000000000007</v>
       </c>
       <c r="H364" s="6" t="s">
         <v>9</v>
@@ -14068,7 +14400,7 @@
       </c>
       <c r="G365" s="5">
         <f t="shared" si="5"/>
-        <v>7.4400000000000013</v>
+        <v>5.8125</v>
       </c>
       <c r="H365" s="10" t="s">
         <v>9</v>
@@ -14095,7 +14427,7 @@
       </c>
       <c r="G366" s="5">
         <f t="shared" si="5"/>
-        <v>5.5840000000000005</v>
+        <v>4.3625000000000007</v>
       </c>
       <c r="H366" s="6" t="s">
         <v>9</v>
@@ -14122,7 +14454,7 @@
       </c>
       <c r="G367" s="5">
         <f t="shared" si="5"/>
-        <v>13.424000000000001</v>
+        <v>10.487500000000001</v>
       </c>
       <c r="H367" s="10" t="s">
         <v>9</v>
@@ -14149,7 +14481,7 @@
       </c>
       <c r="G368" s="5">
         <f t="shared" si="5"/>
-        <v>10.064</v>
+        <v>7.8624999999999998</v>
       </c>
       <c r="H368" s="6" t="s">
         <v>9</v>
@@ -14176,7 +14508,7 @@
       </c>
       <c r="G369" s="5">
         <f t="shared" si="5"/>
-        <v>4.7840000000000007</v>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H369" s="10" t="s">
         <v>9</v>
@@ -14203,7 +14535,7 @@
       </c>
       <c r="G370" s="5">
         <f t="shared" si="5"/>
-        <v>13.424000000000001</v>
+        <v>10.487500000000001</v>
       </c>
       <c r="H370" s="6" t="s">
         <v>9</v>
@@ -14229,8 +14561,8 @@
         <v>6.19</v>
       </c>
       <c r="G371" s="5">
-        <f t="shared" si="5"/>
-        <v>9.9040000000000017</v>
+        <f t="shared" ref="G371:G434" si="6">F371*1.25</f>
+        <v>7.7375000000000007</v>
       </c>
       <c r="H371" s="10" t="s">
         <v>9</v>
@@ -14256,8 +14588,8 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="G372" s="5">
-        <f t="shared" si="5"/>
-        <v>3.9840000000000004</v>
+        <f t="shared" si="6"/>
+        <v>3.1125000000000003</v>
       </c>
       <c r="H372" s="6" t="s">
         <v>9</v>
@@ -14283,8 +14615,8 @@
         <v>7.99</v>
       </c>
       <c r="G373" s="5">
-        <f t="shared" si="5"/>
-        <v>12.784000000000001</v>
+        <f t="shared" si="6"/>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H373" s="10" t="s">
         <v>9</v>
@@ -14336,8 +14668,8 @@
         <v>12.99</v>
       </c>
       <c r="G375" s="5">
-        <f t="shared" si="5"/>
-        <v>20.784000000000002</v>
+        <f t="shared" si="6"/>
+        <v>16.237500000000001</v>
       </c>
       <c r="H375" s="6" t="s">
         <v>9</v>
@@ -14363,8 +14695,8 @@
         <v>2.39</v>
       </c>
       <c r="G376" s="5">
-        <f t="shared" si="5"/>
-        <v>3.8240000000000003</v>
+        <f t="shared" si="6"/>
+        <v>2.9875000000000003</v>
       </c>
       <c r="H376" s="10" t="s">
         <v>9</v>
@@ -14390,8 +14722,8 @@
         <v>3.49</v>
       </c>
       <c r="G377" s="5">
-        <f t="shared" si="5"/>
-        <v>5.5840000000000005</v>
+        <f t="shared" si="6"/>
+        <v>4.3625000000000007</v>
       </c>
       <c r="H377" s="6" t="s">
         <v>9</v>
@@ -14443,8 +14775,8 @@
         <v>45.99</v>
       </c>
       <c r="G379" s="5">
-        <f t="shared" si="5"/>
-        <v>73.584000000000003</v>
+        <f t="shared" si="6"/>
+        <v>57.487500000000004</v>
       </c>
       <c r="H379" s="10" t="s">
         <v>9</v>
@@ -14470,8 +14802,8 @@
         <v>41.29</v>
       </c>
       <c r="G380" s="5">
-        <f t="shared" si="5"/>
-        <v>66.064000000000007</v>
+        <f t="shared" si="6"/>
+        <v>51.612499999999997</v>
       </c>
       <c r="H380" s="6" t="s">
         <v>9</v>
@@ -14497,8 +14829,8 @@
         <v>17.989999999999998</v>
       </c>
       <c r="G381" s="5">
-        <f t="shared" si="5"/>
-        <v>28.783999999999999</v>
+        <f t="shared" si="6"/>
+        <v>22.487499999999997</v>
       </c>
       <c r="H381" s="10" t="s">
         <v>9</v>
@@ -14524,8 +14856,8 @@
         <v>24.99</v>
       </c>
       <c r="G382" s="5">
-        <f t="shared" si="5"/>
-        <v>39.984000000000002</v>
+        <f t="shared" si="6"/>
+        <v>31.237499999999997</v>
       </c>
       <c r="H382" s="6" t="s">
         <v>9</v>
@@ -14551,8 +14883,8 @@
         <v>12.99</v>
       </c>
       <c r="G383" s="5">
-        <f t="shared" si="5"/>
-        <v>20.784000000000002</v>
+        <f t="shared" si="6"/>
+        <v>16.237500000000001</v>
       </c>
       <c r="H383" s="10" t="s">
         <v>9</v>
@@ -14578,8 +14910,8 @@
         <v>9.9</v>
       </c>
       <c r="G384" s="5">
-        <f t="shared" si="5"/>
-        <v>15.840000000000002</v>
+        <f t="shared" si="6"/>
+        <v>12.375</v>
       </c>
       <c r="H384" s="6" t="s">
         <v>9</v>
@@ -14605,8 +14937,8 @@
         <v>38.119999999999997</v>
       </c>
       <c r="G385" s="5">
-        <f t="shared" si="5"/>
-        <v>60.991999999999997</v>
+        <f t="shared" si="6"/>
+        <v>47.65</v>
       </c>
       <c r="H385" s="10" t="s">
         <v>9</v>
@@ -14632,8 +14964,8 @@
         <v>25</v>
       </c>
       <c r="G386" s="5">
-        <f t="shared" si="5"/>
-        <v>40</v>
+        <f t="shared" si="6"/>
+        <v>31.25</v>
       </c>
       <c r="H386" s="6" t="s">
         <v>9</v>
@@ -14659,8 +14991,8 @@
         <v>16.29</v>
       </c>
       <c r="G387" s="5">
-        <f t="shared" si="5"/>
-        <v>26.064</v>
+        <f t="shared" si="6"/>
+        <v>20.362499999999997</v>
       </c>
       <c r="H387" s="10" t="s">
         <v>9</v>
@@ -14686,8 +15018,8 @@
         <v>19.690000000000001</v>
       </c>
       <c r="G388" s="5">
-        <f t="shared" ref="G388:G451" si="6">F388*1.6</f>
-        <v>31.504000000000005</v>
+        <f t="shared" si="6"/>
+        <v>24.612500000000001</v>
       </c>
       <c r="H388" s="6" t="s">
         <v>9</v>
@@ -15550,7 +15882,7 @@
       </c>
       <c r="G420" s="5">
         <f t="shared" si="6"/>
-        <v>63.984000000000009</v>
+        <v>49.987500000000004</v>
       </c>
       <c r="H420" s="10" t="s">
         <v>9</v>
@@ -15577,7 +15909,7 @@
       </c>
       <c r="G421" s="5">
         <f t="shared" si="6"/>
-        <v>5.9039999999999999</v>
+        <v>4.6124999999999998</v>
       </c>
       <c r="H421" s="6" t="s">
         <v>9</v>
@@ -15604,7 +15936,7 @@
       </c>
       <c r="G422" s="5">
         <f t="shared" si="6"/>
-        <v>11.024000000000001</v>
+        <v>8.6124999999999989</v>
       </c>
       <c r="H422" s="10" t="s">
         <v>9</v>
@@ -15625,7 +15957,7 @@
       </c>
       <c r="G423" s="5">
         <f t="shared" si="6"/>
-        <v>57.584000000000003</v>
+        <v>44.987500000000004</v>
       </c>
       <c r="H423" s="10"/>
     </row>
@@ -15650,7 +15982,7 @@
       </c>
       <c r="G424" s="5">
         <f t="shared" si="6"/>
-        <v>22.864000000000001</v>
+        <v>17.862499999999997</v>
       </c>
       <c r="H424" s="6" t="s">
         <v>9</v>
@@ -15677,7 +16009,7 @@
       </c>
       <c r="G425" s="5">
         <f t="shared" si="6"/>
-        <v>10.16</v>
+        <v>7.9375</v>
       </c>
       <c r="H425" s="10" t="s">
         <v>9</v>
@@ -15704,7 +16036,7 @@
       </c>
       <c r="G426" s="5">
         <f t="shared" si="6"/>
-        <v>16.784000000000002</v>
+        <v>13.112500000000001</v>
       </c>
       <c r="H426" s="6" t="s">
         <v>9</v>
@@ -15731,7 +16063,7 @@
       </c>
       <c r="G427" s="5">
         <f t="shared" si="6"/>
-        <v>13.103999999999999</v>
+        <v>10.237499999999999</v>
       </c>
       <c r="H427" s="10" t="s">
         <v>9</v>
@@ -15758,7 +16090,7 @@
       </c>
       <c r="G428" s="5">
         <f t="shared" si="6"/>
-        <v>14.704000000000001</v>
+        <v>11.487499999999999</v>
       </c>
       <c r="H428" s="6" t="s">
         <v>9</v>
@@ -15812,7 +16144,7 @@
       </c>
       <c r="G430" s="5">
         <f t="shared" si="6"/>
-        <v>11.984000000000002</v>
+        <v>9.3625000000000007</v>
       </c>
       <c r="H430" s="6" t="s">
         <v>9</v>
@@ -15839,7 +16171,7 @@
       </c>
       <c r="G431" s="5">
         <f t="shared" si="6"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H431" s="10" t="s">
         <v>9</v>
@@ -15919,7 +16251,7 @@
       </c>
       <c r="G434" s="5">
         <f t="shared" si="6"/>
-        <v>65.584000000000003</v>
+        <v>51.237500000000004</v>
       </c>
       <c r="H434" s="10" t="s">
         <v>9</v>
@@ -15945,8 +16277,8 @@
         <v>25.99</v>
       </c>
       <c r="G435" s="5">
-        <f t="shared" si="6"/>
-        <v>41.584000000000003</v>
+        <f t="shared" ref="G435:G498" si="7">F435*1.25</f>
+        <v>32.487499999999997</v>
       </c>
       <c r="H435" s="6" t="s">
         <v>9</v>
@@ -15972,7 +16304,7 @@
         <v>9</v>
       </c>
       <c r="G436" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H436" s="10" t="s">
@@ -15999,8 +16331,8 @@
         <v>18.79</v>
       </c>
       <c r="G437" s="5">
-        <f t="shared" si="6"/>
-        <v>30.064</v>
+        <f t="shared" si="7"/>
+        <v>23.487499999999997</v>
       </c>
       <c r="H437" s="6" t="s">
         <v>9</v>
@@ -16026,8 +16358,8 @@
         <v>22.99</v>
       </c>
       <c r="G438" s="5">
-        <f t="shared" si="6"/>
-        <v>36.783999999999999</v>
+        <f t="shared" si="7"/>
+        <v>28.737499999999997</v>
       </c>
       <c r="H438" s="10" t="s">
         <v>9</v>
@@ -16053,7 +16385,7 @@
         <v>9</v>
       </c>
       <c r="G439" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H439" s="6" t="s">
@@ -16080,8 +16412,8 @@
         <v>15.99</v>
       </c>
       <c r="G440" s="5">
-        <f t="shared" si="6"/>
-        <v>25.584000000000003</v>
+        <f t="shared" si="7"/>
+        <v>19.987500000000001</v>
       </c>
       <c r="H440" s="10" t="s">
         <v>9</v>
@@ -16107,7 +16439,7 @@
         <v>9</v>
       </c>
       <c r="G441" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H441" s="6" t="s">
@@ -16134,8 +16466,8 @@
         <v>10.99</v>
       </c>
       <c r="G442" s="5">
-        <f t="shared" si="6"/>
-        <v>17.584</v>
+        <f t="shared" si="7"/>
+        <v>13.737500000000001</v>
       </c>
       <c r="H442" s="10" t="s">
         <v>9</v>
@@ -16161,7 +16493,7 @@
         <v>9</v>
       </c>
       <c r="G443" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H443" s="6" t="s">
@@ -16188,8 +16520,8 @@
         <v>14.99</v>
       </c>
       <c r="G444" s="5">
-        <f t="shared" si="6"/>
-        <v>23.984000000000002</v>
+        <f t="shared" si="7"/>
+        <v>18.737500000000001</v>
       </c>
       <c r="H444" s="10" t="s">
         <v>9</v>
@@ -16215,7 +16547,7 @@
         <v>9</v>
       </c>
       <c r="G445" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H445" s="6" t="s">
@@ -16268,7 +16600,7 @@
         <v>9</v>
       </c>
       <c r="G447" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H447" s="10" t="s">
@@ -16295,7 +16627,7 @@
         <v>9</v>
       </c>
       <c r="G448" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H448" s="6" t="s">
@@ -16322,7 +16654,7 @@
         <v>9</v>
       </c>
       <c r="G449" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H449" s="10" t="s">
@@ -16349,7 +16681,7 @@
         <v>9</v>
       </c>
       <c r="G450" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H450" s="6" t="s">
@@ -16376,7 +16708,7 @@
         <v>9</v>
       </c>
       <c r="G451" s="5" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H451" s="10" t="s">
@@ -16403,7 +16735,7 @@
         <v>9</v>
       </c>
       <c r="G452" s="5" t="e">
-        <f t="shared" ref="G452:G515" si="7">F452*1.6</f>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="H452" s="6" t="s">
@@ -16862,7 +17194,7 @@
       </c>
       <c r="G469" s="5">
         <f t="shared" si="7"/>
-        <v>30.8</v>
+        <v>24.0625</v>
       </c>
       <c r="H469" s="6" t="s">
         <v>9</v>
@@ -16889,7 +17221,7 @@
       </c>
       <c r="G470" s="5">
         <f t="shared" si="7"/>
-        <v>110.384</v>
+        <v>86.237499999999997</v>
       </c>
       <c r="H470" s="10" t="s">
         <v>9</v>
@@ -16916,7 +17248,7 @@
       </c>
       <c r="G471" s="5">
         <f t="shared" si="7"/>
-        <v>11.984000000000002</v>
+        <v>9.3625000000000007</v>
       </c>
       <c r="H471" s="6" t="s">
         <v>9</v>
@@ -16943,7 +17275,7 @@
       </c>
       <c r="G472" s="5">
         <f t="shared" si="7"/>
-        <v>13.584000000000001</v>
+        <v>10.612500000000001</v>
       </c>
       <c r="H472" s="10" t="s">
         <v>9</v>
@@ -16970,7 +17302,7 @@
       </c>
       <c r="G473" s="5">
         <f t="shared" si="7"/>
-        <v>37.839999999999996</v>
+        <v>29.5625</v>
       </c>
       <c r="H473" s="6" t="s">
         <v>9</v>
@@ -16997,7 +17329,7 @@
       </c>
       <c r="G474" s="5">
         <f t="shared" si="7"/>
-        <v>31.183999999999997</v>
+        <v>24.362499999999997</v>
       </c>
       <c r="H474" s="10" t="s">
         <v>9</v>
@@ -17050,7 +17382,7 @@
       </c>
       <c r="G476" s="5">
         <f t="shared" si="7"/>
-        <v>9.5840000000000014</v>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H476" s="6" t="s">
         <v>9</v>
@@ -17077,7 +17409,7 @@
       </c>
       <c r="G477" s="5">
         <f t="shared" si="7"/>
-        <v>9.9680000000000017</v>
+        <v>7.7875000000000005</v>
       </c>
       <c r="H477" s="10" t="s">
         <v>9</v>
@@ -17104,7 +17436,7 @@
       </c>
       <c r="G478" s="5">
         <f t="shared" si="7"/>
-        <v>9.5840000000000014</v>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H478" s="6" t="s">
         <v>9</v>
@@ -17184,7 +17516,7 @@
       </c>
       <c r="G481" s="5">
         <f t="shared" si="7"/>
-        <v>31.183999999999997</v>
+        <v>24.362499999999997</v>
       </c>
       <c r="H481" s="6" t="s">
         <v>9</v>
@@ -17211,7 +17543,7 @@
       </c>
       <c r="G482" s="5">
         <f t="shared" si="7"/>
-        <v>83.184000000000012</v>
+        <v>64.987499999999997</v>
       </c>
       <c r="H482" s="10" t="s">
         <v>9</v>
@@ -17238,7 +17570,7 @@
       </c>
       <c r="G483" s="5">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>17.1875</v>
       </c>
       <c r="H483" s="6" t="s">
         <v>9</v>
@@ -17265,7 +17597,7 @@
       </c>
       <c r="G484" s="5">
         <f t="shared" si="7"/>
-        <v>27.200000000000003</v>
+        <v>21.25</v>
       </c>
       <c r="H484" s="10" t="s">
         <v>9</v>
@@ -17292,7 +17624,7 @@
       </c>
       <c r="G485" s="5">
         <f t="shared" si="7"/>
-        <v>1.7440000000000002</v>
+        <v>1.3625</v>
       </c>
       <c r="H485" s="6" t="s">
         <v>9</v>
@@ -17319,7 +17651,7 @@
       </c>
       <c r="G486" s="5">
         <f t="shared" si="7"/>
-        <v>1.2800000000000002</v>
+        <v>1</v>
       </c>
       <c r="H486" s="10" t="s">
         <v>9</v>
@@ -17346,7 +17678,7 @@
       </c>
       <c r="G487" s="5">
         <f t="shared" si="7"/>
-        <v>16.559999999999999</v>
+        <v>12.9375</v>
       </c>
       <c r="H487" s="6" t="s">
         <v>9</v>
@@ -17373,7 +17705,7 @@
       </c>
       <c r="G488" s="5">
         <f t="shared" si="7"/>
-        <v>22.384</v>
+        <v>17.487500000000001</v>
       </c>
       <c r="H488" s="10" t="s">
         <v>9</v>
@@ -17400,7 +17732,7 @@
       </c>
       <c r="G489" s="5">
         <f t="shared" si="7"/>
-        <v>24.880000000000003</v>
+        <v>19.4375</v>
       </c>
       <c r="H489" s="6" t="s">
         <v>9</v>
@@ -17421,7 +17753,7 @@
       </c>
       <c r="G490" s="5">
         <f t="shared" si="7"/>
-        <v>4.6240000000000006</v>
+        <v>3.6125000000000003</v>
       </c>
       <c r="H490" s="6"/>
     </row>
@@ -17446,7 +17778,7 @@
       </c>
       <c r="G491" s="5">
         <f t="shared" si="7"/>
-        <v>24.880000000000003</v>
+        <v>19.4375</v>
       </c>
       <c r="H491" s="10" t="s">
         <v>9</v>
@@ -17473,7 +17805,7 @@
       </c>
       <c r="G492" s="5">
         <f t="shared" si="7"/>
-        <v>46.384</v>
+        <v>36.237499999999997</v>
       </c>
       <c r="H492" s="6" t="s">
         <v>9</v>
@@ -17500,7 +17832,7 @@
       </c>
       <c r="G493" s="5">
         <f t="shared" si="7"/>
-        <v>16.784000000000002</v>
+        <v>13.112500000000001</v>
       </c>
       <c r="H493" s="10" t="s">
         <v>9</v>
@@ -17553,7 +17885,7 @@
       </c>
       <c r="G495" s="5">
         <f t="shared" si="7"/>
-        <v>8.4640000000000004</v>
+        <v>6.6124999999999998</v>
       </c>
       <c r="H495" s="6" t="s">
         <v>9</v>
@@ -17580,7 +17912,7 @@
       </c>
       <c r="G496" s="5">
         <f t="shared" si="7"/>
-        <v>4.7840000000000007</v>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H496" s="10" t="s">
         <v>9</v>
@@ -17607,7 +17939,7 @@
       </c>
       <c r="G497" s="5">
         <f t="shared" si="7"/>
-        <v>2.3839999999999999</v>
+        <v>1.8625</v>
       </c>
       <c r="H497" s="6" t="s">
         <v>9</v>
@@ -17634,7 +17966,7 @@
       </c>
       <c r="G498" s="5">
         <f t="shared" si="7"/>
-        <v>2.3839999999999999</v>
+        <v>1.8625</v>
       </c>
       <c r="H498" s="10" t="s">
         <v>9</v>
@@ -17660,8 +17992,8 @@
         <v>1.49</v>
       </c>
       <c r="G499" s="5">
-        <f t="shared" si="7"/>
-        <v>2.3839999999999999</v>
+        <f t="shared" ref="G499:G562" si="8">F499*1.25</f>
+        <v>1.8625</v>
       </c>
       <c r="H499" s="6" t="s">
         <v>9</v>
@@ -17687,8 +18019,8 @@
         <v>9.99</v>
       </c>
       <c r="G500" s="5">
-        <f t="shared" si="7"/>
-        <v>15.984000000000002</v>
+        <f t="shared" si="8"/>
+        <v>12.487500000000001</v>
       </c>
       <c r="H500" s="10" t="s">
         <v>9</v>
@@ -17740,8 +18072,8 @@
         <v>12.75</v>
       </c>
       <c r="G502" s="5">
-        <f t="shared" si="7"/>
-        <v>20.400000000000002</v>
+        <f t="shared" si="8"/>
+        <v>15.9375</v>
       </c>
       <c r="H502" s="6" t="s">
         <v>9</v>
@@ -17767,8 +18099,8 @@
         <v>2.99</v>
       </c>
       <c r="G503" s="5">
-        <f t="shared" si="7"/>
-        <v>4.7840000000000007</v>
+        <f t="shared" si="8"/>
+        <v>3.7375000000000003</v>
       </c>
       <c r="H503" s="10" t="s">
         <v>9</v>
@@ -17794,8 +18126,8 @@
         <v>9.0500000000000007</v>
       </c>
       <c r="G504" s="5">
-        <f t="shared" si="7"/>
-        <v>14.480000000000002</v>
+        <f t="shared" si="8"/>
+        <v>11.3125</v>
       </c>
       <c r="H504" s="6" t="s">
         <v>9</v>
@@ -17847,8 +18179,8 @@
         <v>29.99</v>
       </c>
       <c r="G506" s="5">
-        <f t="shared" si="7"/>
-        <v>47.984000000000002</v>
+        <f t="shared" si="8"/>
+        <v>37.487499999999997</v>
       </c>
       <c r="H506" s="10" t="s">
         <v>9</v>
@@ -17874,8 +18206,8 @@
         <v>6.45</v>
       </c>
       <c r="G507" s="5">
-        <f t="shared" si="7"/>
-        <v>10.32</v>
+        <f t="shared" si="8"/>
+        <v>8.0625</v>
       </c>
       <c r="H507" s="6" t="s">
         <v>9</v>
@@ -17901,8 +18233,8 @@
         <v>32.49</v>
       </c>
       <c r="G508" s="5">
-        <f t="shared" si="7"/>
-        <v>51.984000000000009</v>
+        <f t="shared" si="8"/>
+        <v>40.612500000000004</v>
       </c>
       <c r="H508" s="10" t="s">
         <v>9</v>
@@ -17928,8 +18260,8 @@
         <v>7.69</v>
       </c>
       <c r="G509" s="5">
-        <f t="shared" si="7"/>
-        <v>12.304000000000002</v>
+        <f t="shared" si="8"/>
+        <v>9.6125000000000007</v>
       </c>
       <c r="H509" s="6" t="s">
         <v>9</v>
@@ -17981,8 +18313,8 @@
         <v>7.29</v>
       </c>
       <c r="G511" s="5">
-        <f t="shared" si="7"/>
-        <v>11.664000000000001</v>
+        <f t="shared" si="8"/>
+        <v>9.1125000000000007</v>
       </c>
       <c r="H511" s="10" t="s">
         <v>9</v>
@@ -18008,8 +18340,8 @@
         <v>7.99</v>
       </c>
       <c r="G512" s="5">
-        <f t="shared" si="7"/>
-        <v>12.784000000000001</v>
+        <f t="shared" si="8"/>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H512" s="6" t="s">
         <v>9</v>
@@ -18035,8 +18367,8 @@
         <v>9.7899999999999991</v>
       </c>
       <c r="G513" s="5">
-        <f t="shared" si="7"/>
-        <v>15.664</v>
+        <f t="shared" si="8"/>
+        <v>12.237499999999999</v>
       </c>
       <c r="H513" s="10" t="s">
         <v>9</v>
@@ -18062,8 +18394,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G514" s="5">
-        <f t="shared" si="7"/>
-        <v>27.183999999999997</v>
+        <f t="shared" si="8"/>
+        <v>21.237499999999997</v>
       </c>
       <c r="H514" s="6" t="s">
         <v>9</v>
@@ -18089,8 +18421,8 @@
         <v>12.99</v>
       </c>
       <c r="G515" s="5">
-        <f t="shared" si="7"/>
-        <v>20.784000000000002</v>
+        <f t="shared" si="8"/>
+        <v>16.237500000000001</v>
       </c>
       <c r="H515" s="10" t="s">
         <v>9</v>
@@ -18116,8 +18448,8 @@
         <v>1.99</v>
       </c>
       <c r="G516" s="5">
-        <f t="shared" ref="G516:G579" si="8">F516*1.6</f>
-        <v>3.1840000000000002</v>
+        <f t="shared" si="8"/>
+        <v>2.4874999999999998</v>
       </c>
       <c r="H516" s="6" t="s">
         <v>9</v>
@@ -18144,7 +18476,7 @@
       </c>
       <c r="G517" s="5">
         <f t="shared" si="8"/>
-        <v>17.584</v>
+        <v>13.737500000000001</v>
       </c>
       <c r="H517" s="10" t="s">
         <v>9</v>
@@ -18171,7 +18503,7 @@
       </c>
       <c r="G518" s="5">
         <f t="shared" si="8"/>
-        <v>15.984000000000002</v>
+        <v>12.487500000000001</v>
       </c>
       <c r="H518" s="6" t="s">
         <v>9</v>
@@ -18198,7 +18530,7 @@
       </c>
       <c r="G519" s="5">
         <f t="shared" si="8"/>
-        <v>17.584</v>
+        <v>13.737500000000001</v>
       </c>
       <c r="H519" s="10" t="s">
         <v>9</v>
@@ -18225,7 +18557,7 @@
       </c>
       <c r="G520" s="5">
         <f t="shared" si="8"/>
-        <v>7.6000000000000005</v>
+        <v>5.9375</v>
       </c>
       <c r="H520" s="6" t="s">
         <v>9</v>
@@ -18252,7 +18584,7 @@
       </c>
       <c r="G521" s="5">
         <f t="shared" si="8"/>
-        <v>3.6</v>
+        <v>2.8125</v>
       </c>
       <c r="H521" s="10" t="s">
         <v>9</v>
@@ -18279,7 +18611,7 @@
       </c>
       <c r="G522" s="5">
         <f t="shared" si="8"/>
-        <v>2.7680000000000002</v>
+        <v>2.1625000000000001</v>
       </c>
       <c r="H522" s="6" t="s">
         <v>9</v>
@@ -18306,7 +18638,7 @@
       </c>
       <c r="G523" s="5">
         <f t="shared" si="8"/>
-        <v>8.8000000000000007</v>
+        <v>6.875</v>
       </c>
       <c r="H523" s="10" t="s">
         <v>9</v>
@@ -18333,7 +18665,7 @@
       </c>
       <c r="G524" s="5">
         <f t="shared" si="8"/>
-        <v>8.32</v>
+        <v>6.5</v>
       </c>
       <c r="H524" s="6" t="s">
         <v>9</v>
@@ -18386,7 +18718,7 @@
       </c>
       <c r="G526" s="5">
         <f t="shared" si="8"/>
-        <v>19.184000000000001</v>
+        <v>14.987500000000001</v>
       </c>
       <c r="H526" s="10" t="s">
         <v>9</v>
@@ -18413,7 +18745,7 @@
       </c>
       <c r="G527" s="5">
         <f t="shared" si="8"/>
-        <v>51.183999999999997</v>
+        <v>39.987499999999997</v>
       </c>
       <c r="H527" s="6" t="s">
         <v>9</v>
@@ -18493,7 +18825,7 @@
       </c>
       <c r="G530" s="5">
         <f t="shared" si="8"/>
-        <v>5.7439999999999998</v>
+        <v>4.4874999999999998</v>
       </c>
       <c r="H530" s="6" t="s">
         <v>9</v>
@@ -18520,7 +18852,7 @@
       </c>
       <c r="G531" s="5">
         <f t="shared" si="8"/>
-        <v>4.6079999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="H531" s="10" t="s">
         <v>9</v>
@@ -18547,7 +18879,7 @@
       </c>
       <c r="G532" s="5">
         <f t="shared" si="8"/>
-        <v>6.3840000000000003</v>
+        <v>4.9875000000000007</v>
       </c>
       <c r="H532" s="6" t="s">
         <v>9</v>
@@ -18574,7 +18906,7 @@
       </c>
       <c r="G533" s="5">
         <f t="shared" si="8"/>
-        <v>2.016</v>
+        <v>1.575</v>
       </c>
       <c r="H533" s="10" t="s">
         <v>9</v>
@@ -18601,7 +18933,7 @@
       </c>
       <c r="G534" s="5">
         <f t="shared" si="8"/>
-        <v>5.36</v>
+        <v>4.1875</v>
       </c>
       <c r="H534" s="6" t="s">
         <v>9</v>
@@ -18628,7 +18960,7 @@
       </c>
       <c r="G535" s="5">
         <f t="shared" si="8"/>
-        <v>21.584000000000003</v>
+        <v>16.862500000000001</v>
       </c>
       <c r="H535" s="10" t="s">
         <v>9</v>
@@ -18655,7 +18987,7 @@
       </c>
       <c r="G536" s="5">
         <f t="shared" si="8"/>
-        <v>15.984000000000002</v>
+        <v>12.487500000000001</v>
       </c>
       <c r="H536" s="6" t="s">
         <v>9</v>
@@ -18682,7 +19014,7 @@
       </c>
       <c r="G537" s="5">
         <f t="shared" si="8"/>
-        <v>28.783999999999999</v>
+        <v>22.487499999999997</v>
       </c>
       <c r="H537" s="10" t="s">
         <v>9</v>
@@ -18735,7 +19067,7 @@
       </c>
       <c r="G539" s="5">
         <f t="shared" si="8"/>
-        <v>8.64</v>
+        <v>6.75</v>
       </c>
       <c r="H539" s="6" t="s">
         <v>9</v>
@@ -18762,7 +19094,7 @@
       </c>
       <c r="G540" s="5">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="H540" s="10" t="s">
         <v>9</v>
@@ -18789,7 +19121,7 @@
       </c>
       <c r="G541" s="5">
         <f t="shared" si="8"/>
-        <v>21.344000000000001</v>
+        <v>16.675000000000001</v>
       </c>
       <c r="H541" s="6" t="s">
         <v>9</v>
@@ -18816,7 +19148,7 @@
       </c>
       <c r="G542" s="5">
         <f t="shared" si="8"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H542" s="10" t="s">
         <v>9</v>
@@ -18843,7 +19175,7 @@
       </c>
       <c r="G543" s="5">
         <f t="shared" si="8"/>
-        <v>12.64</v>
+        <v>9.875</v>
       </c>
       <c r="H543" s="6" t="s">
         <v>9</v>
@@ -18870,7 +19202,7 @@
       </c>
       <c r="G544" s="5">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1.5625</v>
       </c>
       <c r="H544" s="10" t="s">
         <v>9</v>
@@ -18897,7 +19229,7 @@
       </c>
       <c r="G545" s="5">
         <f t="shared" si="8"/>
-        <v>16.8</v>
+        <v>13.125</v>
       </c>
       <c r="H545" s="6" t="s">
         <v>9</v>
@@ -18924,7 +19256,7 @@
       </c>
       <c r="G546" s="5">
         <f t="shared" si="8"/>
-        <v>3.056</v>
+        <v>2.3874999999999997</v>
       </c>
       <c r="H546" s="10" t="s">
         <v>9</v>
@@ -18951,7 +19283,7 @@
       </c>
       <c r="G547" s="5">
         <f t="shared" si="8"/>
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H547" s="6" t="s">
         <v>9</v>
@@ -18978,7 +19310,7 @@
       </c>
       <c r="G548" s="5">
         <f t="shared" si="8"/>
-        <v>22.32</v>
+        <v>17.4375</v>
       </c>
       <c r="H548" s="10" t="s">
         <v>9</v>
@@ -19005,7 +19337,7 @@
       </c>
       <c r="G549" s="5">
         <f t="shared" si="8"/>
-        <v>22.400000000000002</v>
+        <v>17.5</v>
       </c>
       <c r="H549" s="6" t="s">
         <v>9</v>
@@ -19032,7 +19364,7 @@
       </c>
       <c r="G550" s="5">
         <f t="shared" si="8"/>
-        <v>26.688000000000002</v>
+        <v>20.85</v>
       </c>
       <c r="H550" s="10" t="s">
         <v>9</v>
@@ -19059,7 +19391,7 @@
       </c>
       <c r="G551" s="5">
         <f t="shared" si="8"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H551" s="6" t="s">
         <v>9</v>
@@ -19086,7 +19418,7 @@
       </c>
       <c r="G552" s="5">
         <f t="shared" si="8"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H552" s="10" t="s">
         <v>9</v>
@@ -19113,7 +19445,7 @@
       </c>
       <c r="G553" s="5">
         <f t="shared" si="8"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H553" s="6" t="s">
         <v>9</v>
@@ -19140,7 +19472,7 @@
       </c>
       <c r="G554" s="5">
         <f t="shared" si="8"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H554" s="10" t="s">
         <v>9</v>
@@ -19167,7 +19499,7 @@
       </c>
       <c r="G555" s="5">
         <f t="shared" si="8"/>
-        <v>22.400000000000002</v>
+        <v>17.5</v>
       </c>
       <c r="H555" s="6" t="s">
         <v>9</v>
@@ -19194,7 +19526,7 @@
       </c>
       <c r="G556" s="5">
         <f t="shared" si="8"/>
-        <v>12.16</v>
+        <v>9.5</v>
       </c>
       <c r="H556" s="10" t="s">
         <v>9</v>
@@ -19221,7 +19553,7 @@
       </c>
       <c r="G557" s="5">
         <f t="shared" si="8"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H557" s="10" t="s">
         <v>9</v>
@@ -19248,7 +19580,7 @@
       </c>
       <c r="G558" s="5">
         <f t="shared" si="8"/>
-        <v>35.200000000000003</v>
+        <v>27.5</v>
       </c>
       <c r="H558" s="6" t="s">
         <v>9</v>
@@ -19275,7 +19607,7 @@
       </c>
       <c r="G559" s="5">
         <f t="shared" si="8"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H559" s="10" t="s">
         <v>9</v>
@@ -19302,7 +19634,7 @@
       </c>
       <c r="G560" s="5">
         <f t="shared" si="8"/>
-        <v>17.584</v>
+        <v>13.737500000000001</v>
       </c>
       <c r="H560" s="6" t="s">
         <v>9</v>
@@ -19382,8 +19714,8 @@
         <v>1.3</v>
       </c>
       <c r="G563" s="5">
-        <f t="shared" si="8"/>
-        <v>2.08</v>
+        <f t="shared" ref="G563:G626" si="9">F563*1.25</f>
+        <v>1.625</v>
       </c>
       <c r="H563" s="10" t="s">
         <v>9</v>
@@ -19409,8 +19741,8 @@
         <v>15</v>
       </c>
       <c r="G564" s="5">
-        <f t="shared" si="8"/>
-        <v>24</v>
+        <f t="shared" si="9"/>
+        <v>18.75</v>
       </c>
       <c r="H564" s="6" t="s">
         <v>9</v>
@@ -19436,8 +19768,8 @@
         <v>22</v>
       </c>
       <c r="G565" s="5">
-        <f t="shared" si="8"/>
-        <v>35.200000000000003</v>
+        <f t="shared" si="9"/>
+        <v>27.5</v>
       </c>
       <c r="H565" s="10" t="s">
         <v>9</v>
@@ -19463,7 +19795,7 @@
         <v>9</v>
       </c>
       <c r="G566" s="5" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
       <c r="H566" s="6" t="s">
@@ -19490,8 +19822,8 @@
         <v>18</v>
       </c>
       <c r="G567" s="5">
-        <f t="shared" si="8"/>
-        <v>28.8</v>
+        <f t="shared" si="9"/>
+        <v>22.5</v>
       </c>
       <c r="H567" s="10" t="s">
         <v>9</v>
@@ -19517,8 +19849,8 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="G568" s="5">
-        <f t="shared" si="8"/>
-        <v>7.3599999999999994</v>
+        <f t="shared" si="9"/>
+        <v>5.75</v>
       </c>
       <c r="H568" s="6" t="s">
         <v>9</v>
@@ -19544,8 +19876,8 @@
         <v>8</v>
       </c>
       <c r="G569" s="5">
-        <f t="shared" si="8"/>
-        <v>12.8</v>
+        <f t="shared" si="9"/>
+        <v>10</v>
       </c>
       <c r="H569" s="10" t="s">
         <v>9</v>
@@ -19571,8 +19903,8 @@
         <v>6.99</v>
       </c>
       <c r="G570" s="5">
-        <f t="shared" si="8"/>
-        <v>11.184000000000001</v>
+        <f t="shared" si="9"/>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H570" s="6" t="s">
         <v>9</v>
@@ -19598,8 +19930,8 @@
         <v>6.99</v>
       </c>
       <c r="G571" s="5">
-        <f t="shared" si="8"/>
-        <v>11.184000000000001</v>
+        <f t="shared" si="9"/>
+        <v>8.7375000000000007</v>
       </c>
       <c r="H571" s="10" t="s">
         <v>9</v>
@@ -19625,8 +19957,8 @@
         <v>3.89</v>
       </c>
       <c r="G572" s="5">
-        <f t="shared" si="8"/>
-        <v>6.2240000000000002</v>
+        <f t="shared" si="9"/>
+        <v>4.8624999999999998</v>
       </c>
       <c r="H572" s="6" t="s">
         <v>9</v>
@@ -19652,8 +19984,8 @@
         <v>10.199999999999999</v>
       </c>
       <c r="G573" s="5">
-        <f t="shared" si="8"/>
-        <v>16.32</v>
+        <f t="shared" si="9"/>
+        <v>12.75</v>
       </c>
       <c r="H573" s="10" t="s">
         <v>9</v>
@@ -19679,8 +20011,8 @@
         <v>14</v>
       </c>
       <c r="G574" s="5">
-        <f t="shared" si="8"/>
-        <v>22.400000000000002</v>
+        <f t="shared" si="9"/>
+        <v>17.5</v>
       </c>
       <c r="H574" s="6" t="s">
         <v>9</v>
@@ -19706,8 +20038,8 @@
         <v>22</v>
       </c>
       <c r="G575" s="5">
-        <f t="shared" si="8"/>
-        <v>35.200000000000003</v>
+        <f t="shared" si="9"/>
+        <v>27.5</v>
       </c>
       <c r="H575" s="10" t="s">
         <v>9</v>
@@ -19733,8 +20065,8 @@
         <v>5.49</v>
       </c>
       <c r="G576" s="5">
-        <f t="shared" si="8"/>
-        <v>8.7840000000000007</v>
+        <f t="shared" si="9"/>
+        <v>6.8625000000000007</v>
       </c>
       <c r="H576" s="6" t="s">
         <v>9</v>
@@ -19760,8 +20092,8 @@
         <v>22</v>
       </c>
       <c r="G577" s="5">
-        <f t="shared" si="8"/>
-        <v>35.200000000000003</v>
+        <f t="shared" si="9"/>
+        <v>27.5</v>
       </c>
       <c r="H577" s="10" t="s">
         <v>9</v>
@@ -19787,8 +20119,8 @@
         <v>1.3</v>
       </c>
       <c r="G578" s="5">
-        <f t="shared" si="8"/>
-        <v>2.08</v>
+        <f t="shared" si="9"/>
+        <v>1.625</v>
       </c>
       <c r="H578" s="6" t="s">
         <v>9</v>
@@ -19814,8 +20146,8 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="G579" s="5">
-        <f t="shared" si="8"/>
-        <v>13.280000000000001</v>
+        <f t="shared" si="9"/>
+        <v>10.375</v>
       </c>
       <c r="H579" s="10" t="s">
         <v>9</v>
@@ -19841,8 +20173,8 @@
         <v>36</v>
       </c>
       <c r="G580" s="5">
-        <f t="shared" ref="G580:G631" si="9">F580*1.6</f>
-        <v>57.6</v>
+        <f t="shared" si="9"/>
+        <v>45</v>
       </c>
       <c r="H580" s="6" t="s">
         <v>9</v>
@@ -19869,7 +20201,7 @@
       </c>
       <c r="G581" s="5">
         <f t="shared" si="9"/>
-        <v>8.9440000000000008</v>
+        <v>6.9874999999999998</v>
       </c>
       <c r="H581" s="10" t="s">
         <v>9</v>
@@ -19896,7 +20228,7 @@
       </c>
       <c r="G582" s="5">
         <f t="shared" si="9"/>
-        <v>11.984000000000002</v>
+        <v>9.3625000000000007</v>
       </c>
       <c r="H582" s="6" t="s">
         <v>9</v>
@@ -19923,7 +20255,7 @@
       </c>
       <c r="G583" s="5">
         <f t="shared" si="9"/>
-        <v>2.8000000000000003</v>
+        <v>2.1875</v>
       </c>
       <c r="H583" s="10" t="s">
         <v>9</v>
@@ -19950,7 +20282,7 @@
       </c>
       <c r="G584" s="5">
         <f t="shared" si="9"/>
-        <v>19.184000000000001</v>
+        <v>14.987500000000001</v>
       </c>
       <c r="H584" s="6" t="s">
         <v>9</v>
@@ -19977,7 +20309,7 @@
       </c>
       <c r="G585" s="5">
         <f t="shared" si="9"/>
-        <v>19.184000000000001</v>
+        <v>14.987500000000001</v>
       </c>
       <c r="H585" s="10" t="s">
         <v>9</v>
@@ -20004,7 +20336,7 @@
       </c>
       <c r="G586" s="5">
         <f t="shared" si="9"/>
-        <v>5.5840000000000005</v>
+        <v>4.3625000000000007</v>
       </c>
       <c r="H586" s="6" t="s">
         <v>9</v>
@@ -20031,7 +20363,7 @@
       </c>
       <c r="G587" s="5">
         <f t="shared" si="9"/>
-        <v>14.4</v>
+        <v>11.25</v>
       </c>
       <c r="H587" s="10" t="s">
         <v>9</v>
@@ -20058,7 +20390,7 @@
       </c>
       <c r="G588" s="5">
         <f t="shared" si="9"/>
-        <v>3.5200000000000005</v>
+        <v>2.75</v>
       </c>
       <c r="H588" s="6" t="s">
         <v>9</v>
@@ -20085,7 +20417,7 @@
       </c>
       <c r="G589" s="5">
         <f t="shared" si="9"/>
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="H589" s="10" t="s">
         <v>9</v>
@@ -20112,7 +20444,7 @@
       </c>
       <c r="G590" s="5">
         <f t="shared" si="9"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H590" s="6" t="s">
         <v>9</v>
@@ -20139,7 +20471,7 @@
       </c>
       <c r="G591" s="5">
         <f t="shared" si="9"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H591" s="10" t="s">
         <v>9</v>
@@ -20166,7 +20498,7 @@
       </c>
       <c r="G592" s="5">
         <f t="shared" si="9"/>
-        <v>5.120000000000001</v>
+        <v>4</v>
       </c>
       <c r="H592" s="6" t="s">
         <v>9</v>
@@ -20193,7 +20525,7 @@
       </c>
       <c r="G593" s="5">
         <f t="shared" si="9"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H593" s="10" t="s">
         <v>9</v>
@@ -20220,7 +20552,7 @@
       </c>
       <c r="G594" s="5">
         <f t="shared" si="9"/>
-        <v>5.2640000000000002</v>
+        <v>4.1124999999999998</v>
       </c>
       <c r="H594" s="6" t="s">
         <v>9</v>
@@ -20247,7 +20579,7 @@
       </c>
       <c r="G595" s="5">
         <f t="shared" si="9"/>
-        <v>9.5840000000000014</v>
+        <v>7.4875000000000007</v>
       </c>
       <c r="H595" s="10" t="s">
         <v>9</v>
@@ -20274,7 +20606,7 @@
       </c>
       <c r="G596" s="5">
         <f t="shared" si="9"/>
-        <v>3.04</v>
+        <v>2.375</v>
       </c>
       <c r="H596" s="6" t="s">
         <v>9</v>
@@ -20301,7 +20633,7 @@
       </c>
       <c r="G597" s="5">
         <f t="shared" si="9"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H597" s="10" t="s">
         <v>9</v>
@@ -20328,7 +20660,7 @@
       </c>
       <c r="G598" s="5">
         <f t="shared" si="9"/>
-        <v>6.8000000000000007</v>
+        <v>5.3125</v>
       </c>
       <c r="H598" s="6" t="s">
         <v>9</v>
@@ -20355,7 +20687,7 @@
       </c>
       <c r="G599" s="5">
         <f t="shared" si="9"/>
-        <v>12.784000000000001</v>
+        <v>9.9875000000000007</v>
       </c>
       <c r="H599" s="10" t="s">
         <v>9</v>
@@ -20382,7 +20714,7 @@
       </c>
       <c r="G600" s="5">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>31.25</v>
       </c>
       <c r="H600" s="6" t="s">
         <v>9</v>
@@ -20409,7 +20741,7 @@
       </c>
       <c r="G601" s="5">
         <f t="shared" si="9"/>
-        <v>21.6</v>
+        <v>16.875</v>
       </c>
       <c r="H601" s="10" t="s">
         <v>9</v>
@@ -20436,7 +20768,7 @@
       </c>
       <c r="G602" s="5">
         <f t="shared" si="9"/>
-        <v>5.120000000000001</v>
+        <v>4</v>
       </c>
       <c r="H602" s="6" t="s">
         <v>9</v>
@@ -20463,7 +20795,7 @@
       </c>
       <c r="G603" s="5">
         <f t="shared" si="9"/>
-        <v>14.4</v>
+        <v>11.25</v>
       </c>
       <c r="H603" s="10" t="s">
         <v>9</v>
@@ -20490,7 +20822,7 @@
       </c>
       <c r="G604" s="5">
         <f t="shared" si="9"/>
-        <v>2.08</v>
+        <v>1.625</v>
       </c>
       <c r="H604" s="6" t="s">
         <v>9</v>
@@ -20517,7 +20849,7 @@
       </c>
       <c r="G605" s="5">
         <f t="shared" si="9"/>
-        <v>2.8000000000000003</v>
+        <v>2.1875</v>
       </c>
       <c r="H605" s="10" t="s">
         <v>9</v>
@@ -20544,7 +20876,7 @@
       </c>
       <c r="G606" s="5">
         <f t="shared" si="9"/>
-        <v>2.8000000000000003</v>
+        <v>2.1875</v>
       </c>
       <c r="H606" s="6" t="s">
         <v>9</v>
@@ -20571,7 +20903,7 @@
       </c>
       <c r="G607" s="5">
         <f t="shared" si="9"/>
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="H607" s="10" t="s">
         <v>9</v>
@@ -20624,7 +20956,7 @@
       </c>
       <c r="G609" s="5">
         <f t="shared" si="9"/>
-        <v>44.800000000000004</v>
+        <v>35</v>
       </c>
       <c r="H609" s="6" t="s">
         <v>9</v>
@@ -20651,7 +20983,7 @@
       </c>
       <c r="G610" s="5">
         <f t="shared" si="9"/>
-        <v>41.6</v>
+        <v>32.5</v>
       </c>
       <c r="H610" s="10" t="s">
         <v>9</v>
@@ -20678,7 +21010,7 @@
       </c>
       <c r="G611" s="5">
         <f t="shared" si="9"/>
-        <v>42.672000000000004</v>
+        <v>33.337500000000006</v>
       </c>
       <c r="H611" s="6" t="s">
         <v>9</v>
@@ -20705,7 +21037,7 @@
       </c>
       <c r="G612" s="5">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H612" s="10" t="s">
         <v>9</v>
@@ -20732,7 +21064,7 @@
       </c>
       <c r="G613" s="5">
         <f t="shared" si="9"/>
-        <v>46.400000000000006</v>
+        <v>36.25</v>
       </c>
       <c r="H613" s="6" t="s">
         <v>9</v>
@@ -20759,7 +21091,7 @@
       </c>
       <c r="G614" s="5">
         <f t="shared" si="9"/>
-        <v>29.92</v>
+        <v>23.375</v>
       </c>
       <c r="H614" s="10" t="s">
         <v>9</v>
@@ -20786,7 +21118,7 @@
       </c>
       <c r="G615" s="5">
         <f t="shared" si="9"/>
-        <v>1.1679999999999999</v>
+        <v>0.91249999999999998</v>
       </c>
       <c r="H615" s="6" t="s">
         <v>9</v>
@@ -20813,7 +21145,7 @@
       </c>
       <c r="G616" s="5">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>31.25</v>
       </c>
       <c r="H616" s="10" t="s">
         <v>9</v>
@@ -20840,7 +21172,7 @@
       </c>
       <c r="G617" s="5">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>31.25</v>
       </c>
       <c r="H617" s="6" t="s">
         <v>9</v>
@@ -20867,7 +21199,7 @@
       </c>
       <c r="G618" s="5">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>31.25</v>
       </c>
       <c r="H618" s="10" t="s">
         <v>9</v>
@@ -20894,7 +21226,7 @@
       </c>
       <c r="G619" s="5">
         <f t="shared" si="9"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H619" s="6" t="s">
         <v>9</v>
@@ -20921,7 +21253,7 @@
       </c>
       <c r="G620" s="5">
         <f t="shared" si="9"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H620" s="10" t="s">
         <v>9</v>
@@ -20948,7 +21280,7 @@
       </c>
       <c r="G621" s="5">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>31.25</v>
       </c>
       <c r="H621" s="6" t="s">
         <v>9</v>
@@ -20975,7 +21307,7 @@
       </c>
       <c r="G622" s="5">
         <f t="shared" si="9"/>
-        <v>22.400000000000002</v>
+        <v>17.5</v>
       </c>
       <c r="H622" s="10" t="s">
         <v>9</v>
@@ -21002,7 +21334,7 @@
       </c>
       <c r="G623" s="5">
         <f t="shared" si="9"/>
-        <v>38.400000000000006</v>
+        <v>30</v>
       </c>
       <c r="H623" s="6" t="s">
         <v>9</v>
@@ -21029,7 +21361,7 @@
       </c>
       <c r="G624" s="5">
         <f t="shared" si="9"/>
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="H624" s="10" t="s">
         <v>9</v>
@@ -21056,7 +21388,7 @@
       </c>
       <c r="G625" s="5">
         <f t="shared" si="9"/>
-        <v>51.2</v>
+        <v>40</v>
       </c>
       <c r="H625" s="6" t="s">
         <v>9</v>
@@ -21083,7 +21415,7 @@
       </c>
       <c r="G626" s="5">
         <f t="shared" si="9"/>
-        <v>38.400000000000006</v>
+        <v>30</v>
       </c>
       <c r="H626" s="10" t="s">
         <v>9</v>
@@ -21109,8 +21441,8 @@
         <v>16</v>
       </c>
       <c r="G627" s="5">
-        <f t="shared" si="9"/>
-        <v>25.6</v>
+        <f t="shared" ref="G627:G631" si="10">F627*1.25</f>
+        <v>20</v>
       </c>
       <c r="H627" s="6" t="s">
         <v>9</v>
@@ -21136,8 +21468,8 @@
         <v>20</v>
       </c>
       <c r="G628" s="5">
-        <f t="shared" si="9"/>
-        <v>32</v>
+        <f t="shared" si="10"/>
+        <v>25</v>
       </c>
       <c r="H628" s="10" t="s">
         <v>9</v>
@@ -21163,8 +21495,8 @@
         <v>18</v>
       </c>
       <c r="G629" s="5">
-        <f t="shared" si="9"/>
-        <v>28.8</v>
+        <f t="shared" si="10"/>
+        <v>22.5</v>
       </c>
       <c r="H629" s="6" t="s">
         <v>9</v>
@@ -21190,8 +21522,8 @@
         <v>4.75</v>
       </c>
       <c r="G630" s="5">
-        <f t="shared" si="9"/>
-        <v>7.6000000000000005</v>
+        <f t="shared" si="10"/>
+        <v>5.9375</v>
       </c>
       <c r="H630" s="10" t="s">
         <v>9</v>
@@ -21217,8 +21549,8 @@
         <v>28</v>
       </c>
       <c r="G631" s="5">
-        <f t="shared" si="9"/>
-        <v>44.800000000000004</v>
+        <f t="shared" si="10"/>
+        <v>35</v>
       </c>
       <c r="H631" s="6" t="s">
         <v>9</v>
@@ -21233,6 +21565,721 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="47.77734375" customWidth="1"/>
+    <col min="3" max="8" width="17.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="18"/>
+    </row>
+    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
+    </row>
+    <row r="26" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
+    </row>
+    <row r="28" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
+    </row>
+    <row r="34" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="16"/>
+    </row>
+    <row r="36" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="14"/>
+    </row>
+    <row r="37" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C37" s="15"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="16"/>
+    </row>
+    <row r="38" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C39" s="15"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C41" s="15"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="14"/>
+    </row>
+    <row r="43" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="16"/>
+    </row>
+    <row r="44" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C45" s="15"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C46" s="13"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C47" s="15"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="16"/>
+    </row>
+    <row r="48" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="14"/>
+    </row>
+    <row r="49" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C49" s="15"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B22EAF7B-D4FC-4572-9342-174A19C42A9D}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -22380,16 +23427,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
 </file>
--- a/data/ATH PRICE LIST - MAIN.xlsx
+++ b/data/ATH PRICE LIST - MAIN.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED65F06-6616-4804-852C-663334A79F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB6AD57-4A86-487A-AA46-A29FBFBD0902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4786,8 +4786,8 @@
         <v>8.51</v>
       </c>
       <c r="G3" s="5">
-        <f>F3*1.3</f>
-        <v>11.063000000000001</v>
+        <f>F3*1.35</f>
+        <v>11.4885</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>9</v>
@@ -4813,8 +4813,8 @@
         <v>7.5</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" ref="G4:G67" si="0">F4*1.3</f>
-        <v>9.75</v>
+        <f t="shared" ref="G4:G67" si="0">F4*1.35</f>
+        <v>10.125</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>9</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G5" s="5">
         <f t="shared" si="0"/>
-        <v>5.3819999999999997</v>
+        <v>5.5889999999999995</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>9</v>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="G6" s="5">
         <f t="shared" si="0"/>
-        <v>5.6029999999999998</v>
+        <v>5.8185000000000002</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>9</v>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>32.591000000000001</v>
+        <v>33.844500000000004</v>
       </c>
       <c r="H7" s="10"/>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>28.938000000000002</v>
+        <v>30.051000000000005</v>
       </c>
       <c r="H8" s="10"/>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>16.38</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>9</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>13.26</v>
+        <v>13.77</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>9</v>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>19.876999999999999</v>
+        <v>20.641500000000001</v>
       </c>
       <c r="H11" s="10"/>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>13.26</v>
+        <v>13.77</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>9</v>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>14.040000000000001</v>
+        <v>14.580000000000002</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>9</v>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="G14" s="5">
         <f t="shared" si="0"/>
-        <v>11.687000000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>14.040000000000001</v>
+        <v>14.580000000000002</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>9</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="G16" s="5">
         <f t="shared" si="0"/>
-        <v>17.55</v>
+        <v>18.225000000000001</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>16.458000000000002</v>
+        <v>17.091000000000001</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>9</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>14.43</v>
+        <v>14.985000000000001</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>9</v>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>19.487000000000002</v>
+        <v>20.236500000000003</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>9</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G20" s="5">
         <f t="shared" si="0"/>
-        <v>17.615000000000002</v>
+        <v>18.2925</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>9</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>4.6669999999999998</v>
+        <v>4.8464999999999998</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>9</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="G22" s="5">
         <f t="shared" si="0"/>
-        <v>11.687000000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>9</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="G24" s="5">
         <f t="shared" si="0"/>
-        <v>14.807</v>
+        <v>15.376500000000002</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>9</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="G25" s="5">
         <f t="shared" si="0"/>
-        <v>14.026999999999999</v>
+        <v>14.5665</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>9</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G26" s="5">
         <f t="shared" si="0"/>
-        <v>14.807</v>
+        <v>15.376500000000002</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>9</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G27" s="5">
         <f t="shared" si="0"/>
-        <v>31.186999999999998</v>
+        <v>32.386499999999998</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>9</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="G28" s="5">
         <f t="shared" si="0"/>
-        <v>16.055</v>
+        <v>16.672499999999999</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>9</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G29" s="5">
         <f t="shared" si="0"/>
-        <v>38.987000000000002</v>
+        <v>40.486499999999999</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>9</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="G30" s="5">
         <f t="shared" si="0"/>
-        <v>16.367000000000001</v>
+        <v>16.996500000000001</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>9</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G31" s="5">
         <f t="shared" si="0"/>
-        <v>16.367000000000001</v>
+        <v>16.996500000000001</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>9</v>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G32" s="5">
         <f t="shared" si="0"/>
-        <v>31.044</v>
+        <v>32.238</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>9</v>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="G33" s="5">
         <f t="shared" si="0"/>
-        <v>19.019000000000002</v>
+        <v>19.750500000000002</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>9</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="G34" s="5">
         <f t="shared" si="0"/>
-        <v>14.807</v>
+        <v>15.376500000000002</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>9</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="G35" s="5">
         <f t="shared" si="0"/>
-        <v>19.019000000000002</v>
+        <v>19.750500000000002</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>9</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="G36" s="5">
         <f t="shared" si="0"/>
-        <v>14.767999999999999</v>
+        <v>15.336</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>9</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="G38" s="5">
         <f t="shared" si="0"/>
-        <v>10.205</v>
+        <v>10.5975</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>9</v>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="G39" s="5">
         <f t="shared" si="0"/>
-        <v>10.205</v>
+        <v>10.5975</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>9</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G40" s="5">
         <f t="shared" si="0"/>
-        <v>10.205</v>
+        <v>10.5975</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>9</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G41" s="5">
         <f t="shared" si="0"/>
-        <v>25.025000000000002</v>
+        <v>25.987500000000001</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>9</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="G42" s="5">
         <f t="shared" si="0"/>
-        <v>19.175000000000001</v>
+        <v>19.912500000000001</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>9</v>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="G43" s="5">
         <f t="shared" si="0"/>
-        <v>11.687000000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>9</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="G44" s="5">
         <f t="shared" si="0"/>
-        <v>11.037000000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>9</v>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G45" s="5">
         <f t="shared" si="0"/>
-        <v>15.275</v>
+        <v>15.862500000000001</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G46" s="5">
         <f t="shared" si="0"/>
-        <v>31.186999999999998</v>
+        <v>32.386499999999998</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>9</v>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="G47" s="5">
         <f t="shared" si="0"/>
-        <v>24.297000000000004</v>
+        <v>25.231500000000004</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>9</v>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G48" s="5">
         <f t="shared" si="0"/>
-        <v>34.307000000000002</v>
+        <v>35.6265</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>9</v>
@@ -6012,8 +6012,8 @@
         <v>118.69</v>
       </c>
       <c r="G50" s="5">
-        <f>F50*1.25</f>
-        <v>148.36250000000001</v>
+        <f t="shared" si="0"/>
+        <v>160.23150000000001</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>9</v>
@@ -6039,8 +6039,8 @@
         <v>16.489999999999998</v>
       </c>
       <c r="G51" s="5">
-        <f t="shared" ref="G51:G114" si="1">F51*1.25</f>
-        <v>20.612499999999997</v>
+        <f t="shared" si="0"/>
+        <v>22.261499999999998</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>9</v>
@@ -6066,8 +6066,8 @@
         <v>78.989999999999995</v>
       </c>
       <c r="G52" s="5">
-        <f t="shared" si="1"/>
-        <v>98.737499999999997</v>
+        <f t="shared" si="0"/>
+        <v>106.6365</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>9</v>
@@ -6093,8 +6093,8 @@
         <v>10.99</v>
       </c>
       <c r="G53" s="5">
-        <f t="shared" si="1"/>
-        <v>13.737500000000001</v>
+        <f t="shared" si="0"/>
+        <v>14.836500000000001</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>9</v>
@@ -6120,8 +6120,8 @@
         <v>28.99</v>
       </c>
       <c r="G54" s="5">
-        <f t="shared" si="1"/>
-        <v>36.237499999999997</v>
+        <f t="shared" si="0"/>
+        <v>39.136499999999998</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>9</v>
@@ -6147,8 +6147,8 @@
         <v>31.99</v>
       </c>
       <c r="G55" s="5">
-        <f t="shared" si="1"/>
-        <v>39.987499999999997</v>
+        <f t="shared" si="0"/>
+        <v>43.186500000000002</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>9</v>
@@ -6174,8 +6174,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G56" s="5">
-        <f t="shared" si="1"/>
-        <v>21.237499999999997</v>
+        <f t="shared" si="0"/>
+        <v>22.936499999999999</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>9</v>
@@ -6201,8 +6201,8 @@
         <v>29.99</v>
       </c>
       <c r="G57" s="5">
-        <f t="shared" si="1"/>
-        <v>37.487499999999997</v>
+        <f t="shared" si="0"/>
+        <v>40.486499999999999</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>9</v>
@@ -6228,8 +6228,8 @@
         <v>17.489999999999998</v>
       </c>
       <c r="G58" s="5">
-        <f t="shared" si="1"/>
-        <v>21.862499999999997</v>
+        <f t="shared" si="0"/>
+        <v>23.611499999999999</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>9</v>
@@ -6255,8 +6255,8 @@
         <v>9.99</v>
       </c>
       <c r="G59" s="5">
-        <f t="shared" si="1"/>
-        <v>12.487500000000001</v>
+        <f t="shared" si="0"/>
+        <v>13.486500000000001</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>9</v>
@@ -6282,8 +6282,8 @@
         <v>6.49</v>
       </c>
       <c r="G60" s="5">
-        <f t="shared" si="1"/>
-        <v>8.1125000000000007</v>
+        <f t="shared" si="0"/>
+        <v>8.7615000000000016</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>9</v>
@@ -6309,8 +6309,8 @@
         <v>6.59</v>
       </c>
       <c r="G61" s="5">
-        <f t="shared" si="1"/>
-        <v>8.2375000000000007</v>
+        <f t="shared" si="0"/>
+        <v>8.8964999999999996</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>9</v>
@@ -6336,8 +6336,8 @@
         <v>9.99</v>
       </c>
       <c r="G62" s="5">
-        <f t="shared" si="1"/>
-        <v>12.487500000000001</v>
+        <f t="shared" si="0"/>
+        <v>13.486500000000001</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>9</v>
@@ -6389,8 +6389,8 @@
         <v>8.89</v>
       </c>
       <c r="G64" s="5">
-        <f t="shared" si="1"/>
-        <v>11.112500000000001</v>
+        <f t="shared" si="0"/>
+        <v>12.001500000000002</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>9</v>
@@ -6416,8 +6416,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G65" s="5">
-        <f t="shared" si="1"/>
-        <v>21.237499999999997</v>
+        <f t="shared" si="0"/>
+        <v>22.936499999999999</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>9</v>
@@ -6443,8 +6443,8 @@
         <v>5.75</v>
       </c>
       <c r="G66" s="5">
-        <f t="shared" si="1"/>
-        <v>7.1875</v>
+        <f t="shared" si="0"/>
+        <v>7.7625000000000002</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>9</v>
@@ -6470,8 +6470,8 @@
         <v>22.99</v>
       </c>
       <c r="G67" s="5">
-        <f t="shared" si="1"/>
-        <v>28.737499999999997</v>
+        <f t="shared" si="0"/>
+        <v>31.0365</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>9</v>
@@ -6497,8 +6497,8 @@
         <v>11.59</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" si="1"/>
-        <v>14.487500000000001</v>
+        <f t="shared" ref="G68:G131" si="1">F68*1.35</f>
+        <v>15.646500000000001</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>9</v>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G69" s="5">
         <f t="shared" si="1"/>
-        <v>14.487500000000001</v>
+        <v>15.646500000000001</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>9</v>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="G70" s="5">
         <f t="shared" si="1"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>9</v>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="G71" s="5">
         <f t="shared" si="1"/>
-        <v>8.8625000000000007</v>
+        <v>9.5715000000000003</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>9</v>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="G72" s="5">
         <f t="shared" si="1"/>
-        <v>8.2375000000000007</v>
+        <v>8.8964999999999996</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>9</v>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="G73" s="5">
         <f t="shared" si="1"/>
-        <v>12.487500000000001</v>
+        <v>13.486500000000001</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>9</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G74" s="5">
         <f t="shared" si="1"/>
-        <v>8.7375000000000007</v>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>9</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="G75" s="5">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>2.9700000000000006</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>9</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G76" s="5">
         <f t="shared" si="1"/>
-        <v>13.112500000000001</v>
+        <v>14.161500000000002</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="G77" s="5">
         <f t="shared" si="1"/>
-        <v>12.862499999999999</v>
+        <v>13.891500000000001</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>9</v>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="G78" s="5">
         <f t="shared" si="1"/>
-        <v>39.362499999999997</v>
+        <v>42.511499999999998</v>
       </c>
       <c r="H78" s="10"/>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="G79" s="5">
         <f t="shared" si="1"/>
-        <v>12.362500000000001</v>
+        <v>13.351500000000001</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>9</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G81" s="5">
         <f t="shared" si="1"/>
-        <v>35.612499999999997</v>
+        <v>38.461500000000001</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>9</v>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G82" s="5">
         <f t="shared" si="1"/>
-        <v>14.737499999999999</v>
+        <v>15.916499999999999</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>9</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="G83" s="5">
         <f t="shared" si="1"/>
-        <v>19.987500000000001</v>
+        <v>21.586500000000001</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>9</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="G84" s="5">
         <f t="shared" si="1"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>9</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="G85" s="5">
         <f t="shared" si="1"/>
-        <v>21.237499999999997</v>
+        <v>22.936499999999999</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>9</v>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="G86" s="5">
         <f t="shared" si="1"/>
-        <v>21.237499999999997</v>
+        <v>22.936499999999999</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>9</v>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="G88" s="5">
         <f t="shared" si="1"/>
-        <v>12.362500000000001</v>
+        <v>13.351500000000001</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>9</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G89" s="5">
         <f t="shared" si="1"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>9</v>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G90" s="5">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>9</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G91" s="5">
         <f t="shared" si="1"/>
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>9</v>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G92" s="5">
         <f t="shared" si="1"/>
-        <v>16.612499999999997</v>
+        <v>17.941500000000001</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>9</v>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="G93" s="5">
         <f t="shared" si="1"/>
-        <v>16.612499999999997</v>
+        <v>17.941500000000001</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>9</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="G94" s="5">
         <f t="shared" si="1"/>
-        <v>30.1875</v>
+        <v>32.602499999999999</v>
       </c>
       <c r="H94" s="10" t="s">
         <v>9</v>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="G95" s="5">
         <f t="shared" si="1"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>9</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G96" s="5">
         <f t="shared" si="1"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>9</v>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G97" s="5">
         <f t="shared" si="1"/>
-        <v>19.237500000000001</v>
+        <v>20.776500000000002</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>9</v>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="G98" s="5">
         <f t="shared" si="1"/>
-        <v>127.3625</v>
+        <v>137.5515</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>9</v>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="G101" s="5">
         <f t="shared" si="1"/>
-        <v>53.737500000000004</v>
+        <v>58.036500000000004</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>9</v>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G102" s="5">
         <f t="shared" si="1"/>
-        <v>13.737500000000001</v>
+        <v>14.836500000000001</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>9</v>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G103" s="5">
         <f t="shared" si="1"/>
-        <v>24.487500000000001</v>
+        <v>26.4465</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>9</v>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G104" s="5">
         <f t="shared" si="1"/>
-        <v>13.487499999999999</v>
+        <v>14.5665</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>9</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="G105" s="5">
         <f t="shared" si="1"/>
-        <v>10.737500000000001</v>
+        <v>11.596500000000001</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>9</v>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G107" s="5">
         <f t="shared" si="1"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>9</v>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G108" s="5">
         <f t="shared" si="1"/>
-        <v>1.875</v>
+        <v>2.0250000000000004</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>9</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="G109" s="5">
         <f t="shared" si="1"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>9</v>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G110" s="5">
         <f t="shared" si="1"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>9</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G111" s="5">
         <f t="shared" si="1"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>9</v>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="G112" s="5">
         <f t="shared" si="1"/>
-        <v>31.237499999999997</v>
+        <v>33.736499999999999</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>9</v>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G113" s="5">
         <f t="shared" si="1"/>
-        <v>8.9375</v>
+        <v>9.6525000000000016</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>9</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="G114" s="5">
         <f t="shared" si="1"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>9</v>
@@ -7754,8 +7754,8 @@
         <v>8.99</v>
       </c>
       <c r="G115" s="5">
-        <f t="shared" ref="G115:G178" si="2">F115*1.25</f>
-        <v>11.237500000000001</v>
+        <f t="shared" si="1"/>
+        <v>12.136500000000002</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>9</v>
@@ -7807,8 +7807,8 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G117" s="5">
-        <f t="shared" si="2"/>
-        <v>24.987499999999997</v>
+        <f t="shared" si="1"/>
+        <v>26.986499999999999</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>9</v>
@@ -7834,8 +7834,8 @@
         <v>14.99</v>
       </c>
       <c r="G118" s="5">
-        <f t="shared" si="2"/>
-        <v>18.737500000000001</v>
+        <f t="shared" si="1"/>
+        <v>20.236500000000003</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>9</v>
@@ -7861,8 +7861,8 @@
         <v>9.49</v>
       </c>
       <c r="G119" s="5">
-        <f t="shared" si="2"/>
-        <v>11.862500000000001</v>
+        <f t="shared" si="1"/>
+        <v>12.811500000000001</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>9</v>
@@ -7888,8 +7888,8 @@
         <v>14.99</v>
       </c>
       <c r="G120" s="5">
-        <f t="shared" si="2"/>
-        <v>18.737500000000001</v>
+        <f t="shared" si="1"/>
+        <v>20.236500000000003</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>9</v>
@@ -7915,8 +7915,8 @@
         <v>9.19</v>
       </c>
       <c r="G121" s="5">
-        <f t="shared" si="2"/>
-        <v>11.487499999999999</v>
+        <f t="shared" si="1"/>
+        <v>12.406499999999999</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>9</v>
@@ -7942,8 +7942,8 @@
         <v>14.99</v>
       </c>
       <c r="G122" s="5">
-        <f t="shared" si="2"/>
-        <v>18.737500000000001</v>
+        <f t="shared" si="1"/>
+        <v>20.236500000000003</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>9</v>
@@ -7969,8 +7969,8 @@
         <v>6.99</v>
       </c>
       <c r="G123" s="5">
-        <f t="shared" si="2"/>
-        <v>8.7375000000000007</v>
+        <f t="shared" si="1"/>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>9</v>
@@ -7996,8 +7996,8 @@
         <v>25.65</v>
       </c>
       <c r="G124" s="5">
-        <f t="shared" si="2"/>
-        <v>32.0625</v>
+        <f t="shared" si="1"/>
+        <v>34.627499999999998</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>9</v>
@@ -8023,8 +8023,8 @@
         <v>6.59</v>
       </c>
       <c r="G125" s="5">
-        <f t="shared" si="2"/>
-        <v>8.2375000000000007</v>
+        <f t="shared" si="1"/>
+        <v>8.8964999999999996</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>9</v>
@@ -8050,8 +8050,8 @@
         <v>9.99</v>
       </c>
       <c r="G126" s="5">
-        <f t="shared" si="2"/>
-        <v>12.487500000000001</v>
+        <f t="shared" si="1"/>
+        <v>13.486500000000001</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>9</v>
@@ -8077,8 +8077,8 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G127" s="5">
-        <f t="shared" si="2"/>
-        <v>24.987499999999997</v>
+        <f t="shared" si="1"/>
+        <v>26.986499999999999</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>9</v>
@@ -8104,8 +8104,8 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="G128" s="5">
-        <f t="shared" si="2"/>
-        <v>10.362499999999999</v>
+        <f t="shared" si="1"/>
+        <v>11.1915</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>9</v>
@@ -8131,8 +8131,8 @@
         <v>14.99</v>
       </c>
       <c r="G129" s="5">
-        <f t="shared" si="2"/>
-        <v>18.737500000000001</v>
+        <f t="shared" si="1"/>
+        <v>20.236500000000003</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>9</v>
@@ -8158,8 +8158,8 @@
         <v>19.190000000000001</v>
       </c>
       <c r="G130" s="5">
-        <f t="shared" si="2"/>
-        <v>23.987500000000001</v>
+        <f t="shared" si="1"/>
+        <v>25.906500000000005</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>9</v>
@@ -8185,8 +8185,8 @@
         <v>13.29</v>
       </c>
       <c r="G131" s="5">
-        <f t="shared" si="2"/>
-        <v>16.612499999999997</v>
+        <f t="shared" si="1"/>
+        <v>17.941500000000001</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>9</v>
@@ -8212,8 +8212,8 @@
         <v>12.49</v>
       </c>
       <c r="G132" s="5">
-        <f t="shared" si="2"/>
-        <v>15.612500000000001</v>
+        <f t="shared" ref="G132:G195" si="2">F132*1.35</f>
+        <v>16.861500000000003</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="G133" s="5">
         <f t="shared" si="2"/>
-        <v>13.112500000000001</v>
+        <v>14.161500000000002</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>9</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G134" s="5">
         <f t="shared" si="2"/>
-        <v>14.612499999999999</v>
+        <v>15.781500000000001</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>9</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="G135" s="5">
         <f t="shared" si="2"/>
-        <v>12.612500000000001</v>
+        <v>13.621500000000001</v>
       </c>
       <c r="H135" s="10" t="s">
         <v>9</v>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="G136" s="5">
         <f t="shared" si="2"/>
-        <v>14.362500000000001</v>
+        <v>15.511500000000002</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>9</v>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="G137" s="5">
         <f t="shared" si="2"/>
-        <v>22.237499999999997</v>
+        <v>24.016500000000001</v>
       </c>
       <c r="H137" s="10" t="s">
         <v>9</v>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="G138" s="5">
         <f t="shared" si="2"/>
-        <v>3.8624999999999998</v>
+        <v>4.1715</v>
       </c>
       <c r="H138" s="6" t="s">
         <v>9</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G139" s="5">
         <f t="shared" si="2"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>9</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="G140" s="5">
         <f t="shared" si="2"/>
-        <v>12.237499999999999</v>
+        <v>13.2165</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>9</v>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="G141" s="5">
         <f t="shared" si="2"/>
-        <v>5.6125000000000007</v>
+        <v>6.0615000000000006</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>9</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="G142" s="5">
         <f t="shared" si="2"/>
-        <v>13.612500000000001</v>
+        <v>14.701500000000001</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>9</v>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G143" s="5">
         <f t="shared" si="2"/>
-        <v>29.737499999999997</v>
+        <v>32.116500000000002</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>9</v>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G144" s="5">
         <f t="shared" si="2"/>
-        <v>47.487500000000004</v>
+        <v>51.286500000000004</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>9</v>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G145" s="5">
         <f t="shared" si="2"/>
-        <v>19.987500000000001</v>
+        <v>21.586500000000001</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>9</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="G146" s="5">
         <f t="shared" si="2"/>
-        <v>9.6875</v>
+        <v>10.4625</v>
       </c>
       <c r="H146" s="6" t="s">
         <v>9</v>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="G147" s="5">
         <f t="shared" si="2"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>9</v>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="G148" s="5">
         <f t="shared" si="2"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>9</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="G149" s="5">
         <f t="shared" si="2"/>
-        <v>30.862500000000001</v>
+        <v>33.331500000000005</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>9</v>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G150" s="5">
         <f t="shared" si="2"/>
-        <v>8.3625000000000007</v>
+        <v>9.0315000000000012</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>9</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G151" s="5">
         <f t="shared" si="2"/>
-        <v>12.737499999999999</v>
+        <v>13.756500000000001</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>9</v>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="G152" s="5">
         <f t="shared" si="2"/>
-        <v>32.0625</v>
+        <v>34.627499999999998</v>
       </c>
       <c r="H152" s="6" t="s">
         <v>9</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="G153" s="5">
         <f t="shared" si="2"/>
-        <v>18.862500000000001</v>
+        <v>20.371500000000001</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>9</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G154" s="5">
         <f t="shared" si="2"/>
-        <v>10.3125</v>
+        <v>11.137500000000001</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>9</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G155" s="5">
         <f t="shared" si="2"/>
-        <v>35.612499999999997</v>
+        <v>38.461500000000001</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>9</v>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G156" s="5">
         <f t="shared" si="2"/>
-        <v>18.737500000000001</v>
+        <v>20.236500000000003</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>9</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G157" s="5">
         <f t="shared" si="2"/>
-        <v>18.737500000000001</v>
+        <v>20.236500000000003</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>9</v>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="G158" s="5">
         <f t="shared" si="2"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="G159" s="5">
         <f t="shared" si="2"/>
-        <v>8.1125000000000007</v>
+        <v>8.7615000000000016</v>
       </c>
       <c r="H159" s="10" t="s">
         <v>9</v>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="G160" s="5">
         <f t="shared" si="2"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>9</v>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G161" s="5">
         <f t="shared" si="2"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H161" s="10" t="s">
         <v>9</v>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G162" s="5">
         <f t="shared" si="2"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>9</v>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="G163" s="5">
         <f t="shared" si="2"/>
-        <v>8.7375000000000007</v>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H163" s="10" t="s">
         <v>9</v>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="G164" s="5">
         <f t="shared" si="2"/>
-        <v>7.2374999999999998</v>
+        <v>7.8165000000000004</v>
       </c>
       <c r="H164" s="6" t="s">
         <v>9</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G165" s="5">
         <f t="shared" si="2"/>
-        <v>9.3625000000000007</v>
+        <v>10.111500000000001</v>
       </c>
       <c r="H165" s="10" t="s">
         <v>9</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="G166" s="5">
         <f t="shared" si="2"/>
-        <v>12.487500000000001</v>
+        <v>13.486500000000001</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>9</v>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="G168" s="5">
         <f t="shared" si="2"/>
-        <v>25.612499999999997</v>
+        <v>27.6615</v>
       </c>
       <c r="H168" s="10" t="s">
         <v>9</v>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G169" s="5">
         <f t="shared" si="2"/>
-        <v>23.112499999999997</v>
+        <v>24.961500000000001</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>9</v>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="G170" s="5">
         <f t="shared" si="2"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H170" s="10" t="s">
         <v>9</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="G171" s="5">
         <f t="shared" si="2"/>
-        <v>23.112499999999997</v>
+        <v>24.961500000000001</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>9</v>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G172" s="5">
         <f t="shared" si="2"/>
-        <v>24.987499999999997</v>
+        <v>26.986499999999999</v>
       </c>
       <c r="H172" s="10" t="s">
         <v>9</v>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="G173" s="5">
         <f t="shared" si="2"/>
-        <v>13.737500000000001</v>
+        <v>14.836500000000001</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>9</v>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="G174" s="5">
         <f t="shared" si="2"/>
-        <v>22.112500000000001</v>
+        <v>23.881500000000003</v>
       </c>
       <c r="H174" s="10" t="s">
         <v>9</v>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="G175" s="5">
         <f t="shared" si="2"/>
-        <v>24.987499999999997</v>
+        <v>26.986499999999999</v>
       </c>
       <c r="H175" s="6" t="s">
         <v>9</v>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G176" s="5">
         <f t="shared" si="2"/>
-        <v>11.862500000000001</v>
+        <v>12.811500000000001</v>
       </c>
       <c r="H176" s="10" t="s">
         <v>9</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G177" s="5">
         <f t="shared" si="2"/>
-        <v>8.4875000000000007</v>
+        <v>9.166500000000001</v>
       </c>
       <c r="H177" s="6" t="s">
         <v>9</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G178" s="5">
         <f t="shared" si="2"/>
-        <v>8.4875000000000007</v>
+        <v>9.166500000000001</v>
       </c>
       <c r="H178" s="10" t="s">
         <v>9</v>
@@ -9480,8 +9480,8 @@
         <v>6.79</v>
       </c>
       <c r="G179" s="5">
-        <f t="shared" ref="G179:G242" si="3">F179*1.25</f>
-        <v>8.4875000000000007</v>
+        <f t="shared" si="2"/>
+        <v>9.166500000000001</v>
       </c>
       <c r="H179" s="6" t="s">
         <v>9</v>
@@ -9507,8 +9507,8 @@
         <v>9.49</v>
       </c>
       <c r="G180" s="5">
-        <f t="shared" si="3"/>
-        <v>11.862500000000001</v>
+        <f t="shared" si="2"/>
+        <v>12.811500000000001</v>
       </c>
       <c r="H180" s="10" t="s">
         <v>9</v>
@@ -9534,8 +9534,8 @@
         <v>11.89</v>
       </c>
       <c r="G181" s="5">
-        <f t="shared" si="3"/>
-        <v>14.862500000000001</v>
+        <f t="shared" si="2"/>
+        <v>16.051500000000001</v>
       </c>
       <c r="H181" s="6" t="s">
         <v>9</v>
@@ -9561,8 +9561,8 @@
         <v>14.59</v>
       </c>
       <c r="G182" s="5">
-        <f t="shared" si="3"/>
-        <v>18.237500000000001</v>
+        <f t="shared" si="2"/>
+        <v>19.6965</v>
       </c>
       <c r="H182" s="10" t="s">
         <v>9</v>
@@ -9588,8 +9588,8 @@
         <v>14.19</v>
       </c>
       <c r="G183" s="5">
-        <f t="shared" si="3"/>
-        <v>17.737500000000001</v>
+        <f t="shared" si="2"/>
+        <v>19.156500000000001</v>
       </c>
       <c r="H183" s="6" t="s">
         <v>9</v>
@@ -9615,8 +9615,8 @@
         <v>6.59</v>
       </c>
       <c r="G184" s="5">
-        <f t="shared" si="3"/>
-        <v>8.2375000000000007</v>
+        <f t="shared" si="2"/>
+        <v>8.8964999999999996</v>
       </c>
       <c r="H184" s="10" t="s">
         <v>9</v>
@@ -9642,8 +9642,8 @@
         <v>6.59</v>
       </c>
       <c r="G185" s="5">
-        <f t="shared" si="3"/>
-        <v>8.2375000000000007</v>
+        <f t="shared" si="2"/>
+        <v>8.8964999999999996</v>
       </c>
       <c r="H185" s="6" t="s">
         <v>9</v>
@@ -9669,8 +9669,8 @@
         <v>14.79</v>
       </c>
       <c r="G186" s="5">
-        <f t="shared" si="3"/>
-        <v>18.487499999999997</v>
+        <f t="shared" si="2"/>
+        <v>19.9665</v>
       </c>
       <c r="H186" s="10" t="s">
         <v>9</v>
@@ -9696,8 +9696,8 @@
         <v>61.79</v>
       </c>
       <c r="G187" s="5">
-        <f t="shared" si="3"/>
-        <v>77.237499999999997</v>
+        <f t="shared" si="2"/>
+        <v>83.416499999999999</v>
       </c>
       <c r="H187" s="6" t="s">
         <v>9</v>
@@ -9723,8 +9723,8 @@
         <v>49.99</v>
       </c>
       <c r="G188" s="5">
-        <f t="shared" si="3"/>
-        <v>62.487500000000004</v>
+        <f t="shared" si="2"/>
+        <v>67.486500000000007</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>9</v>
@@ -9750,8 +9750,8 @@
         <v>14.79</v>
       </c>
       <c r="G189" s="5">
-        <f t="shared" si="3"/>
-        <v>18.487499999999997</v>
+        <f t="shared" si="2"/>
+        <v>19.9665</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>9</v>
@@ -9803,8 +9803,8 @@
         <v>11.79</v>
       </c>
       <c r="G191" s="5">
-        <f t="shared" si="3"/>
-        <v>14.737499999999999</v>
+        <f t="shared" si="2"/>
+        <v>15.916499999999999</v>
       </c>
       <c r="H191" s="10" t="s">
         <v>9</v>
@@ -9830,8 +9830,8 @@
         <v>34.49</v>
       </c>
       <c r="G192" s="5">
-        <f t="shared" si="3"/>
-        <v>43.112500000000004</v>
+        <f t="shared" si="2"/>
+        <v>46.561500000000002</v>
       </c>
       <c r="H192" s="6" t="s">
         <v>9</v>
@@ -9857,8 +9857,8 @@
         <v>34.49</v>
       </c>
       <c r="G193" s="5">
-        <f t="shared" si="3"/>
-        <v>43.112500000000004</v>
+        <f t="shared" si="2"/>
+        <v>46.561500000000002</v>
       </c>
       <c r="H193" s="10" t="s">
         <v>9</v>
@@ -9884,8 +9884,8 @@
         <v>34.49</v>
       </c>
       <c r="G194" s="5">
-        <f t="shared" si="3"/>
-        <v>43.112500000000004</v>
+        <f t="shared" si="2"/>
+        <v>46.561500000000002</v>
       </c>
       <c r="H194" s="6" t="s">
         <v>9</v>
@@ -9911,8 +9911,8 @@
         <v>34.49</v>
       </c>
       <c r="G195" s="5">
-        <f t="shared" si="3"/>
-        <v>43.112500000000004</v>
+        <f t="shared" si="2"/>
+        <v>46.561500000000002</v>
       </c>
       <c r="H195" s="10" t="s">
         <v>9</v>
@@ -9938,8 +9938,8 @@
         <v>34.49</v>
       </c>
       <c r="G196" s="5">
-        <f t="shared" si="3"/>
-        <v>43.112500000000004</v>
+        <f t="shared" ref="G196:G259" si="3">F196*1.35</f>
+        <v>46.561500000000002</v>
       </c>
       <c r="H196" s="6" t="s">
         <v>9</v>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="G197" s="5">
         <f t="shared" si="3"/>
-        <v>43.112500000000004</v>
+        <v>46.561500000000002</v>
       </c>
       <c r="H197" s="10" t="s">
         <v>9</v>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G199" s="5">
         <f t="shared" si="3"/>
-        <v>29.612500000000001</v>
+        <v>31.981500000000004</v>
       </c>
       <c r="H199" s="6" t="s">
         <v>9</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G200" s="5">
         <f t="shared" si="3"/>
-        <v>23.362500000000001</v>
+        <v>25.231500000000004</v>
       </c>
       <c r="H200" s="10" t="s">
         <v>9</v>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="G201" s="5">
         <f t="shared" si="3"/>
-        <v>23.362500000000001</v>
+        <v>25.231500000000004</v>
       </c>
       <c r="H201" s="6" t="s">
         <v>9</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="G202" s="5">
         <f t="shared" si="3"/>
-        <v>0.9375</v>
+        <v>1.0125000000000002</v>
       </c>
       <c r="H202" s="10" t="s">
         <v>9</v>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="G203" s="5">
         <f t="shared" si="3"/>
-        <v>29.612500000000001</v>
+        <v>31.981500000000004</v>
       </c>
       <c r="H203" s="6" t="s">
         <v>9</v>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="G204" s="5">
         <f t="shared" si="3"/>
-        <v>0.9375</v>
+        <v>1.0125000000000002</v>
       </c>
       <c r="H204" s="10" t="s">
         <v>9</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="G205" s="5">
         <f t="shared" si="3"/>
-        <v>31.237499999999997</v>
+        <v>33.736499999999999</v>
       </c>
       <c r="H205" s="6" t="s">
         <v>9</v>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="G206" s="5">
         <f t="shared" si="3"/>
-        <v>27.487499999999997</v>
+        <v>29.686499999999999</v>
       </c>
       <c r="H206" s="10" t="s">
         <v>9</v>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="G207" s="5">
         <f t="shared" si="3"/>
-        <v>23.112499999999997</v>
+        <v>24.961500000000001</v>
       </c>
       <c r="H207" s="6" t="s">
         <v>9</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="G208" s="5">
         <f t="shared" si="3"/>
-        <v>15.612500000000001</v>
+        <v>16.861500000000003</v>
       </c>
       <c r="H208" s="10" t="s">
         <v>9</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G209" s="5">
         <f t="shared" si="3"/>
-        <v>5.6125000000000007</v>
+        <v>6.0615000000000006</v>
       </c>
       <c r="H209" s="6" t="s">
         <v>9</v>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G211" s="5">
         <f t="shared" si="3"/>
-        <v>32.487499999999997</v>
+        <v>35.086500000000001</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>9</v>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G212" s="5">
         <f t="shared" si="3"/>
-        <v>38.737499999999997</v>
+        <v>41.836500000000001</v>
       </c>
       <c r="H212" s="6" t="s">
         <v>9</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="G213" s="5">
         <f t="shared" si="3"/>
-        <v>16.237500000000001</v>
+        <v>17.5365</v>
       </c>
       <c r="H213" s="10" t="s">
         <v>9</v>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="G214" s="5">
         <f t="shared" si="3"/>
-        <v>22.487499999999997</v>
+        <v>24.2865</v>
       </c>
       <c r="H214" s="6" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="G215" s="5">
         <f t="shared" si="3"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H215" s="10" t="s">
         <v>9</v>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G216" s="5">
         <f t="shared" si="3"/>
-        <v>5.6125000000000007</v>
+        <v>6.0615000000000006</v>
       </c>
       <c r="H216" s="6" t="s">
         <v>9</v>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="G217" s="5">
         <f t="shared" si="3"/>
-        <v>6.8625000000000007</v>
+        <v>7.4115000000000011</v>
       </c>
       <c r="H217" s="10" t="s">
         <v>9</v>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="G218" s="5">
         <f t="shared" si="3"/>
-        <v>4.8624999999999998</v>
+        <v>5.2515000000000009</v>
       </c>
       <c r="H218" s="6" t="s">
         <v>9</v>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="G219" s="5">
         <f t="shared" si="3"/>
-        <v>4.7374999999999998</v>
+        <v>5.1165000000000003</v>
       </c>
       <c r="H219" s="10" t="s">
         <v>9</v>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="G220" s="5">
         <f t="shared" si="3"/>
-        <v>7.4875000000000007</v>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H220" s="6" t="s">
         <v>9</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="G221" s="5">
         <f t="shared" si="3"/>
-        <v>10.862499999999999</v>
+        <v>11.7315</v>
       </c>
       <c r="H221" s="10" t="s">
         <v>9</v>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="G222" s="5">
         <f t="shared" si="3"/>
-        <v>10.725</v>
+        <v>11.583</v>
       </c>
       <c r="H222" s="6" t="s">
         <v>9</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="G223" s="5">
         <f t="shared" si="3"/>
-        <v>24.987499999999997</v>
+        <v>26.986499999999999</v>
       </c>
       <c r="H223" s="10" t="s">
         <v>9</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="G224" s="5">
         <f t="shared" si="3"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H224" s="10"/>
     </row>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="G225" s="5">
         <f t="shared" si="3"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H225" s="10"/>
     </row>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="G226" s="5">
         <f t="shared" si="3"/>
-        <v>4.4874999999999998</v>
+        <v>4.8464999999999998</v>
       </c>
       <c r="H226" s="10"/>
     </row>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="G229" s="5">
         <f t="shared" si="3"/>
-        <v>12.862499999999999</v>
+        <v>13.891500000000001</v>
       </c>
       <c r="H229" s="6" t="s">
         <v>9</v>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="G230" s="5">
         <f t="shared" si="3"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H230" s="10" t="s">
         <v>9</v>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="G231" s="5">
         <f t="shared" si="3"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H231" s="6" t="s">
         <v>9</v>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="G232" s="5">
         <f t="shared" si="3"/>
-        <v>12.862499999999999</v>
+        <v>13.891500000000001</v>
       </c>
       <c r="H232" s="10" t="s">
         <v>9</v>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G233" s="5">
         <f t="shared" si="3"/>
-        <v>29.987499999999997</v>
+        <v>32.386499999999998</v>
       </c>
       <c r="H233" s="6" t="s">
         <v>9</v>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G234" s="5">
         <f t="shared" si="3"/>
-        <v>11.862500000000001</v>
+        <v>12.811500000000001</v>
       </c>
       <c r="H234" s="10" t="s">
         <v>9</v>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="G235" s="5">
         <f t="shared" si="3"/>
-        <v>11.862500000000001</v>
+        <v>12.811500000000001</v>
       </c>
       <c r="H235" s="6" t="s">
         <v>9</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="G236" s="5">
         <f t="shared" si="3"/>
-        <v>8.1125000000000007</v>
+        <v>8.7615000000000016</v>
       </c>
       <c r="H236" s="10" t="s">
         <v>9</v>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="G237" s="5">
         <f t="shared" si="3"/>
-        <v>12.487500000000001</v>
+        <v>13.486500000000001</v>
       </c>
       <c r="H237" s="6" t="s">
         <v>9</v>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="G238" s="5">
         <f t="shared" si="3"/>
-        <v>10.987499999999999</v>
+        <v>11.8665</v>
       </c>
       <c r="H238" s="10" t="s">
         <v>9</v>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G240" s="5">
         <f t="shared" si="3"/>
-        <v>11.9375</v>
+        <v>12.892500000000002</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>9</v>
@@ -11112,7 +11112,7 @@
       </c>
       <c r="G241" s="5">
         <f t="shared" si="3"/>
-        <v>11.487499999999999</v>
+        <v>12.406499999999999</v>
       </c>
       <c r="H241" s="10" t="s">
         <v>9</v>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="G242" s="5">
         <f t="shared" si="3"/>
-        <v>16.737500000000001</v>
+        <v>18.076500000000003</v>
       </c>
       <c r="H242" s="6" t="s">
         <v>9</v>
@@ -11165,8 +11165,8 @@
         <v>20.99</v>
       </c>
       <c r="G243" s="5">
-        <f t="shared" ref="G243:G306" si="4">F243*1.25</f>
-        <v>26.237499999999997</v>
+        <f t="shared" si="3"/>
+        <v>28.336500000000001</v>
       </c>
       <c r="H243" s="10" t="s">
         <v>9</v>
@@ -11192,8 +11192,8 @@
         <v>4.49</v>
       </c>
       <c r="G244" s="5">
-        <f t="shared" si="4"/>
-        <v>5.6125000000000007</v>
+        <f t="shared" si="3"/>
+        <v>6.0615000000000006</v>
       </c>
       <c r="H244" s="6" t="s">
         <v>9</v>
@@ -11219,8 +11219,8 @@
         <v>21.99</v>
       </c>
       <c r="G245" s="5">
-        <f t="shared" si="4"/>
-        <v>27.487499999999997</v>
+        <f t="shared" si="3"/>
+        <v>29.686499999999999</v>
       </c>
       <c r="H245" s="10" t="s">
         <v>9</v>
@@ -11246,8 +11246,8 @@
         <v>23.49</v>
       </c>
       <c r="G246" s="5">
-        <f t="shared" si="4"/>
-        <v>29.362499999999997</v>
+        <f t="shared" si="3"/>
+        <v>31.711500000000001</v>
       </c>
       <c r="H246" s="6" t="s">
         <v>9</v>
@@ -11273,8 +11273,8 @@
         <v>22.99</v>
       </c>
       <c r="G247" s="5">
-        <f t="shared" si="4"/>
-        <v>28.737499999999997</v>
+        <f t="shared" si="3"/>
+        <v>31.0365</v>
       </c>
       <c r="H247" s="10" t="s">
         <v>9</v>
@@ -11300,8 +11300,8 @@
         <v>25.49</v>
       </c>
       <c r="G248" s="5">
-        <f t="shared" si="4"/>
-        <v>31.862499999999997</v>
+        <f t="shared" si="3"/>
+        <v>34.411499999999997</v>
       </c>
       <c r="H248" s="6" t="s">
         <v>9</v>
@@ -11327,8 +11327,8 @@
         <v>9.49</v>
       </c>
       <c r="G249" s="5">
-        <f t="shared" si="4"/>
-        <v>11.862500000000001</v>
+        <f t="shared" si="3"/>
+        <v>12.811500000000001</v>
       </c>
       <c r="H249" s="10" t="s">
         <v>9</v>
@@ -11380,8 +11380,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G251" s="5">
-        <f t="shared" si="4"/>
-        <v>21.237499999999997</v>
+        <f t="shared" si="3"/>
+        <v>22.936499999999999</v>
       </c>
       <c r="H251" s="6" t="s">
         <v>9</v>
@@ -11407,8 +11407,8 @@
         <v>19.350000000000001</v>
       </c>
       <c r="G252" s="5">
-        <f t="shared" si="4"/>
-        <v>24.1875</v>
+        <f t="shared" si="3"/>
+        <v>26.122500000000002</v>
       </c>
       <c r="H252" s="10" t="s">
         <v>9</v>
@@ -11434,8 +11434,8 @@
         <v>16.55</v>
       </c>
       <c r="G253" s="5">
-        <f t="shared" si="4"/>
-        <v>20.6875</v>
+        <f t="shared" si="3"/>
+        <v>22.342500000000001</v>
       </c>
       <c r="H253" s="6" t="s">
         <v>9</v>
@@ -11461,8 +11461,8 @@
         <v>13.89</v>
       </c>
       <c r="G254" s="5">
-        <f t="shared" si="4"/>
-        <v>17.362500000000001</v>
+        <f t="shared" si="3"/>
+        <v>18.751500000000004</v>
       </c>
       <c r="H254" s="10" t="s">
         <v>9</v>
@@ -11488,8 +11488,8 @@
         <v>22.09</v>
       </c>
       <c r="G255" s="5">
-        <f t="shared" si="4"/>
-        <v>27.612500000000001</v>
+        <f t="shared" si="3"/>
+        <v>29.8215</v>
       </c>
       <c r="H255" s="6" t="s">
         <v>9</v>
@@ -11515,8 +11515,8 @@
         <v>7.59</v>
       </c>
       <c r="G256" s="5">
-        <f t="shared" si="4"/>
-        <v>9.4875000000000007</v>
+        <f t="shared" si="3"/>
+        <v>10.246500000000001</v>
       </c>
       <c r="H256" s="10" t="s">
         <v>9</v>
@@ -11542,8 +11542,8 @@
         <v>15.69</v>
       </c>
       <c r="G257" s="5">
-        <f t="shared" si="4"/>
-        <v>19.612500000000001</v>
+        <f t="shared" si="3"/>
+        <v>21.1815</v>
       </c>
       <c r="H257" s="6" t="s">
         <v>9</v>
@@ -11569,8 +11569,8 @@
         <v>16.59</v>
       </c>
       <c r="G258" s="5">
-        <f t="shared" si="4"/>
-        <v>20.737500000000001</v>
+        <f t="shared" si="3"/>
+        <v>22.3965</v>
       </c>
       <c r="H258" s="10" t="s">
         <v>9</v>
@@ -11596,8 +11596,8 @@
         <v>27.75</v>
       </c>
       <c r="G259" s="5">
-        <f t="shared" si="4"/>
-        <v>34.6875</v>
+        <f t="shared" si="3"/>
+        <v>37.462500000000006</v>
       </c>
       <c r="H259" s="6" t="s">
         <v>9</v>
@@ -11623,8 +11623,8 @@
         <v>3.49</v>
       </c>
       <c r="G260" s="5">
-        <f t="shared" si="4"/>
-        <v>4.3625000000000007</v>
+        <f t="shared" ref="G260:G323" si="4">F260*1.35</f>
+        <v>4.7115000000000009</v>
       </c>
       <c r="H260" s="10" t="s">
         <v>9</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="G262" s="5">
         <f t="shared" si="4"/>
-        <v>36.200000000000003</v>
+        <v>39.096000000000004</v>
       </c>
       <c r="H262" s="6" t="s">
         <v>9</v>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="G263" s="5">
         <f t="shared" si="4"/>
-        <v>58.487499999999997</v>
+        <v>63.166500000000006</v>
       </c>
       <c r="H263" s="10" t="s">
         <v>9</v>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G264" s="5">
         <f t="shared" si="4"/>
-        <v>30.112500000000001</v>
+        <v>32.521500000000003</v>
       </c>
       <c r="H264" s="6" t="s">
         <v>9</v>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="G265" s="5">
         <f t="shared" si="4"/>
-        <v>36.237499999999997</v>
+        <v>39.136499999999998</v>
       </c>
       <c r="H265" s="10" t="s">
         <v>9</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="G266" s="5">
         <f t="shared" si="4"/>
-        <v>6.8625000000000007</v>
+        <v>7.4115000000000011</v>
       </c>
       <c r="H266" s="6" t="s">
         <v>9</v>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G267" s="5">
         <f t="shared" si="4"/>
-        <v>16.862500000000001</v>
+        <v>18.211500000000001</v>
       </c>
       <c r="H267" s="10" t="s">
         <v>9</v>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="G268" s="5">
         <f t="shared" si="4"/>
-        <v>20.612499999999997</v>
+        <v>22.261499999999998</v>
       </c>
       <c r="H268" s="6" t="s">
         <v>9</v>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="G269" s="5">
         <f t="shared" si="4"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>9</v>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="G270" s="5">
         <f t="shared" si="4"/>
-        <v>30.612499999999997</v>
+        <v>33.061500000000002</v>
       </c>
       <c r="H270" s="6" t="s">
         <v>9</v>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="G272" s="5">
         <f t="shared" si="4"/>
-        <v>33.737499999999997</v>
+        <v>36.436500000000002</v>
       </c>
       <c r="H272" s="10" t="s">
         <v>9</v>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="G273" s="5">
         <f t="shared" si="4"/>
-        <v>23.487499999999997</v>
+        <v>25.366500000000002</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>9</v>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="G274" s="5">
         <f t="shared" si="4"/>
-        <v>24.362499999999997</v>
+        <v>26.311499999999999</v>
       </c>
       <c r="H274" s="10" t="s">
         <v>9</v>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="G275" s="5">
         <f t="shared" si="4"/>
-        <v>39.737499999999997</v>
+        <v>42.916499999999999</v>
       </c>
       <c r="H275" s="6" t="s">
         <v>9</v>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="G276" s="5">
         <f t="shared" si="4"/>
-        <v>40.612500000000004</v>
+        <v>43.861500000000007</v>
       </c>
       <c r="H276" s="10" t="s">
         <v>9</v>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="G277" s="5">
         <f t="shared" si="4"/>
-        <v>8.7375000000000007</v>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>9</v>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G279" s="5">
         <f t="shared" si="4"/>
-        <v>24.862500000000001</v>
+        <v>26.851500000000001</v>
       </c>
       <c r="H279" s="10" t="s">
         <v>9</v>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="G280" s="5">
         <f t="shared" si="4"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H280" s="6" t="s">
         <v>9</v>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="G281" s="5">
         <f t="shared" si="4"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H281" s="10" t="s">
         <v>9</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G282" s="5">
         <f t="shared" si="4"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H282" s="6" t="s">
         <v>9</v>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="G283" s="5">
         <f t="shared" si="4"/>
-        <v>6.8625000000000007</v>
+        <v>7.4115000000000011</v>
       </c>
       <c r="H283" s="10" t="s">
         <v>9</v>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="G284" s="5">
         <f t="shared" si="4"/>
-        <v>6.2375000000000007</v>
+        <v>6.7365000000000004</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G285" s="5">
         <f t="shared" si="4"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H285" s="10" t="s">
         <v>9</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="G286" s="5">
         <f t="shared" si="4"/>
-        <v>6.8625000000000007</v>
+        <v>7.4115000000000011</v>
       </c>
       <c r="H286" s="6" t="s">
         <v>9</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="G287" s="5">
         <f t="shared" si="4"/>
-        <v>16.237500000000001</v>
+        <v>17.5365</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>9</v>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G288" s="5">
         <f t="shared" si="4"/>
-        <v>14.987500000000001</v>
+        <v>16.186500000000002</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>9</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G289" s="5">
         <f t="shared" si="4"/>
-        <v>6.2375000000000007</v>
+        <v>6.7365000000000004</v>
       </c>
       <c r="H289" s="10" t="s">
         <v>9</v>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="G290" s="5">
         <f t="shared" si="4"/>
-        <v>11.862500000000001</v>
+        <v>12.811500000000001</v>
       </c>
       <c r="H290" s="6" t="s">
         <v>9</v>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="G291" s="5">
         <f t="shared" si="4"/>
-        <v>7.4875000000000007</v>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H291" s="10" t="s">
         <v>9</v>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="G292" s="5">
         <f t="shared" si="4"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H292" s="6" t="s">
         <v>9</v>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G293" s="5">
         <f t="shared" si="4"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>9</v>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G294" s="5">
         <f t="shared" si="4"/>
-        <v>6.2375000000000007</v>
+        <v>6.7365000000000004</v>
       </c>
       <c r="H294" s="6" t="s">
         <v>9</v>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G295" s="5">
         <f t="shared" si="4"/>
-        <v>6.2250000000000005</v>
+        <v>6.7230000000000008</v>
       </c>
       <c r="H295" s="10" t="s">
         <v>9</v>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G296" s="5">
         <f t="shared" si="4"/>
-        <v>8.3625000000000007</v>
+        <v>9.0315000000000012</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>9</v>
@@ -12620,7 +12620,7 @@
       </c>
       <c r="G297" s="5">
         <f t="shared" si="4"/>
-        <v>4.375</v>
+        <v>4.7250000000000005</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>9</v>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="G298" s="5">
         <f t="shared" si="4"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H298" s="6" t="s">
         <v>9</v>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="G299" s="5">
         <f t="shared" si="4"/>
-        <v>7.4875000000000007</v>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>9</v>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="G300" s="5">
         <f t="shared" si="4"/>
-        <v>3.7375000000000003</v>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H300" s="6" t="s">
         <v>9</v>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="G301" s="5">
         <f t="shared" si="4"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>9</v>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G302" s="5">
         <f t="shared" si="4"/>
-        <v>3.7375000000000003</v>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H302" s="6" t="s">
         <v>9</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="G303" s="5">
         <f t="shared" si="4"/>
-        <v>3.7375000000000003</v>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H303" s="10" t="s">
         <v>9</v>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="G304" s="5">
         <f t="shared" si="4"/>
-        <v>3.7375000000000003</v>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H304" s="6" t="s">
         <v>9</v>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="G305" s="5">
         <f t="shared" si="4"/>
-        <v>2.8624999999999998</v>
+        <v>3.0915000000000004</v>
       </c>
       <c r="H305" s="10" t="s">
         <v>9</v>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G306" s="5">
         <f t="shared" si="4"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H306" s="6" t="s">
         <v>9</v>
@@ -12883,8 +12883,8 @@
         <v>5.99</v>
       </c>
       <c r="G307" s="5">
-        <f t="shared" ref="G307:G370" si="5">F307*1.25</f>
-        <v>7.4875000000000007</v>
+        <f t="shared" si="4"/>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H307" s="6"/>
     </row>
@@ -12934,8 +12934,8 @@
         <v>7.49</v>
       </c>
       <c r="G309" s="5">
-        <f t="shared" si="5"/>
-        <v>9.3625000000000007</v>
+        <f t="shared" si="4"/>
+        <v>10.111500000000001</v>
       </c>
       <c r="H309" s="10" t="s">
         <v>9</v>
@@ -12961,8 +12961,8 @@
         <v>7.49</v>
       </c>
       <c r="G310" s="5">
-        <f t="shared" si="5"/>
-        <v>9.3625000000000007</v>
+        <f t="shared" si="4"/>
+        <v>10.111500000000001</v>
       </c>
       <c r="H310" s="6" t="s">
         <v>9</v>
@@ -12988,8 +12988,8 @@
         <v>15.09</v>
       </c>
       <c r="G311" s="5">
-        <f t="shared" si="5"/>
-        <v>18.862500000000001</v>
+        <f t="shared" si="4"/>
+        <v>20.371500000000001</v>
       </c>
       <c r="H311" s="10" t="s">
         <v>9</v>
@@ -13015,8 +13015,8 @@
         <v>11.49</v>
       </c>
       <c r="G312" s="5">
-        <f t="shared" si="5"/>
-        <v>14.362500000000001</v>
+        <f t="shared" si="4"/>
+        <v>15.511500000000002</v>
       </c>
       <c r="H312" s="6" t="s">
         <v>9</v>
@@ -13042,8 +13042,8 @@
         <v>6.99</v>
       </c>
       <c r="G313" s="5">
-        <f t="shared" si="5"/>
-        <v>8.7375000000000007</v>
+        <f t="shared" si="4"/>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H313" s="10" t="s">
         <v>9</v>
@@ -13069,8 +13069,8 @@
         <v>11.55</v>
       </c>
       <c r="G314" s="5">
-        <f t="shared" si="5"/>
-        <v>14.4375</v>
+        <f t="shared" si="4"/>
+        <v>15.592500000000001</v>
       </c>
       <c r="H314" s="6" t="s">
         <v>9</v>
@@ -13096,8 +13096,8 @@
         <v>1.49</v>
       </c>
       <c r="G315" s="5">
-        <f t="shared" si="5"/>
-        <v>1.8625</v>
+        <f t="shared" si="4"/>
+        <v>2.0115000000000003</v>
       </c>
       <c r="H315" s="10" t="s">
         <v>9</v>
@@ -13149,8 +13149,8 @@
         <v>19.5</v>
       </c>
       <c r="G317" s="5">
-        <f t="shared" si="5"/>
-        <v>24.375</v>
+        <f t="shared" si="4"/>
+        <v>26.325000000000003</v>
       </c>
       <c r="H317" s="6" t="s">
         <v>9</v>
@@ -13176,8 +13176,8 @@
         <v>25.74</v>
       </c>
       <c r="G318" s="5">
-        <f t="shared" si="5"/>
-        <v>32.174999999999997</v>
+        <f t="shared" si="4"/>
+        <v>34.749000000000002</v>
       </c>
       <c r="H318" s="10" t="s">
         <v>9</v>
@@ -13203,8 +13203,8 @@
         <v>37.79</v>
       </c>
       <c r="G319" s="5">
-        <f t="shared" si="5"/>
-        <v>47.237499999999997</v>
+        <f t="shared" si="4"/>
+        <v>51.016500000000001</v>
       </c>
       <c r="H319" s="6" t="s">
         <v>9</v>
@@ -13230,8 +13230,8 @@
         <v>25.5</v>
       </c>
       <c r="G320" s="5">
-        <f t="shared" si="5"/>
-        <v>31.875</v>
+        <f t="shared" si="4"/>
+        <v>34.425000000000004</v>
       </c>
       <c r="H320" s="10" t="s">
         <v>9</v>
@@ -13257,8 +13257,8 @@
         <v>19.739999999999998</v>
       </c>
       <c r="G321" s="5">
-        <f t="shared" si="5"/>
-        <v>24.674999999999997</v>
+        <f t="shared" si="4"/>
+        <v>26.649000000000001</v>
       </c>
       <c r="H321" s="6" t="s">
         <v>9</v>
@@ -13284,8 +13284,8 @@
         <v>29.94</v>
       </c>
       <c r="G322" s="5">
-        <f t="shared" si="5"/>
-        <v>37.425000000000004</v>
+        <f t="shared" si="4"/>
+        <v>40.419000000000004</v>
       </c>
       <c r="H322" s="10" t="s">
         <v>9</v>
@@ -13311,8 +13311,8 @@
         <v>38.94</v>
       </c>
       <c r="G323" s="5">
-        <f t="shared" si="5"/>
-        <v>48.674999999999997</v>
+        <f t="shared" si="4"/>
+        <v>52.569000000000003</v>
       </c>
       <c r="H323" s="6" t="s">
         <v>9</v>
@@ -13338,8 +13338,8 @@
         <v>17.489999999999998</v>
       </c>
       <c r="G324" s="5">
-        <f t="shared" si="5"/>
-        <v>21.862499999999997</v>
+        <f t="shared" ref="G324:G387" si="5">F324*1.35</f>
+        <v>23.611499999999999</v>
       </c>
       <c r="H324" s="10" t="s">
         <v>9</v>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="G325" s="5">
         <f t="shared" si="5"/>
-        <v>14.987500000000001</v>
+        <v>16.186500000000002</v>
       </c>
       <c r="H325" s="6" t="s">
         <v>9</v>
@@ -13393,7 +13393,7 @@
       </c>
       <c r="G326" s="5">
         <f t="shared" si="5"/>
-        <v>13.987499999999999</v>
+        <v>15.1065</v>
       </c>
       <c r="H326" s="10" t="s">
         <v>9</v>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G327" s="5">
         <f t="shared" si="5"/>
-        <v>13.987499999999999</v>
+        <v>15.1065</v>
       </c>
       <c r="H327" s="6" t="s">
         <v>9</v>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="G328" s="5">
         <f t="shared" si="5"/>
-        <v>36.5625</v>
+        <v>39.487500000000004</v>
       </c>
       <c r="H328" s="10" t="s">
         <v>9</v>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="G329" s="5">
         <f t="shared" si="5"/>
-        <v>8.8625000000000007</v>
+        <v>9.5715000000000003</v>
       </c>
       <c r="H329" s="6" t="s">
         <v>9</v>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="G330" s="5">
         <f t="shared" si="5"/>
-        <v>13.0625</v>
+        <v>14.1075</v>
       </c>
       <c r="H330" s="10" t="s">
         <v>9</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="G331" s="5">
         <f t="shared" si="5"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H331" s="6" t="s">
         <v>9</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="G332" s="5">
         <f t="shared" si="5"/>
-        <v>18.5625</v>
+        <v>20.047499999999999</v>
       </c>
       <c r="H332" s="10" t="s">
         <v>9</v>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="G333" s="5">
         <f t="shared" si="5"/>
-        <v>11.487499999999999</v>
+        <v>12.406499999999999</v>
       </c>
       <c r="H333" s="6" t="s">
         <v>9</v>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="G334" s="5">
         <f t="shared" si="5"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H334" s="6"/>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G335" s="5">
         <f t="shared" si="5"/>
-        <v>5.3624999999999998</v>
+        <v>5.7915000000000001</v>
       </c>
       <c r="H335" s="6"/>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G337" s="5">
         <f t="shared" si="5"/>
-        <v>5.6125000000000007</v>
+        <v>6.0615000000000006</v>
       </c>
       <c r="H337" s="10" t="s">
         <v>9</v>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="G338" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H338" s="6" t="s">
         <v>9</v>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="G339" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H339" s="10" t="s">
         <v>9</v>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="G340" s="5">
         <f t="shared" si="5"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H340" s="6" t="s">
         <v>9</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="G341" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H341" s="10" t="s">
         <v>9</v>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="G342" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H342" s="6" t="s">
         <v>9</v>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="G343" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H343" s="10" t="s">
         <v>9</v>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="G344" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H344" s="6" t="s">
         <v>9</v>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="G345" s="5">
         <f t="shared" si="5"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H345" s="10" t="s">
         <v>9</v>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="G346" s="5">
         <f t="shared" si="5"/>
-        <v>8.7375000000000007</v>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H346" s="6" t="s">
         <v>9</v>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="G347" s="5">
         <f t="shared" si="5"/>
-        <v>16.237500000000001</v>
+        <v>17.5365</v>
       </c>
       <c r="H347" s="10" t="s">
         <v>9</v>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G348" s="5">
         <f t="shared" si="5"/>
-        <v>16.862500000000001</v>
+        <v>18.211500000000001</v>
       </c>
       <c r="H348" s="6" t="s">
         <v>9</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="G349" s="5">
         <f t="shared" si="5"/>
-        <v>12.487500000000001</v>
+        <v>13.486500000000001</v>
       </c>
       <c r="H349" s="10" t="s">
         <v>9</v>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="G350" s="5">
         <f t="shared" si="5"/>
-        <v>13.737500000000001</v>
+        <v>14.836500000000001</v>
       </c>
       <c r="H350" s="6" t="s">
         <v>9</v>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="G351" s="5">
         <f t="shared" si="5"/>
-        <v>11.237500000000001</v>
+        <v>12.136500000000002</v>
       </c>
       <c r="H351" s="10" t="s">
         <v>9</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="G352" s="5">
         <f t="shared" si="5"/>
-        <v>16.237500000000001</v>
+        <v>17.5365</v>
       </c>
       <c r="H352" s="6" t="s">
         <v>9</v>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G353" s="5">
         <f t="shared" si="5"/>
-        <v>9.1125000000000007</v>
+        <v>9.8414999999999999</v>
       </c>
       <c r="H353" s="10" t="s">
         <v>9</v>
@@ -14128,7 +14128,7 @@
       </c>
       <c r="G354" s="5">
         <f t="shared" si="5"/>
-        <v>19.987500000000001</v>
+        <v>21.586500000000001</v>
       </c>
       <c r="H354" s="6" t="s">
         <v>9</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G355" s="5">
         <f t="shared" si="5"/>
-        <v>39.987499999999997</v>
+        <v>43.186500000000002</v>
       </c>
       <c r="H355" s="10" t="s">
         <v>9</v>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="G356" s="5">
         <f t="shared" si="5"/>
-        <v>18.737500000000001</v>
+        <v>20.236500000000003</v>
       </c>
       <c r="H356" s="6" t="s">
         <v>9</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="G357" s="5">
         <f t="shared" si="5"/>
-        <v>21.237499999999997</v>
+        <v>22.936499999999999</v>
       </c>
       <c r="H357" s="10" t="s">
         <v>9</v>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="G358" s="5">
         <f t="shared" si="5"/>
-        <v>29.362499999999997</v>
+        <v>31.711500000000001</v>
       </c>
       <c r="H358" s="10"/>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="G359" s="5">
         <f t="shared" si="5"/>
-        <v>14.362500000000001</v>
+        <v>15.511500000000002</v>
       </c>
       <c r="H359" s="10"/>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="G360" s="5">
         <f t="shared" si="5"/>
-        <v>19.987500000000001</v>
+        <v>21.586500000000001</v>
       </c>
       <c r="H360" s="10"/>
     </row>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="G361" s="5">
         <f t="shared" si="5"/>
-        <v>8.8625000000000007</v>
+        <v>9.5715000000000003</v>
       </c>
       <c r="H361" s="6" t="s">
         <v>9</v>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="G362" s="5">
         <f t="shared" si="5"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H362" s="10" t="s">
         <v>9</v>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="G364" s="5">
         <f t="shared" si="5"/>
-        <v>8.1125000000000007</v>
+        <v>8.7615000000000016</v>
       </c>
       <c r="H364" s="6" t="s">
         <v>9</v>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="G365" s="5">
         <f t="shared" si="5"/>
-        <v>5.8125</v>
+        <v>6.2775000000000007</v>
       </c>
       <c r="H365" s="10" t="s">
         <v>9</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="G366" s="5">
         <f t="shared" si="5"/>
-        <v>4.3625000000000007</v>
+        <v>4.7115000000000009</v>
       </c>
       <c r="H366" s="6" t="s">
         <v>9</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="G367" s="5">
         <f t="shared" si="5"/>
-        <v>10.487500000000001</v>
+        <v>11.326500000000001</v>
       </c>
       <c r="H367" s="10" t="s">
         <v>9</v>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="G368" s="5">
         <f t="shared" si="5"/>
-        <v>7.8624999999999998</v>
+        <v>8.4915000000000003</v>
       </c>
       <c r="H368" s="6" t="s">
         <v>9</v>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="G369" s="5">
         <f t="shared" si="5"/>
-        <v>3.7375000000000003</v>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H369" s="10" t="s">
         <v>9</v>
@@ -14535,7 +14535,7 @@
       </c>
       <c r="G370" s="5">
         <f t="shared" si="5"/>
-        <v>10.487500000000001</v>
+        <v>11.326500000000001</v>
       </c>
       <c r="H370" s="6" t="s">
         <v>9</v>
@@ -14561,8 +14561,8 @@
         <v>6.19</v>
       </c>
       <c r="G371" s="5">
-        <f t="shared" ref="G371:G434" si="6">F371*1.25</f>
-        <v>7.7375000000000007</v>
+        <f t="shared" si="5"/>
+        <v>8.3565000000000005</v>
       </c>
       <c r="H371" s="10" t="s">
         <v>9</v>
@@ -14588,8 +14588,8 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="G372" s="5">
-        <f t="shared" si="6"/>
-        <v>3.1125000000000003</v>
+        <f t="shared" si="5"/>
+        <v>3.3615000000000004</v>
       </c>
       <c r="H372" s="6" t="s">
         <v>9</v>
@@ -14615,8 +14615,8 @@
         <v>7.99</v>
       </c>
       <c r="G373" s="5">
-        <f t="shared" si="6"/>
-        <v>9.9875000000000007</v>
+        <f t="shared" si="5"/>
+        <v>10.7865</v>
       </c>
       <c r="H373" s="10" t="s">
         <v>9</v>
@@ -14668,8 +14668,8 @@
         <v>12.99</v>
       </c>
       <c r="G375" s="5">
-        <f t="shared" si="6"/>
-        <v>16.237500000000001</v>
+        <f t="shared" si="5"/>
+        <v>17.5365</v>
       </c>
       <c r="H375" s="6" t="s">
         <v>9</v>
@@ -14695,8 +14695,8 @@
         <v>2.39</v>
       </c>
       <c r="G376" s="5">
-        <f t="shared" si="6"/>
-        <v>2.9875000000000003</v>
+        <f t="shared" si="5"/>
+        <v>3.2265000000000006</v>
       </c>
       <c r="H376" s="10" t="s">
         <v>9</v>
@@ -14722,8 +14722,8 @@
         <v>3.49</v>
       </c>
       <c r="G377" s="5">
-        <f t="shared" si="6"/>
-        <v>4.3625000000000007</v>
+        <f t="shared" si="5"/>
+        <v>4.7115000000000009</v>
       </c>
       <c r="H377" s="6" t="s">
         <v>9</v>
@@ -14775,8 +14775,8 @@
         <v>45.99</v>
       </c>
       <c r="G379" s="5">
-        <f t="shared" si="6"/>
-        <v>57.487500000000004</v>
+        <f t="shared" si="5"/>
+        <v>62.086500000000008</v>
       </c>
       <c r="H379" s="10" t="s">
         <v>9</v>
@@ -14802,8 +14802,8 @@
         <v>41.29</v>
       </c>
       <c r="G380" s="5">
-        <f t="shared" si="6"/>
-        <v>51.612499999999997</v>
+        <f t="shared" si="5"/>
+        <v>55.741500000000002</v>
       </c>
       <c r="H380" s="6" t="s">
         <v>9</v>
@@ -14829,8 +14829,8 @@
         <v>17.989999999999998</v>
       </c>
       <c r="G381" s="5">
-        <f t="shared" si="6"/>
-        <v>22.487499999999997</v>
+        <f t="shared" si="5"/>
+        <v>24.2865</v>
       </c>
       <c r="H381" s="10" t="s">
         <v>9</v>
@@ -14856,8 +14856,8 @@
         <v>24.99</v>
       </c>
       <c r="G382" s="5">
-        <f t="shared" si="6"/>
-        <v>31.237499999999997</v>
+        <f t="shared" si="5"/>
+        <v>33.736499999999999</v>
       </c>
       <c r="H382" s="6" t="s">
         <v>9</v>
@@ -14883,8 +14883,8 @@
         <v>12.99</v>
       </c>
       <c r="G383" s="5">
-        <f t="shared" si="6"/>
-        <v>16.237500000000001</v>
+        <f t="shared" si="5"/>
+        <v>17.5365</v>
       </c>
       <c r="H383" s="10" t="s">
         <v>9</v>
@@ -14910,8 +14910,8 @@
         <v>9.9</v>
       </c>
       <c r="G384" s="5">
-        <f t="shared" si="6"/>
-        <v>12.375</v>
+        <f t="shared" si="5"/>
+        <v>13.365000000000002</v>
       </c>
       <c r="H384" s="6" t="s">
         <v>9</v>
@@ -14937,8 +14937,8 @@
         <v>38.119999999999997</v>
       </c>
       <c r="G385" s="5">
-        <f t="shared" si="6"/>
-        <v>47.65</v>
+        <f t="shared" si="5"/>
+        <v>51.462000000000003</v>
       </c>
       <c r="H385" s="10" t="s">
         <v>9</v>
@@ -14964,8 +14964,8 @@
         <v>25</v>
       </c>
       <c r="G386" s="5">
-        <f t="shared" si="6"/>
-        <v>31.25</v>
+        <f t="shared" si="5"/>
+        <v>33.75</v>
       </c>
       <c r="H386" s="6" t="s">
         <v>9</v>
@@ -14991,8 +14991,8 @@
         <v>16.29</v>
       </c>
       <c r="G387" s="5">
-        <f t="shared" si="6"/>
-        <v>20.362499999999997</v>
+        <f t="shared" si="5"/>
+        <v>21.991500000000002</v>
       </c>
       <c r="H387" s="10" t="s">
         <v>9</v>
@@ -15018,8 +15018,8 @@
         <v>19.690000000000001</v>
       </c>
       <c r="G388" s="5">
-        <f t="shared" si="6"/>
-        <v>24.612500000000001</v>
+        <f t="shared" ref="G388:G451" si="6">F388*1.35</f>
+        <v>26.581500000000002</v>
       </c>
       <c r="H388" s="6" t="s">
         <v>9</v>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="G420" s="5">
         <f t="shared" si="6"/>
-        <v>49.987500000000004</v>
+        <v>53.986500000000007</v>
       </c>
       <c r="H420" s="10" t="s">
         <v>9</v>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="G421" s="5">
         <f t="shared" si="6"/>
-        <v>4.6124999999999998</v>
+        <v>4.9815000000000005</v>
       </c>
       <c r="H421" s="6" t="s">
         <v>9</v>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="G422" s="5">
         <f t="shared" si="6"/>
-        <v>8.6124999999999989</v>
+        <v>9.3015000000000008</v>
       </c>
       <c r="H422" s="10" t="s">
         <v>9</v>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="G423" s="5">
         <f t="shared" si="6"/>
-        <v>44.987500000000004</v>
+        <v>48.586500000000008</v>
       </c>
       <c r="H423" s="10"/>
     </row>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="G424" s="5">
         <f t="shared" si="6"/>
-        <v>17.862499999999997</v>
+        <v>19.291499999999999</v>
       </c>
       <c r="H424" s="6" t="s">
         <v>9</v>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="G425" s="5">
         <f t="shared" si="6"/>
-        <v>7.9375</v>
+        <v>8.5724999999999998</v>
       </c>
       <c r="H425" s="10" t="s">
         <v>9</v>
@@ -16036,7 +16036,7 @@
       </c>
       <c r="G426" s="5">
         <f t="shared" si="6"/>
-        <v>13.112500000000001</v>
+        <v>14.161500000000002</v>
       </c>
       <c r="H426" s="6" t="s">
         <v>9</v>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G427" s="5">
         <f t="shared" si="6"/>
-        <v>10.237499999999999</v>
+        <v>11.0565</v>
       </c>
       <c r="H427" s="10" t="s">
         <v>9</v>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="G428" s="5">
         <f t="shared" si="6"/>
-        <v>11.487499999999999</v>
+        <v>12.406499999999999</v>
       </c>
       <c r="H428" s="6" t="s">
         <v>9</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="G430" s="5">
         <f t="shared" si="6"/>
-        <v>9.3625000000000007</v>
+        <v>10.111500000000001</v>
       </c>
       <c r="H430" s="6" t="s">
         <v>9</v>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="G431" s="5">
         <f t="shared" si="6"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H431" s="10" t="s">
         <v>9</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="G434" s="5">
         <f t="shared" si="6"/>
-        <v>51.237500000000004</v>
+        <v>55.336500000000008</v>
       </c>
       <c r="H434" s="10" t="s">
         <v>9</v>
@@ -16277,8 +16277,8 @@
         <v>25.99</v>
       </c>
       <c r="G435" s="5">
-        <f t="shared" ref="G435:G498" si="7">F435*1.25</f>
-        <v>32.487499999999997</v>
+        <f t="shared" si="6"/>
+        <v>35.086500000000001</v>
       </c>
       <c r="H435" s="6" t="s">
         <v>9</v>
@@ -16304,7 +16304,7 @@
         <v>9</v>
       </c>
       <c r="G436" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H436" s="10" t="s">
@@ -16331,8 +16331,8 @@
         <v>18.79</v>
       </c>
       <c r="G437" s="5">
-        <f t="shared" si="7"/>
-        <v>23.487499999999997</v>
+        <f t="shared" si="6"/>
+        <v>25.366500000000002</v>
       </c>
       <c r="H437" s="6" t="s">
         <v>9</v>
@@ -16358,8 +16358,8 @@
         <v>22.99</v>
       </c>
       <c r="G438" s="5">
-        <f t="shared" si="7"/>
-        <v>28.737499999999997</v>
+        <f t="shared" si="6"/>
+        <v>31.0365</v>
       </c>
       <c r="H438" s="10" t="s">
         <v>9</v>
@@ -16385,7 +16385,7 @@
         <v>9</v>
       </c>
       <c r="G439" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H439" s="6" t="s">
@@ -16412,8 +16412,8 @@
         <v>15.99</v>
       </c>
       <c r="G440" s="5">
-        <f t="shared" si="7"/>
-        <v>19.987500000000001</v>
+        <f t="shared" si="6"/>
+        <v>21.586500000000001</v>
       </c>
       <c r="H440" s="10" t="s">
         <v>9</v>
@@ -16439,7 +16439,7 @@
         <v>9</v>
       </c>
       <c r="G441" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H441" s="6" t="s">
@@ -16466,8 +16466,8 @@
         <v>10.99</v>
       </c>
       <c r="G442" s="5">
-        <f t="shared" si="7"/>
-        <v>13.737500000000001</v>
+        <f t="shared" si="6"/>
+        <v>14.836500000000001</v>
       </c>
       <c r="H442" s="10" t="s">
         <v>9</v>
@@ -16493,7 +16493,7 @@
         <v>9</v>
       </c>
       <c r="G443" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H443" s="6" t="s">
@@ -16520,8 +16520,8 @@
         <v>14.99</v>
       </c>
       <c r="G444" s="5">
-        <f t="shared" si="7"/>
-        <v>18.737500000000001</v>
+        <f t="shared" si="6"/>
+        <v>20.236500000000003</v>
       </c>
       <c r="H444" s="10" t="s">
         <v>9</v>
@@ -16547,7 +16547,7 @@
         <v>9</v>
       </c>
       <c r="G445" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H445" s="6" t="s">
@@ -16600,7 +16600,7 @@
         <v>9</v>
       </c>
       <c r="G447" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H447" s="10" t="s">
@@ -16627,7 +16627,7 @@
         <v>9</v>
       </c>
       <c r="G448" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H448" s="6" t="s">
@@ -16654,7 +16654,7 @@
         <v>9</v>
       </c>
       <c r="G449" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H449" s="10" t="s">
@@ -16681,7 +16681,7 @@
         <v>9</v>
       </c>
       <c r="G450" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H450" s="6" t="s">
@@ -16708,7 +16708,7 @@
         <v>9</v>
       </c>
       <c r="G451" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H451" s="10" t="s">
@@ -16735,7 +16735,7 @@
         <v>9</v>
       </c>
       <c r="G452" s="5" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="G452:G515" si="7">F452*1.35</f>
         <v>#VALUE!</v>
       </c>
       <c r="H452" s="6" t="s">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="G469" s="5">
         <f t="shared" si="7"/>
-        <v>24.0625</v>
+        <v>25.987500000000001</v>
       </c>
       <c r="H469" s="6" t="s">
         <v>9</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="G470" s="5">
         <f t="shared" si="7"/>
-        <v>86.237499999999997</v>
+        <v>93.136499999999998</v>
       </c>
       <c r="H470" s="10" t="s">
         <v>9</v>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="G471" s="5">
         <f t="shared" si="7"/>
-        <v>9.3625000000000007</v>
+        <v>10.111500000000001</v>
       </c>
       <c r="H471" s="6" t="s">
         <v>9</v>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="G472" s="5">
         <f t="shared" si="7"/>
-        <v>10.612500000000001</v>
+        <v>11.461500000000001</v>
       </c>
       <c r="H472" s="10" t="s">
         <v>9</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="G473" s="5">
         <f t="shared" si="7"/>
-        <v>29.5625</v>
+        <v>31.927499999999998</v>
       </c>
       <c r="H473" s="6" t="s">
         <v>9</v>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="G474" s="5">
         <f t="shared" si="7"/>
-        <v>24.362499999999997</v>
+        <v>26.311499999999999</v>
       </c>
       <c r="H474" s="10" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="G476" s="5">
         <f t="shared" si="7"/>
-        <v>7.4875000000000007</v>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H476" s="6" t="s">
         <v>9</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="G477" s="5">
         <f t="shared" si="7"/>
-        <v>7.7875000000000005</v>
+        <v>8.4105000000000008</v>
       </c>
       <c r="H477" s="10" t="s">
         <v>9</v>
@@ -17436,7 +17436,7 @@
       </c>
       <c r="G478" s="5">
         <f t="shared" si="7"/>
-        <v>7.4875000000000007</v>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H478" s="6" t="s">
         <v>9</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="G481" s="5">
         <f t="shared" si="7"/>
-        <v>24.362499999999997</v>
+        <v>26.311499999999999</v>
       </c>
       <c r="H481" s="6" t="s">
         <v>9</v>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G482" s="5">
         <f t="shared" si="7"/>
-        <v>64.987499999999997</v>
+        <v>70.186500000000009</v>
       </c>
       <c r="H482" s="10" t="s">
         <v>9</v>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="G483" s="5">
         <f t="shared" si="7"/>
-        <v>17.1875</v>
+        <v>18.5625</v>
       </c>
       <c r="H483" s="6" t="s">
         <v>9</v>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="G484" s="5">
         <f t="shared" si="7"/>
-        <v>21.25</v>
+        <v>22.950000000000003</v>
       </c>
       <c r="H484" s="10" t="s">
         <v>9</v>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="G485" s="5">
         <f t="shared" si="7"/>
-        <v>1.3625</v>
+        <v>1.4715000000000003</v>
       </c>
       <c r="H485" s="6" t="s">
         <v>9</v>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="G486" s="5">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H486" s="10" t="s">
         <v>9</v>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="G487" s="5">
         <f t="shared" si="7"/>
-        <v>12.9375</v>
+        <v>13.9725</v>
       </c>
       <c r="H487" s="6" t="s">
         <v>9</v>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="G488" s="5">
         <f t="shared" si="7"/>
-        <v>17.487500000000001</v>
+        <v>18.886500000000002</v>
       </c>
       <c r="H488" s="10" t="s">
         <v>9</v>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="G489" s="5">
         <f t="shared" si="7"/>
-        <v>19.4375</v>
+        <v>20.992500000000003</v>
       </c>
       <c r="H489" s="6" t="s">
         <v>9</v>
@@ -17753,7 +17753,7 @@
       </c>
       <c r="G490" s="5">
         <f t="shared" si="7"/>
-        <v>3.6125000000000003</v>
+        <v>3.9015000000000004</v>
       </c>
       <c r="H490" s="6"/>
     </row>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="G491" s="5">
         <f t="shared" si="7"/>
-        <v>19.4375</v>
+        <v>20.992500000000003</v>
       </c>
       <c r="H491" s="10" t="s">
         <v>9</v>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="G492" s="5">
         <f t="shared" si="7"/>
-        <v>36.237499999999997</v>
+        <v>39.136499999999998</v>
       </c>
       <c r="H492" s="6" t="s">
         <v>9</v>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="G493" s="5">
         <f t="shared" si="7"/>
-        <v>13.112500000000001</v>
+        <v>14.161500000000002</v>
       </c>
       <c r="H493" s="10" t="s">
         <v>9</v>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="G495" s="5">
         <f t="shared" si="7"/>
-        <v>6.6124999999999998</v>
+        <v>7.1415000000000006</v>
       </c>
       <c r="H495" s="6" t="s">
         <v>9</v>
@@ -17912,7 +17912,7 @@
       </c>
       <c r="G496" s="5">
         <f t="shared" si="7"/>
-        <v>3.7375000000000003</v>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H496" s="10" t="s">
         <v>9</v>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G497" s="5">
         <f t="shared" si="7"/>
-        <v>1.8625</v>
+        <v>2.0115000000000003</v>
       </c>
       <c r="H497" s="6" t="s">
         <v>9</v>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="G498" s="5">
         <f t="shared" si="7"/>
-        <v>1.8625</v>
+        <v>2.0115000000000003</v>
       </c>
       <c r="H498" s="10" t="s">
         <v>9</v>
@@ -17992,8 +17992,8 @@
         <v>1.49</v>
       </c>
       <c r="G499" s="5">
-        <f t="shared" ref="G499:G562" si="8">F499*1.25</f>
-        <v>1.8625</v>
+        <f t="shared" si="7"/>
+        <v>2.0115000000000003</v>
       </c>
       <c r="H499" s="6" t="s">
         <v>9</v>
@@ -18019,8 +18019,8 @@
         <v>9.99</v>
       </c>
       <c r="G500" s="5">
-        <f t="shared" si="8"/>
-        <v>12.487500000000001</v>
+        <f t="shared" si="7"/>
+        <v>13.486500000000001</v>
       </c>
       <c r="H500" s="10" t="s">
         <v>9</v>
@@ -18072,8 +18072,8 @@
         <v>12.75</v>
       </c>
       <c r="G502" s="5">
-        <f t="shared" si="8"/>
-        <v>15.9375</v>
+        <f t="shared" si="7"/>
+        <v>17.212500000000002</v>
       </c>
       <c r="H502" s="6" t="s">
         <v>9</v>
@@ -18099,8 +18099,8 @@
         <v>2.99</v>
       </c>
       <c r="G503" s="5">
-        <f t="shared" si="8"/>
-        <v>3.7375000000000003</v>
+        <f t="shared" si="7"/>
+        <v>4.0365000000000002</v>
       </c>
       <c r="H503" s="10" t="s">
         <v>9</v>
@@ -18126,8 +18126,8 @@
         <v>9.0500000000000007</v>
       </c>
       <c r="G504" s="5">
-        <f t="shared" si="8"/>
-        <v>11.3125</v>
+        <f t="shared" si="7"/>
+        <v>12.217500000000001</v>
       </c>
       <c r="H504" s="6" t="s">
         <v>9</v>
@@ -18179,8 +18179,8 @@
         <v>29.99</v>
       </c>
       <c r="G506" s="5">
-        <f t="shared" si="8"/>
-        <v>37.487499999999997</v>
+        <f t="shared" si="7"/>
+        <v>40.486499999999999</v>
       </c>
       <c r="H506" s="10" t="s">
         <v>9</v>
@@ -18206,8 +18206,8 @@
         <v>6.45</v>
       </c>
       <c r="G507" s="5">
-        <f t="shared" si="8"/>
-        <v>8.0625</v>
+        <f t="shared" si="7"/>
+        <v>8.7075000000000014</v>
       </c>
       <c r="H507" s="6" t="s">
         <v>9</v>
@@ -18233,8 +18233,8 @@
         <v>32.49</v>
       </c>
       <c r="G508" s="5">
-        <f t="shared" si="8"/>
-        <v>40.612500000000004</v>
+        <f t="shared" si="7"/>
+        <v>43.861500000000007</v>
       </c>
       <c r="H508" s="10" t="s">
         <v>9</v>
@@ -18260,8 +18260,8 @@
         <v>7.69</v>
       </c>
       <c r="G509" s="5">
-        <f t="shared" si="8"/>
-        <v>9.6125000000000007</v>
+        <f t="shared" si="7"/>
+        <v>10.381500000000001</v>
       </c>
       <c r="H509" s="6" t="s">
         <v>9</v>
@@ -18313,8 +18313,8 @@
         <v>7.29</v>
       </c>
       <c r="G511" s="5">
-        <f t="shared" si="8"/>
-        <v>9.1125000000000007</v>
+        <f t="shared" si="7"/>
+        <v>9.8414999999999999</v>
       </c>
       <c r="H511" s="10" t="s">
         <v>9</v>
@@ -18340,8 +18340,8 @@
         <v>7.99</v>
       </c>
       <c r="G512" s="5">
-        <f t="shared" si="8"/>
-        <v>9.9875000000000007</v>
+        <f t="shared" si="7"/>
+        <v>10.7865</v>
       </c>
       <c r="H512" s="6" t="s">
         <v>9</v>
@@ -18367,8 +18367,8 @@
         <v>9.7899999999999991</v>
       </c>
       <c r="G513" s="5">
-        <f t="shared" si="8"/>
-        <v>12.237499999999999</v>
+        <f t="shared" si="7"/>
+        <v>13.2165</v>
       </c>
       <c r="H513" s="10" t="s">
         <v>9</v>
@@ -18394,8 +18394,8 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G514" s="5">
-        <f t="shared" si="8"/>
-        <v>21.237499999999997</v>
+        <f t="shared" si="7"/>
+        <v>22.936499999999999</v>
       </c>
       <c r="H514" s="6" t="s">
         <v>9</v>
@@ -18421,8 +18421,8 @@
         <v>12.99</v>
       </c>
       <c r="G515" s="5">
-        <f t="shared" si="8"/>
-        <v>16.237500000000001</v>
+        <f t="shared" si="7"/>
+        <v>17.5365</v>
       </c>
       <c r="H515" s="10" t="s">
         <v>9</v>
@@ -18448,8 +18448,8 @@
         <v>1.99</v>
       </c>
       <c r="G516" s="5">
-        <f t="shared" si="8"/>
-        <v>2.4874999999999998</v>
+        <f t="shared" ref="G516:G579" si="8">F516*1.35</f>
+        <v>2.6865000000000001</v>
       </c>
       <c r="H516" s="6" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
       </c>
       <c r="G517" s="5">
         <f t="shared" si="8"/>
-        <v>13.737500000000001</v>
+        <v>14.836500000000001</v>
       </c>
       <c r="H517" s="10" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="G518" s="5">
         <f t="shared" si="8"/>
-        <v>12.487500000000001</v>
+        <v>13.486500000000001</v>
       </c>
       <c r="H518" s="6" t="s">
         <v>9</v>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="G519" s="5">
         <f t="shared" si="8"/>
-        <v>13.737500000000001</v>
+        <v>14.836500000000001</v>
       </c>
       <c r="H519" s="10" t="s">
         <v>9</v>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="G520" s="5">
         <f t="shared" si="8"/>
-        <v>5.9375</v>
+        <v>6.4125000000000005</v>
       </c>
       <c r="H520" s="6" t="s">
         <v>9</v>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="G521" s="5">
         <f t="shared" si="8"/>
-        <v>2.8125</v>
+        <v>3.0375000000000001</v>
       </c>
       <c r="H521" s="10" t="s">
         <v>9</v>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G522" s="5">
         <f t="shared" si="8"/>
-        <v>2.1625000000000001</v>
+        <v>2.3355000000000001</v>
       </c>
       <c r="H522" s="6" t="s">
         <v>9</v>
@@ -18638,7 +18638,7 @@
       </c>
       <c r="G523" s="5">
         <f t="shared" si="8"/>
-        <v>6.875</v>
+        <v>7.4250000000000007</v>
       </c>
       <c r="H523" s="10" t="s">
         <v>9</v>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="G524" s="5">
         <f t="shared" si="8"/>
-        <v>6.5</v>
+        <v>7.0200000000000005</v>
       </c>
       <c r="H524" s="6" t="s">
         <v>9</v>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="G526" s="5">
         <f t="shared" si="8"/>
-        <v>14.987500000000001</v>
+        <v>16.186500000000002</v>
       </c>
       <c r="H526" s="10" t="s">
         <v>9</v>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="G527" s="5">
         <f t="shared" si="8"/>
-        <v>39.987499999999997</v>
+        <v>43.186500000000002</v>
       </c>
       <c r="H527" s="6" t="s">
         <v>9</v>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="G530" s="5">
         <f t="shared" si="8"/>
-        <v>4.4874999999999998</v>
+        <v>4.8464999999999998</v>
       </c>
       <c r="H530" s="6" t="s">
         <v>9</v>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="G531" s="5">
         <f t="shared" si="8"/>
-        <v>3.5999999999999996</v>
+        <v>3.8879999999999999</v>
       </c>
       <c r="H531" s="10" t="s">
         <v>9</v>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="G532" s="5">
         <f t="shared" si="8"/>
-        <v>4.9875000000000007</v>
+        <v>5.3865000000000007</v>
       </c>
       <c r="H532" s="6" t="s">
         <v>9</v>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="G533" s="5">
         <f t="shared" si="8"/>
-        <v>1.575</v>
+        <v>1.7010000000000001</v>
       </c>
       <c r="H533" s="10" t="s">
         <v>9</v>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="G534" s="5">
         <f t="shared" si="8"/>
-        <v>4.1875</v>
+        <v>4.5225000000000009</v>
       </c>
       <c r="H534" s="6" t="s">
         <v>9</v>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G535" s="5">
         <f t="shared" si="8"/>
-        <v>16.862500000000001</v>
+        <v>18.211500000000001</v>
       </c>
       <c r="H535" s="10" t="s">
         <v>9</v>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="G536" s="5">
         <f t="shared" si="8"/>
-        <v>12.487500000000001</v>
+        <v>13.486500000000001</v>
       </c>
       <c r="H536" s="6" t="s">
         <v>9</v>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="G537" s="5">
         <f t="shared" si="8"/>
-        <v>22.487499999999997</v>
+        <v>24.2865</v>
       </c>
       <c r="H537" s="10" t="s">
         <v>9</v>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G539" s="5">
         <f t="shared" si="8"/>
-        <v>6.75</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="H539" s="6" t="s">
         <v>9</v>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="G540" s="5">
         <f t="shared" si="8"/>
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="H540" s="10" t="s">
         <v>9</v>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="G541" s="5">
         <f t="shared" si="8"/>
-        <v>16.675000000000001</v>
+        <v>18.009</v>
       </c>
       <c r="H541" s="6" t="s">
         <v>9</v>
@@ -19148,7 +19148,7 @@
       </c>
       <c r="G542" s="5">
         <f t="shared" si="8"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H542" s="10" t="s">
         <v>9</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G543" s="5">
         <f t="shared" si="8"/>
-        <v>9.875</v>
+        <v>10.665000000000001</v>
       </c>
       <c r="H543" s="6" t="s">
         <v>9</v>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="G544" s="5">
         <f t="shared" si="8"/>
-        <v>1.5625</v>
+        <v>1.6875</v>
       </c>
       <c r="H544" s="10" t="s">
         <v>9</v>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="G545" s="5">
         <f t="shared" si="8"/>
-        <v>13.125</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="H545" s="6" t="s">
         <v>9</v>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="G546" s="5">
         <f t="shared" si="8"/>
-        <v>2.3874999999999997</v>
+        <v>2.5785</v>
       </c>
       <c r="H546" s="10" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="G547" s="5">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H547" s="6" t="s">
         <v>9</v>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="G548" s="5">
         <f t="shared" si="8"/>
-        <v>17.4375</v>
+        <v>18.8325</v>
       </c>
       <c r="H548" s="10" t="s">
         <v>9</v>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="G549" s="5">
         <f t="shared" si="8"/>
-        <v>17.5</v>
+        <v>18.900000000000002</v>
       </c>
       <c r="H549" s="6" t="s">
         <v>9</v>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="G550" s="5">
         <f t="shared" si="8"/>
-        <v>20.85</v>
+        <v>22.518000000000001</v>
       </c>
       <c r="H550" s="10" t="s">
         <v>9</v>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="G551" s="5">
         <f t="shared" si="8"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H551" s="6" t="s">
         <v>9</v>
@@ -19418,7 +19418,7 @@
       </c>
       <c r="G552" s="5">
         <f t="shared" si="8"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H552" s="10" t="s">
         <v>9</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="G553" s="5">
         <f t="shared" si="8"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H553" s="6" t="s">
         <v>9</v>
@@ -19472,7 +19472,7 @@
       </c>
       <c r="G554" s="5">
         <f t="shared" si="8"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H554" s="10" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="G555" s="5">
         <f t="shared" si="8"/>
-        <v>17.5</v>
+        <v>18.900000000000002</v>
       </c>
       <c r="H555" s="6" t="s">
         <v>9</v>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="G556" s="5">
         <f t="shared" si="8"/>
-        <v>9.5</v>
+        <v>10.26</v>
       </c>
       <c r="H556" s="10" t="s">
         <v>9</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="G557" s="5">
         <f t="shared" si="8"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H557" s="10" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="G558" s="5">
         <f t="shared" si="8"/>
-        <v>27.5</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="H558" s="6" t="s">
         <v>9</v>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="G559" s="5">
         <f t="shared" si="8"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H559" s="10" t="s">
         <v>9</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="G560" s="5">
         <f t="shared" si="8"/>
-        <v>13.737500000000001</v>
+        <v>14.836500000000001</v>
       </c>
       <c r="H560" s="6" t="s">
         <v>9</v>
@@ -19714,8 +19714,8 @@
         <v>1.3</v>
       </c>
       <c r="G563" s="5">
-        <f t="shared" ref="G563:G626" si="9">F563*1.25</f>
-        <v>1.625</v>
+        <f t="shared" si="8"/>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H563" s="10" t="s">
         <v>9</v>
@@ -19741,8 +19741,8 @@
         <v>15</v>
       </c>
       <c r="G564" s="5">
-        <f t="shared" si="9"/>
-        <v>18.75</v>
+        <f t="shared" si="8"/>
+        <v>20.25</v>
       </c>
       <c r="H564" s="6" t="s">
         <v>9</v>
@@ -19768,8 +19768,8 @@
         <v>22</v>
       </c>
       <c r="G565" s="5">
-        <f t="shared" si="9"/>
-        <v>27.5</v>
+        <f t="shared" si="8"/>
+        <v>29.700000000000003</v>
       </c>
       <c r="H565" s="10" t="s">
         <v>9</v>
@@ -19795,7 +19795,7 @@
         <v>9</v>
       </c>
       <c r="G566" s="5" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="H566" s="6" t="s">
@@ -19822,8 +19822,8 @@
         <v>18</v>
       </c>
       <c r="G567" s="5">
-        <f t="shared" si="9"/>
-        <v>22.5</v>
+        <f t="shared" si="8"/>
+        <v>24.3</v>
       </c>
       <c r="H567" s="10" t="s">
         <v>9</v>
@@ -19849,8 +19849,8 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="G568" s="5">
-        <f t="shared" si="9"/>
-        <v>5.75</v>
+        <f t="shared" si="8"/>
+        <v>6.21</v>
       </c>
       <c r="H568" s="6" t="s">
         <v>9</v>
@@ -19876,8 +19876,8 @@
         <v>8</v>
       </c>
       <c r="G569" s="5">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>10.8</v>
       </c>
       <c r="H569" s="10" t="s">
         <v>9</v>
@@ -19903,8 +19903,8 @@
         <v>6.99</v>
       </c>
       <c r="G570" s="5">
-        <f t="shared" si="9"/>
-        <v>8.7375000000000007</v>
+        <f t="shared" si="8"/>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H570" s="6" t="s">
         <v>9</v>
@@ -19930,8 +19930,8 @@
         <v>6.99</v>
       </c>
       <c r="G571" s="5">
-        <f t="shared" si="9"/>
-        <v>8.7375000000000007</v>
+        <f t="shared" si="8"/>
+        <v>9.4365000000000006</v>
       </c>
       <c r="H571" s="10" t="s">
         <v>9</v>
@@ -19957,8 +19957,8 @@
         <v>3.89</v>
       </c>
       <c r="G572" s="5">
-        <f t="shared" si="9"/>
-        <v>4.8624999999999998</v>
+        <f t="shared" si="8"/>
+        <v>5.2515000000000009</v>
       </c>
       <c r="H572" s="6" t="s">
         <v>9</v>
@@ -19984,8 +19984,8 @@
         <v>10.199999999999999</v>
       </c>
       <c r="G573" s="5">
-        <f t="shared" si="9"/>
-        <v>12.75</v>
+        <f t="shared" si="8"/>
+        <v>13.77</v>
       </c>
       <c r="H573" s="10" t="s">
         <v>9</v>
@@ -20011,8 +20011,8 @@
         <v>14</v>
       </c>
       <c r="G574" s="5">
-        <f t="shared" si="9"/>
-        <v>17.5</v>
+        <f t="shared" si="8"/>
+        <v>18.900000000000002</v>
       </c>
       <c r="H574" s="6" t="s">
         <v>9</v>
@@ -20038,8 +20038,8 @@
         <v>22</v>
       </c>
       <c r="G575" s="5">
-        <f t="shared" si="9"/>
-        <v>27.5</v>
+        <f t="shared" si="8"/>
+        <v>29.700000000000003</v>
       </c>
       <c r="H575" s="10" t="s">
         <v>9</v>
@@ -20065,8 +20065,8 @@
         <v>5.49</v>
       </c>
       <c r="G576" s="5">
-        <f t="shared" si="9"/>
-        <v>6.8625000000000007</v>
+        <f t="shared" si="8"/>
+        <v>7.4115000000000011</v>
       </c>
       <c r="H576" s="6" t="s">
         <v>9</v>
@@ -20092,8 +20092,8 @@
         <v>22</v>
       </c>
       <c r="G577" s="5">
-        <f t="shared" si="9"/>
-        <v>27.5</v>
+        <f t="shared" si="8"/>
+        <v>29.700000000000003</v>
       </c>
       <c r="H577" s="10" t="s">
         <v>9</v>
@@ -20119,8 +20119,8 @@
         <v>1.3</v>
       </c>
       <c r="G578" s="5">
-        <f t="shared" si="9"/>
-        <v>1.625</v>
+        <f t="shared" si="8"/>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H578" s="6" t="s">
         <v>9</v>
@@ -20146,8 +20146,8 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="G579" s="5">
-        <f t="shared" si="9"/>
-        <v>10.375</v>
+        <f t="shared" si="8"/>
+        <v>11.205000000000002</v>
       </c>
       <c r="H579" s="10" t="s">
         <v>9</v>
@@ -20173,8 +20173,8 @@
         <v>36</v>
       </c>
       <c r="G580" s="5">
-        <f t="shared" si="9"/>
-        <v>45</v>
+        <f t="shared" ref="G580:G631" si="9">F580*1.35</f>
+        <v>48.6</v>
       </c>
       <c r="H580" s="6" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G581" s="5">
         <f t="shared" si="9"/>
-        <v>6.9874999999999998</v>
+        <v>7.5465</v>
       </c>
       <c r="H581" s="10" t="s">
         <v>9</v>
@@ -20228,7 +20228,7 @@
       </c>
       <c r="G582" s="5">
         <f t="shared" si="9"/>
-        <v>9.3625000000000007</v>
+        <v>10.111500000000001</v>
       </c>
       <c r="H582" s="6" t="s">
         <v>9</v>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="G583" s="5">
         <f t="shared" si="9"/>
-        <v>2.1875</v>
+        <v>2.3625000000000003</v>
       </c>
       <c r="H583" s="10" t="s">
         <v>9</v>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="G584" s="5">
         <f t="shared" si="9"/>
-        <v>14.987500000000001</v>
+        <v>16.186500000000002</v>
       </c>
       <c r="H584" s="6" t="s">
         <v>9</v>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="G585" s="5">
         <f t="shared" si="9"/>
-        <v>14.987500000000001</v>
+        <v>16.186500000000002</v>
       </c>
       <c r="H585" s="10" t="s">
         <v>9</v>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="G586" s="5">
         <f t="shared" si="9"/>
-        <v>4.3625000000000007</v>
+        <v>4.7115000000000009</v>
       </c>
       <c r="H586" s="6" t="s">
         <v>9</v>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="G587" s="5">
         <f t="shared" si="9"/>
-        <v>11.25</v>
+        <v>12.15</v>
       </c>
       <c r="H587" s="10" t="s">
         <v>9</v>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="G588" s="5">
         <f t="shared" si="9"/>
-        <v>2.75</v>
+        <v>2.9700000000000006</v>
       </c>
       <c r="H588" s="6" t="s">
         <v>9</v>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="G589" s="5">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="H589" s="10" t="s">
         <v>9</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="G590" s="5">
         <f t="shared" si="9"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H590" s="6" t="s">
         <v>9</v>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="G591" s="5">
         <f t="shared" si="9"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H591" s="10" t="s">
         <v>9</v>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="G592" s="5">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="H592" s="6" t="s">
         <v>9</v>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="G593" s="5">
         <f t="shared" si="9"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H593" s="10" t="s">
         <v>9</v>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="G594" s="5">
         <f t="shared" si="9"/>
-        <v>4.1124999999999998</v>
+        <v>4.4415000000000004</v>
       </c>
       <c r="H594" s="6" t="s">
         <v>9</v>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="G595" s="5">
         <f t="shared" si="9"/>
-        <v>7.4875000000000007</v>
+        <v>8.0865000000000009</v>
       </c>
       <c r="H595" s="10" t="s">
         <v>9</v>
@@ -20606,7 +20606,7 @@
       </c>
       <c r="G596" s="5">
         <f t="shared" si="9"/>
-        <v>2.375</v>
+        <v>2.5649999999999999</v>
       </c>
       <c r="H596" s="6" t="s">
         <v>9</v>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="G597" s="5">
         <f t="shared" si="9"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H597" s="10" t="s">
         <v>9</v>
@@ -20660,7 +20660,7 @@
       </c>
       <c r="G598" s="5">
         <f t="shared" si="9"/>
-        <v>5.3125</v>
+        <v>5.7375000000000007</v>
       </c>
       <c r="H598" s="6" t="s">
         <v>9</v>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="G599" s="5">
         <f t="shared" si="9"/>
-        <v>9.9875000000000007</v>
+        <v>10.7865</v>
       </c>
       <c r="H599" s="10" t="s">
         <v>9</v>
@@ -20714,7 +20714,7 @@
       </c>
       <c r="G600" s="5">
         <f t="shared" si="9"/>
-        <v>31.25</v>
+        <v>33.75</v>
       </c>
       <c r="H600" s="6" t="s">
         <v>9</v>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="G601" s="5">
         <f t="shared" si="9"/>
-        <v>16.875</v>
+        <v>18.225000000000001</v>
       </c>
       <c r="H601" s="10" t="s">
         <v>9</v>
@@ -20768,7 +20768,7 @@
       </c>
       <c r="G602" s="5">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="H602" s="6" t="s">
         <v>9</v>
@@ -20795,7 +20795,7 @@
       </c>
       <c r="G603" s="5">
         <f t="shared" si="9"/>
-        <v>11.25</v>
+        <v>12.15</v>
       </c>
       <c r="H603" s="10" t="s">
         <v>9</v>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="G604" s="5">
         <f t="shared" si="9"/>
-        <v>1.625</v>
+        <v>1.7550000000000001</v>
       </c>
       <c r="H604" s="6" t="s">
         <v>9</v>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G605" s="5">
         <f t="shared" si="9"/>
-        <v>2.1875</v>
+        <v>2.3625000000000003</v>
       </c>
       <c r="H605" s="10" t="s">
         <v>9</v>
@@ -20876,7 +20876,7 @@
       </c>
       <c r="G606" s="5">
         <f t="shared" si="9"/>
-        <v>2.1875</v>
+        <v>2.3625000000000003</v>
       </c>
       <c r="H606" s="6" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
       </c>
       <c r="G607" s="5">
         <f t="shared" si="9"/>
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="H607" s="10" t="s">
         <v>9</v>
@@ -20956,7 +20956,7 @@
       </c>
       <c r="G609" s="5">
         <f t="shared" si="9"/>
-        <v>35</v>
+        <v>37.800000000000004</v>
       </c>
       <c r="H609" s="6" t="s">
         <v>9</v>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="G610" s="5">
         <f t="shared" si="9"/>
-        <v>32.5</v>
+        <v>35.1</v>
       </c>
       <c r="H610" s="10" t="s">
         <v>9</v>
@@ -21010,7 +21010,7 @@
       </c>
       <c r="G611" s="5">
         <f t="shared" si="9"/>
-        <v>33.337500000000006</v>
+        <v>36.004500000000007</v>
       </c>
       <c r="H611" s="6" t="s">
         <v>9</v>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G612" s="5">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H612" s="10" t="s">
         <v>9</v>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="G613" s="5">
         <f t="shared" si="9"/>
-        <v>36.25</v>
+        <v>39.150000000000006</v>
       </c>
       <c r="H613" s="6" t="s">
         <v>9</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="G614" s="5">
         <f t="shared" si="9"/>
-        <v>23.375</v>
+        <v>25.245000000000001</v>
       </c>
       <c r="H614" s="10" t="s">
         <v>9</v>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="G615" s="5">
         <f t="shared" si="9"/>
-        <v>0.91249999999999998</v>
+        <v>0.98550000000000004</v>
       </c>
       <c r="H615" s="6" t="s">
         <v>9</v>
@@ -21145,7 +21145,7 @@
       </c>
       <c r="G616" s="5">
         <f t="shared" si="9"/>
-        <v>31.25</v>
+        <v>33.75</v>
       </c>
       <c r="H616" s="10" t="s">
         <v>9</v>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="G617" s="5">
         <f t="shared" si="9"/>
-        <v>31.25</v>
+        <v>33.75</v>
       </c>
       <c r="H617" s="6" t="s">
         <v>9</v>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="G618" s="5">
         <f t="shared" si="9"/>
-        <v>31.25</v>
+        <v>33.75</v>
       </c>
       <c r="H618" s="10" t="s">
         <v>9</v>
@@ -21226,7 +21226,7 @@
       </c>
       <c r="G619" s="5">
         <f t="shared" si="9"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H619" s="6" t="s">
         <v>9</v>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="G620" s="5">
         <f t="shared" si="9"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H620" s="10" t="s">
         <v>9</v>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="G621" s="5">
         <f t="shared" si="9"/>
-        <v>31.25</v>
+        <v>33.75</v>
       </c>
       <c r="H621" s="6" t="s">
         <v>9</v>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="G622" s="5">
         <f t="shared" si="9"/>
-        <v>17.5</v>
+        <v>18.900000000000002</v>
       </c>
       <c r="H622" s="10" t="s">
         <v>9</v>
@@ -21334,7 +21334,7 @@
       </c>
       <c r="G623" s="5">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>32.400000000000006</v>
       </c>
       <c r="H623" s="6" t="s">
         <v>9</v>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="G624" s="5">
         <f t="shared" si="9"/>
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H624" s="10" t="s">
         <v>9</v>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="G625" s="5">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>43.2</v>
       </c>
       <c r="H625" s="6" t="s">
         <v>9</v>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="G626" s="5">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>32.400000000000006</v>
       </c>
       <c r="H626" s="10" t="s">
         <v>9</v>
@@ -21441,8 +21441,8 @@
         <v>16</v>
       </c>
       <c r="G627" s="5">
-        <f t="shared" ref="G627:G631" si="10">F627*1.25</f>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>21.6</v>
       </c>
       <c r="H627" s="6" t="s">
         <v>9</v>
@@ -21468,8 +21468,8 @@
         <v>20</v>
       </c>
       <c r="G628" s="5">
-        <f t="shared" si="10"/>
-        <v>25</v>
+        <f t="shared" si="9"/>
+        <v>27</v>
       </c>
       <c r="H628" s="10" t="s">
         <v>9</v>
@@ -21495,8 +21495,8 @@
         <v>18</v>
       </c>
       <c r="G629" s="5">
-        <f t="shared" si="10"/>
-        <v>22.5</v>
+        <f t="shared" si="9"/>
+        <v>24.3</v>
       </c>
       <c r="H629" s="6" t="s">
         <v>9</v>
@@ -21522,8 +21522,8 @@
         <v>4.75</v>
       </c>
       <c r="G630" s="5">
-        <f t="shared" si="10"/>
-        <v>5.9375</v>
+        <f t="shared" si="9"/>
+        <v>6.4125000000000005</v>
       </c>
       <c r="H630" s="10" t="s">
         <v>9</v>
@@ -21549,8 +21549,8 @@
         <v>28</v>
       </c>
       <c r="G631" s="5">
-        <f t="shared" si="10"/>
-        <v>35</v>
+        <f t="shared" si="9"/>
+        <v>37.800000000000004</v>
       </c>
       <c r="H631" s="6" t="s">
         <v>9</v>

--- a/data/ATH PRICE LIST - MAIN.xlsx
+++ b/data/ATH PRICE LIST - MAIN.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A45085-BC02-42A1-BC6F-02CA2ABB84D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F39EC97-35D7-47A3-972D-0E217864DC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5094" uniqueCount="1577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5096" uniqueCount="1577">
   <si>
     <t>ITEM CODE</t>
   </si>
@@ -22742,7 +22742,9 @@
       <c r="B615" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="C615" s="8"/>
+      <c r="C615" s="8" t="s">
+        <v>1553</v>
+      </c>
       <c r="D615" s="7" t="s">
         <v>9</v>
       </c>
@@ -22770,7 +22772,9 @@
       <c r="B616" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="C616" s="4"/>
+      <c r="C616" s="4" t="s">
+        <v>1553</v>
+      </c>
       <c r="D616" s="3" t="s">
         <v>9</v>
       </c>
